--- a/code/resultados/NWJSSP_OADG_NEH(MS+ELS+SA).xlsx
+++ b/code/resultados/NWJSSP_OADG_NEH(MS+ELS+SA).xlsx
@@ -12,6 +12,15 @@
     <sheet name="ft10" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="ft10r" sheetId="4" state="visible" r:id="rId4"/>
     <sheet name="ft20" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="ft20r" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="tai_j10_m10_1" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="tai_j10_m10_1r" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="tai_j100_m10_1" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="tai_j100_m10_1r" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="tai_j100_m100_1" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="tai_j100_m100_1r" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="tai_j1000_m10_1" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet name="tai_j1000_m10_1r" sheetId="14" state="visible" r:id="rId14"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -453,6 +462,8024 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:CV2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="n">
+        <v>7011692</v>
+      </c>
+      <c r="B1" t="n">
+        <v>3600295</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>32994</v>
+      </c>
+      <c r="B2" t="n">
+        <v>11834</v>
+      </c>
+      <c r="C2" t="n">
+        <v>68888</v>
+      </c>
+      <c r="D2" t="n">
+        <v>140727</v>
+      </c>
+      <c r="E2" t="n">
+        <v>80593</v>
+      </c>
+      <c r="F2" t="n">
+        <v>70775</v>
+      </c>
+      <c r="G2" t="n">
+        <v>81977</v>
+      </c>
+      <c r="H2" t="n">
+        <v>135122</v>
+      </c>
+      <c r="I2" t="n">
+        <v>139091</v>
+      </c>
+      <c r="J2" t="n">
+        <v>16171</v>
+      </c>
+      <c r="K2" t="n">
+        <v>54750</v>
+      </c>
+      <c r="L2" t="n">
+        <v>43926</v>
+      </c>
+      <c r="M2" t="n">
+        <v>5460</v>
+      </c>
+      <c r="N2" t="n">
+        <v>95181</v>
+      </c>
+      <c r="O2" t="n">
+        <v>41987</v>
+      </c>
+      <c r="P2" t="n">
+        <v>16744</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>39957</v>
+      </c>
+      <c r="R2" t="n">
+        <v>37995</v>
+      </c>
+      <c r="S2" t="n">
+        <v>37072</v>
+      </c>
+      <c r="T2" t="n">
+        <v>72088</v>
+      </c>
+      <c r="U2" t="n">
+        <v>72973</v>
+      </c>
+      <c r="V2" t="n">
+        <v>129735</v>
+      </c>
+      <c r="W2" t="n">
+        <v>25361</v>
+      </c>
+      <c r="X2" t="n">
+        <v>86848</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>40713</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>107636</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>43674</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>93240</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>28297</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>50100</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>124082</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>114691</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>58023</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>28705</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>11443</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>48020</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>137141</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>115952</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>133141</v>
+      </c>
+      <c r="AO2" t="n">
+        <v>1846</v>
+      </c>
+      <c r="AP2" t="n">
+        <v>134739</v>
+      </c>
+      <c r="AQ2" t="n">
+        <v>80179</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>91603</v>
+      </c>
+      <c r="AS2" t="n">
+        <v>21263</v>
+      </c>
+      <c r="AT2" t="n">
+        <v>88427</v>
+      </c>
+      <c r="AU2" t="n">
+        <v>2415</v>
+      </c>
+      <c r="AV2" t="n">
+        <v>56537</v>
+      </c>
+      <c r="AW2" t="n">
+        <v>83936</v>
+      </c>
+      <c r="AX2" t="n">
+        <v>61995</v>
+      </c>
+      <c r="AY2" t="n">
+        <v>131733</v>
+      </c>
+      <c r="AZ2" t="n">
+        <v>127754</v>
+      </c>
+      <c r="BA2" t="n">
+        <v>10562</v>
+      </c>
+      <c r="BB2" t="n">
+        <v>100478</v>
+      </c>
+      <c r="BC2" t="n">
+        <v>20120</v>
+      </c>
+      <c r="BD2" t="n">
+        <v>27215</v>
+      </c>
+      <c r="BE2" t="n">
+        <v>76938</v>
+      </c>
+      <c r="BF2" t="n">
+        <v>109480</v>
+      </c>
+      <c r="BG2" t="n">
+        <v>1354</v>
+      </c>
+      <c r="BH2" t="n">
+        <v>34188</v>
+      </c>
+      <c r="BI2" t="n">
+        <v>30818</v>
+      </c>
+      <c r="BJ2" t="n">
+        <v>31556</v>
+      </c>
+      <c r="BK2" t="n">
+        <v>70497</v>
+      </c>
+      <c r="BL2" t="n">
+        <v>85667</v>
+      </c>
+      <c r="BM2" t="n">
+        <v>64527</v>
+      </c>
+      <c r="BN2" t="n">
+        <v>52081</v>
+      </c>
+      <c r="BO2" t="n">
+        <v>14245</v>
+      </c>
+      <c r="BP2" t="n">
+        <v>58297</v>
+      </c>
+      <c r="BQ2" t="n">
+        <v>78041</v>
+      </c>
+      <c r="BR2" t="n">
+        <v>54570</v>
+      </c>
+      <c r="BS2" t="n">
+        <v>98709</v>
+      </c>
+      <c r="BT2" t="n">
+        <v>90650</v>
+      </c>
+      <c r="BU2" t="n">
+        <v>20345</v>
+      </c>
+      <c r="BV2" t="n">
+        <v>47338</v>
+      </c>
+      <c r="BW2" t="n">
+        <v>65327</v>
+      </c>
+      <c r="BX2" t="n">
+        <v>61276</v>
+      </c>
+      <c r="BY2" t="n">
+        <v>85082</v>
+      </c>
+      <c r="BZ2" t="n">
+        <v>102904</v>
+      </c>
+      <c r="CA2" t="n">
+        <v>32754</v>
+      </c>
+      <c r="CB2" t="n">
+        <v>104354</v>
+      </c>
+      <c r="CC2" t="n">
+        <v>124841</v>
+      </c>
+      <c r="CD2" t="n">
+        <v>24877</v>
+      </c>
+      <c r="CE2" t="n">
+        <v>97314</v>
+      </c>
+      <c r="CF2" t="n">
+        <v>107967</v>
+      </c>
+      <c r="CG2" t="n">
+        <v>22219</v>
+      </c>
+      <c r="CH2" t="n">
+        <v>50714</v>
+      </c>
+      <c r="CI2" t="n">
+        <v>17644</v>
+      </c>
+      <c r="CJ2" t="n">
+        <v>5806</v>
+      </c>
+      <c r="CK2" t="n">
+        <v>120193</v>
+      </c>
+      <c r="CL2" t="n">
+        <v>119470</v>
+      </c>
+      <c r="CM2" t="n">
+        <v>10304</v>
+      </c>
+      <c r="CN2" t="n">
+        <v>66799</v>
+      </c>
+      <c r="CO2" t="n">
+        <v>6426</v>
+      </c>
+      <c r="CP2" t="n">
+        <v>16591</v>
+      </c>
+      <c r="CQ2" t="n">
+        <v>63815</v>
+      </c>
+      <c r="CR2" t="n">
+        <v>112230</v>
+      </c>
+      <c r="CS2" t="n">
+        <v>73861</v>
+      </c>
+      <c r="CT2" t="n">
+        <v>114852</v>
+      </c>
+      <c r="CU2" t="n">
+        <v>74872</v>
+      </c>
+      <c r="CV2" t="n">
+        <v>91164</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:CV2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="n">
+        <v>44005735</v>
+      </c>
+      <c r="B1" t="n">
+        <v>3606431</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>85780</v>
+      </c>
+      <c r="B2" t="n">
+        <v>360674</v>
+      </c>
+      <c r="C2" t="n">
+        <v>733257</v>
+      </c>
+      <c r="D2" t="n">
+        <v>15899</v>
+      </c>
+      <c r="E2" t="n">
+        <v>226172</v>
+      </c>
+      <c r="F2" t="n">
+        <v>762550</v>
+      </c>
+      <c r="G2" t="n">
+        <v>162871</v>
+      </c>
+      <c r="H2" t="n">
+        <v>61034</v>
+      </c>
+      <c r="I2" t="n">
+        <v>684981</v>
+      </c>
+      <c r="J2" t="n">
+        <v>535588</v>
+      </c>
+      <c r="K2" t="n">
+        <v>465784</v>
+      </c>
+      <c r="L2" t="n">
+        <v>502438</v>
+      </c>
+      <c r="M2" t="n">
+        <v>293613</v>
+      </c>
+      <c r="N2" t="n">
+        <v>802522</v>
+      </c>
+      <c r="O2" t="n">
+        <v>151544</v>
+      </c>
+      <c r="P2" t="n">
+        <v>320200</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>140563</v>
+      </c>
+      <c r="R2" t="n">
+        <v>441655</v>
+      </c>
+      <c r="S2" t="n">
+        <v>245691</v>
+      </c>
+      <c r="T2" t="n">
+        <v>118098</v>
+      </c>
+      <c r="U2" t="n">
+        <v>473573</v>
+      </c>
+      <c r="V2" t="n">
+        <v>190009</v>
+      </c>
+      <c r="W2" t="n">
+        <v>19436</v>
+      </c>
+      <c r="X2" t="n">
+        <v>172173</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>699761</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>583817</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>250555</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>813811</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>212265</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>629195</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>784</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>561720</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>72058</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>258573</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>54928</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>581968</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>615019</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>43738</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>511521</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>226053</v>
+      </c>
+      <c r="AO2" t="n">
+        <v>660895</v>
+      </c>
+      <c r="AP2" t="n">
+        <v>547843</v>
+      </c>
+      <c r="AQ2" t="n">
+        <v>452371</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>765810</v>
+      </c>
+      <c r="AS2" t="n">
+        <v>391688</v>
+      </c>
+      <c r="AT2" t="n">
+        <v>154991</v>
+      </c>
+      <c r="AU2" t="n">
+        <v>683009</v>
+      </c>
+      <c r="AV2" t="n">
+        <v>324171</v>
+      </c>
+      <c r="AW2" t="n">
+        <v>837380</v>
+      </c>
+      <c r="AX2" t="n">
+        <v>85613</v>
+      </c>
+      <c r="AY2" t="n">
+        <v>529663</v>
+      </c>
+      <c r="AZ2" t="n">
+        <v>775611</v>
+      </c>
+      <c r="BA2" t="n">
+        <v>373644</v>
+      </c>
+      <c r="BB2" t="n">
+        <v>486629</v>
+      </c>
+      <c r="BC2" t="n">
+        <v>795666</v>
+      </c>
+      <c r="BD2" t="n">
+        <v>425537</v>
+      </c>
+      <c r="BE2" t="n">
+        <v>722188</v>
+      </c>
+      <c r="BF2" t="n">
+        <v>605370</v>
+      </c>
+      <c r="BG2" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH2" t="n">
+        <v>463543</v>
+      </c>
+      <c r="BI2" t="n">
+        <v>669968</v>
+      </c>
+      <c r="BJ2" t="n">
+        <v>396281</v>
+      </c>
+      <c r="BK2" t="n">
+        <v>283642</v>
+      </c>
+      <c r="BL2" t="n">
+        <v>28140</v>
+      </c>
+      <c r="BM2" t="n">
+        <v>674237</v>
+      </c>
+      <c r="BN2" t="n">
+        <v>666225</v>
+      </c>
+      <c r="BO2" t="n">
+        <v>6813</v>
+      </c>
+      <c r="BP2" t="n">
+        <v>349860</v>
+      </c>
+      <c r="BQ2" t="n">
+        <v>116393</v>
+      </c>
+      <c r="BR2" t="n">
+        <v>201074</v>
+      </c>
+      <c r="BS2" t="n">
+        <v>49608</v>
+      </c>
+      <c r="BT2" t="n">
+        <v>129910</v>
+      </c>
+      <c r="BU2" t="n">
+        <v>269145</v>
+      </c>
+      <c r="BV2" t="n">
+        <v>525323</v>
+      </c>
+      <c r="BW2" t="n">
+        <v>332988</v>
+      </c>
+      <c r="BX2" t="n">
+        <v>727742</v>
+      </c>
+      <c r="BY2" t="n">
+        <v>178457</v>
+      </c>
+      <c r="BZ2" t="n">
+        <v>453338</v>
+      </c>
+      <c r="CA2" t="n">
+        <v>406478</v>
+      </c>
+      <c r="CB2" t="n">
+        <v>371403</v>
+      </c>
+      <c r="CC2" t="n">
+        <v>300117</v>
+      </c>
+      <c r="CD2" t="n">
+        <v>815098</v>
+      </c>
+      <c r="CE2" t="n">
+        <v>619501</v>
+      </c>
+      <c r="CF2" t="n">
+        <v>163262</v>
+      </c>
+      <c r="CG2" t="n">
+        <v>84505</v>
+      </c>
+      <c r="CH2" t="n">
+        <v>421154</v>
+      </c>
+      <c r="CI2" t="n">
+        <v>548509</v>
+      </c>
+      <c r="CJ2" t="n">
+        <v>102536</v>
+      </c>
+      <c r="CK2" t="n">
+        <v>565718</v>
+      </c>
+      <c r="CL2" t="n">
+        <v>194760</v>
+      </c>
+      <c r="CM2" t="n">
+        <v>338267</v>
+      </c>
+      <c r="CN2" t="n">
+        <v>254576</v>
+      </c>
+      <c r="CO2" t="n">
+        <v>122722</v>
+      </c>
+      <c r="CP2" t="n">
+        <v>261133</v>
+      </c>
+      <c r="CQ2" t="n">
+        <v>815235</v>
+      </c>
+      <c r="CR2" t="n">
+        <v>636240</v>
+      </c>
+      <c r="CS2" t="n">
+        <v>416553</v>
+      </c>
+      <c r="CT2" t="n">
+        <v>1019</v>
+      </c>
+      <c r="CU2" t="n">
+        <v>747899</v>
+      </c>
+      <c r="CV2" t="n">
+        <v>597745</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:CV2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="n">
+        <v>46649674</v>
+      </c>
+      <c r="B1" t="n">
+        <v>3604681</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>405967</v>
+      </c>
+      <c r="B2" t="n">
+        <v>561113</v>
+      </c>
+      <c r="C2" t="n">
+        <v>320506</v>
+      </c>
+      <c r="D2" t="n">
+        <v>250889</v>
+      </c>
+      <c r="E2" t="n">
+        <v>163472</v>
+      </c>
+      <c r="F2" t="n">
+        <v>843761</v>
+      </c>
+      <c r="G2" t="n">
+        <v>82312</v>
+      </c>
+      <c r="H2" t="n">
+        <v>542879</v>
+      </c>
+      <c r="I2" t="n">
+        <v>581533</v>
+      </c>
+      <c r="J2" t="n">
+        <v>630841</v>
+      </c>
+      <c r="K2" t="n">
+        <v>98132</v>
+      </c>
+      <c r="L2" t="n">
+        <v>462048</v>
+      </c>
+      <c r="M2" t="n">
+        <v>121722</v>
+      </c>
+      <c r="N2" t="n">
+        <v>489094</v>
+      </c>
+      <c r="O2" t="n">
+        <v>487692</v>
+      </c>
+      <c r="P2" t="n">
+        <v>639751</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>448380</v>
+      </c>
+      <c r="R2" t="n">
+        <v>538435</v>
+      </c>
+      <c r="S2" t="n">
+        <v>74716</v>
+      </c>
+      <c r="T2" t="n">
+        <v>349677</v>
+      </c>
+      <c r="U2" t="n">
+        <v>817038</v>
+      </c>
+      <c r="V2" t="n">
+        <v>246009</v>
+      </c>
+      <c r="W2" t="n">
+        <v>394387</v>
+      </c>
+      <c r="X2" t="n">
+        <v>653327</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>134598</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>42869</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>753489</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>672679</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>494846</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>732137</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>716249</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>373305</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>36422</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>87598</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>742641</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>423956</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>765630</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>221853</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>490455</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>150987</v>
+      </c>
+      <c r="AO2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP2" t="n">
+        <v>276039</v>
+      </c>
+      <c r="AQ2" t="n">
+        <v>395038</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>359764</v>
+      </c>
+      <c r="AS2" t="n">
+        <v>441641</v>
+      </c>
+      <c r="AT2" t="n">
+        <v>284316</v>
+      </c>
+      <c r="AU2" t="n">
+        <v>241279</v>
+      </c>
+      <c r="AV2" t="n">
+        <v>693436</v>
+      </c>
+      <c r="AW2" t="n">
+        <v>789789</v>
+      </c>
+      <c r="AX2" t="n">
+        <v>119581</v>
+      </c>
+      <c r="AY2" t="n">
+        <v>841075</v>
+      </c>
+      <c r="AZ2" t="n">
+        <v>311926</v>
+      </c>
+      <c r="BA2" t="n">
+        <v>380124</v>
+      </c>
+      <c r="BB2" t="n">
+        <v>782083</v>
+      </c>
+      <c r="BC2" t="n">
+        <v>529292</v>
+      </c>
+      <c r="BD2" t="n">
+        <v>525165</v>
+      </c>
+      <c r="BE2" t="n">
+        <v>309325</v>
+      </c>
+      <c r="BF2" t="n">
+        <v>721188</v>
+      </c>
+      <c r="BG2" t="n">
+        <v>214787</v>
+      </c>
+      <c r="BH2" t="n">
+        <v>72409</v>
+      </c>
+      <c r="BI2" t="n">
+        <v>341547</v>
+      </c>
+      <c r="BJ2" t="n">
+        <v>879485</v>
+      </c>
+      <c r="BK2" t="n">
+        <v>697752</v>
+      </c>
+      <c r="BL2" t="n">
+        <v>230837</v>
+      </c>
+      <c r="BM2" t="n">
+        <v>352622</v>
+      </c>
+      <c r="BN2" t="n">
+        <v>134294</v>
+      </c>
+      <c r="BO2" t="n">
+        <v>176623</v>
+      </c>
+      <c r="BP2" t="n">
+        <v>808483</v>
+      </c>
+      <c r="BQ2" t="n">
+        <v>572952</v>
+      </c>
+      <c r="BR2" t="n">
+        <v>16313</v>
+      </c>
+      <c r="BS2" t="n">
+        <v>674065</v>
+      </c>
+      <c r="BT2" t="n">
+        <v>644644</v>
+      </c>
+      <c r="BU2" t="n">
+        <v>863554</v>
+      </c>
+      <c r="BV2" t="n">
+        <v>42752</v>
+      </c>
+      <c r="BW2" t="n">
+        <v>776840</v>
+      </c>
+      <c r="BX2" t="n">
+        <v>264682</v>
+      </c>
+      <c r="BY2" t="n">
+        <v>583697</v>
+      </c>
+      <c r="BZ2" t="n">
+        <v>219104</v>
+      </c>
+      <c r="CA2" t="n">
+        <v>468553</v>
+      </c>
+      <c r="CB2" t="n">
+        <v>550247</v>
+      </c>
+      <c r="CC2" t="n">
+        <v>616372</v>
+      </c>
+      <c r="CD2" t="n">
+        <v>418919</v>
+      </c>
+      <c r="CE2" t="n">
+        <v>693982</v>
+      </c>
+      <c r="CF2" t="n">
+        <v>15230</v>
+      </c>
+      <c r="CG2" t="n">
+        <v>505645</v>
+      </c>
+      <c r="CH2" t="n">
+        <v>91278</v>
+      </c>
+      <c r="CI2" t="n">
+        <v>326967</v>
+      </c>
+      <c r="CJ2" t="n">
+        <v>0</v>
+      </c>
+      <c r="CK2" t="n">
+        <v>190703</v>
+      </c>
+      <c r="CL2" t="n">
+        <v>32734</v>
+      </c>
+      <c r="CM2" t="n">
+        <v>522</v>
+      </c>
+      <c r="CN2" t="n">
+        <v>597527</v>
+      </c>
+      <c r="CO2" t="n">
+        <v>644590</v>
+      </c>
+      <c r="CP2" t="n">
+        <v>896858</v>
+      </c>
+      <c r="CQ2" t="n">
+        <v>623500</v>
+      </c>
+      <c r="CR2" t="n">
+        <v>161096</v>
+      </c>
+      <c r="CS2" t="n">
+        <v>201916</v>
+      </c>
+      <c r="CT2" t="n">
+        <v>197006</v>
+      </c>
+      <c r="CU2" t="n">
+        <v>509229</v>
+      </c>
+      <c r="CV2" t="n">
+        <v>296234</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:ALL2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="n">
+        <v>581288120</v>
+      </c>
+      <c r="B1" t="n">
+        <v>3686472</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>906356</v>
+      </c>
+      <c r="B2" t="n">
+        <v>183357</v>
+      </c>
+      <c r="C2" t="n">
+        <v>944053</v>
+      </c>
+      <c r="D2" t="n">
+        <v>859993</v>
+      </c>
+      <c r="E2" t="n">
+        <v>698323</v>
+      </c>
+      <c r="F2" t="n">
+        <v>421585</v>
+      </c>
+      <c r="G2" t="n">
+        <v>316568</v>
+      </c>
+      <c r="H2" t="n">
+        <v>6991</v>
+      </c>
+      <c r="I2" t="n">
+        <v>318497</v>
+      </c>
+      <c r="J2" t="n">
+        <v>706921</v>
+      </c>
+      <c r="K2" t="n">
+        <v>679637</v>
+      </c>
+      <c r="L2" t="n">
+        <v>1122139</v>
+      </c>
+      <c r="M2" t="n">
+        <v>17171</v>
+      </c>
+      <c r="N2" t="n">
+        <v>192314</v>
+      </c>
+      <c r="O2" t="n">
+        <v>758523</v>
+      </c>
+      <c r="P2" t="n">
+        <v>1003796</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>839914</v>
+      </c>
+      <c r="R2" t="n">
+        <v>82735</v>
+      </c>
+      <c r="S2" t="n">
+        <v>1050278</v>
+      </c>
+      <c r="T2" t="n">
+        <v>702026</v>
+      </c>
+      <c r="U2" t="n">
+        <v>22628</v>
+      </c>
+      <c r="V2" t="n">
+        <v>640473</v>
+      </c>
+      <c r="W2" t="n">
+        <v>895130</v>
+      </c>
+      <c r="X2" t="n">
+        <v>984397</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>693003</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>482327</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>796335</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>535384</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>30750</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>129364</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>672460</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>143713</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>178598</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>892905</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>161067</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>134985</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>265393</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>1080102</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>917985</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>798307</v>
+      </c>
+      <c r="AO2" t="n">
+        <v>355520</v>
+      </c>
+      <c r="AP2" t="n">
+        <v>661231</v>
+      </c>
+      <c r="AQ2" t="n">
+        <v>753227</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>4503</v>
+      </c>
+      <c r="AS2" t="n">
+        <v>231221</v>
+      </c>
+      <c r="AT2" t="n">
+        <v>1152838</v>
+      </c>
+      <c r="AU2" t="n">
+        <v>595475</v>
+      </c>
+      <c r="AV2" t="n">
+        <v>616001</v>
+      </c>
+      <c r="AW2" t="n">
+        <v>772288</v>
+      </c>
+      <c r="AX2" t="n">
+        <v>566107</v>
+      </c>
+      <c r="AY2" t="n">
+        <v>983932</v>
+      </c>
+      <c r="AZ2" t="n">
+        <v>293162</v>
+      </c>
+      <c r="BA2" t="n">
+        <v>1154459</v>
+      </c>
+      <c r="BB2" t="n">
+        <v>688301</v>
+      </c>
+      <c r="BC2" t="n">
+        <v>430050</v>
+      </c>
+      <c r="BD2" t="n">
+        <v>251939</v>
+      </c>
+      <c r="BE2" t="n">
+        <v>139523</v>
+      </c>
+      <c r="BF2" t="n">
+        <v>1180361</v>
+      </c>
+      <c r="BG2" t="n">
+        <v>1027693</v>
+      </c>
+      <c r="BH2" t="n">
+        <v>146092</v>
+      </c>
+      <c r="BI2" t="n">
+        <v>670364</v>
+      </c>
+      <c r="BJ2" t="n">
+        <v>1094334</v>
+      </c>
+      <c r="BK2" t="n">
+        <v>875155</v>
+      </c>
+      <c r="BL2" t="n">
+        <v>576936</v>
+      </c>
+      <c r="BM2" t="n">
+        <v>1132715</v>
+      </c>
+      <c r="BN2" t="n">
+        <v>237664</v>
+      </c>
+      <c r="BO2" t="n">
+        <v>136461</v>
+      </c>
+      <c r="BP2" t="n">
+        <v>126871</v>
+      </c>
+      <c r="BQ2" t="n">
+        <v>502696</v>
+      </c>
+      <c r="BR2" t="n">
+        <v>1052360</v>
+      </c>
+      <c r="BS2" t="n">
+        <v>59447</v>
+      </c>
+      <c r="BT2" t="n">
+        <v>309637</v>
+      </c>
+      <c r="BU2" t="n">
+        <v>298870</v>
+      </c>
+      <c r="BV2" t="n">
+        <v>222193</v>
+      </c>
+      <c r="BW2" t="n">
+        <v>71238</v>
+      </c>
+      <c r="BX2" t="n">
+        <v>155087</v>
+      </c>
+      <c r="BY2" t="n">
+        <v>333167</v>
+      </c>
+      <c r="BZ2" t="n">
+        <v>799905</v>
+      </c>
+      <c r="CA2" t="n">
+        <v>713447</v>
+      </c>
+      <c r="CB2" t="n">
+        <v>41495</v>
+      </c>
+      <c r="CC2" t="n">
+        <v>520544</v>
+      </c>
+      <c r="CD2" t="n">
+        <v>719125</v>
+      </c>
+      <c r="CE2" t="n">
+        <v>799197</v>
+      </c>
+      <c r="CF2" t="n">
+        <v>1214404</v>
+      </c>
+      <c r="CG2" t="n">
+        <v>630615</v>
+      </c>
+      <c r="CH2" t="n">
+        <v>446496</v>
+      </c>
+      <c r="CI2" t="n">
+        <v>409336</v>
+      </c>
+      <c r="CJ2" t="n">
+        <v>865896</v>
+      </c>
+      <c r="CK2" t="n">
+        <v>1029246</v>
+      </c>
+      <c r="CL2" t="n">
+        <v>288326</v>
+      </c>
+      <c r="CM2" t="n">
+        <v>654401</v>
+      </c>
+      <c r="CN2" t="n">
+        <v>548385</v>
+      </c>
+      <c r="CO2" t="n">
+        <v>365929</v>
+      </c>
+      <c r="CP2" t="n">
+        <v>99443</v>
+      </c>
+      <c r="CQ2" t="n">
+        <v>709159</v>
+      </c>
+      <c r="CR2" t="n">
+        <v>953695</v>
+      </c>
+      <c r="CS2" t="n">
+        <v>410301</v>
+      </c>
+      <c r="CT2" t="n">
+        <v>511984</v>
+      </c>
+      <c r="CU2" t="n">
+        <v>1041152</v>
+      </c>
+      <c r="CV2" t="n">
+        <v>784673</v>
+      </c>
+      <c r="CW2" t="n">
+        <v>901419</v>
+      </c>
+      <c r="CX2" t="n">
+        <v>214415</v>
+      </c>
+      <c r="CY2" t="n">
+        <v>427056</v>
+      </c>
+      <c r="CZ2" t="n">
+        <v>229132</v>
+      </c>
+      <c r="DA2" t="n">
+        <v>813587</v>
+      </c>
+      <c r="DB2" t="n">
+        <v>197441</v>
+      </c>
+      <c r="DC2" t="n">
+        <v>247906</v>
+      </c>
+      <c r="DD2" t="n">
+        <v>351639</v>
+      </c>
+      <c r="DE2" t="n">
+        <v>6780</v>
+      </c>
+      <c r="DF2" t="n">
+        <v>835261</v>
+      </c>
+      <c r="DG2" t="n">
+        <v>948935</v>
+      </c>
+      <c r="DH2" t="n">
+        <v>206205</v>
+      </c>
+      <c r="DI2" t="n">
+        <v>781199</v>
+      </c>
+      <c r="DJ2" t="n">
+        <v>1065463</v>
+      </c>
+      <c r="DK2" t="n">
+        <v>1130543</v>
+      </c>
+      <c r="DL2" t="n">
+        <v>490098</v>
+      </c>
+      <c r="DM2" t="n">
+        <v>541278</v>
+      </c>
+      <c r="DN2" t="n">
+        <v>278941</v>
+      </c>
+      <c r="DO2" t="n">
+        <v>158055</v>
+      </c>
+      <c r="DP2" t="n">
+        <v>1013707</v>
+      </c>
+      <c r="DQ2" t="n">
+        <v>951757</v>
+      </c>
+      <c r="DR2" t="n">
+        <v>724483</v>
+      </c>
+      <c r="DS2" t="n">
+        <v>1169026</v>
+      </c>
+      <c r="DT2" t="n">
+        <v>624277</v>
+      </c>
+      <c r="DU2" t="n">
+        <v>1043775</v>
+      </c>
+      <c r="DV2" t="n">
+        <v>392408</v>
+      </c>
+      <c r="DW2" t="n">
+        <v>791406</v>
+      </c>
+      <c r="DX2" t="n">
+        <v>726613</v>
+      </c>
+      <c r="DY2" t="n">
+        <v>651714</v>
+      </c>
+      <c r="DZ2" t="n">
+        <v>188868</v>
+      </c>
+      <c r="EA2" t="n">
+        <v>672800</v>
+      </c>
+      <c r="EB2" t="n">
+        <v>746885</v>
+      </c>
+      <c r="EC2" t="n">
+        <v>826197</v>
+      </c>
+      <c r="ED2" t="n">
+        <v>599030</v>
+      </c>
+      <c r="EE2" t="n">
+        <v>114372</v>
+      </c>
+      <c r="EF2" t="n">
+        <v>101763</v>
+      </c>
+      <c r="EG2" t="n">
+        <v>706484</v>
+      </c>
+      <c r="EH2" t="n">
+        <v>225427</v>
+      </c>
+      <c r="EI2" t="n">
+        <v>694130</v>
+      </c>
+      <c r="EJ2" t="n">
+        <v>469945</v>
+      </c>
+      <c r="EK2" t="n">
+        <v>158040</v>
+      </c>
+      <c r="EL2" t="n">
+        <v>756189</v>
+      </c>
+      <c r="EM2" t="n">
+        <v>325127</v>
+      </c>
+      <c r="EN2" t="n">
+        <v>897893</v>
+      </c>
+      <c r="EO2" t="n">
+        <v>510035</v>
+      </c>
+      <c r="EP2" t="n">
+        <v>888960</v>
+      </c>
+      <c r="EQ2" t="n">
+        <v>1155892</v>
+      </c>
+      <c r="ER2" t="n">
+        <v>1119645</v>
+      </c>
+      <c r="ES2" t="n">
+        <v>931177</v>
+      </c>
+      <c r="ET2" t="n">
+        <v>61992</v>
+      </c>
+      <c r="EU2" t="n">
+        <v>742629</v>
+      </c>
+      <c r="EV2" t="n">
+        <v>766862</v>
+      </c>
+      <c r="EW2" t="n">
+        <v>380931</v>
+      </c>
+      <c r="EX2" t="n">
+        <v>790690</v>
+      </c>
+      <c r="EY2" t="n">
+        <v>956859</v>
+      </c>
+      <c r="EZ2" t="n">
+        <v>244936</v>
+      </c>
+      <c r="FA2" t="n">
+        <v>1132132</v>
+      </c>
+      <c r="FB2" t="n">
+        <v>1210068</v>
+      </c>
+      <c r="FC2" t="n">
+        <v>997217</v>
+      </c>
+      <c r="FD2" t="n">
+        <v>1009289</v>
+      </c>
+      <c r="FE2" t="n">
+        <v>354399</v>
+      </c>
+      <c r="FF2" t="n">
+        <v>61936</v>
+      </c>
+      <c r="FG2" t="n">
+        <v>308144</v>
+      </c>
+      <c r="FH2" t="n">
+        <v>1171788</v>
+      </c>
+      <c r="FI2" t="n">
+        <v>198428</v>
+      </c>
+      <c r="FJ2" t="n">
+        <v>180777</v>
+      </c>
+      <c r="FK2" t="n">
+        <v>131307</v>
+      </c>
+      <c r="FL2" t="n">
+        <v>453247</v>
+      </c>
+      <c r="FM2" t="n">
+        <v>1002140</v>
+      </c>
+      <c r="FN2" t="n">
+        <v>105590</v>
+      </c>
+      <c r="FO2" t="n">
+        <v>1085736</v>
+      </c>
+      <c r="FP2" t="n">
+        <v>126322</v>
+      </c>
+      <c r="FQ2" t="n">
+        <v>481806</v>
+      </c>
+      <c r="FR2" t="n">
+        <v>45071</v>
+      </c>
+      <c r="FS2" t="n">
+        <v>19647</v>
+      </c>
+      <c r="FT2" t="n">
+        <v>959499</v>
+      </c>
+      <c r="FU2" t="n">
+        <v>773412</v>
+      </c>
+      <c r="FV2" t="n">
+        <v>46879</v>
+      </c>
+      <c r="FW2" t="n">
+        <v>151924</v>
+      </c>
+      <c r="FX2" t="n">
+        <v>546401</v>
+      </c>
+      <c r="FY2" t="n">
+        <v>593004</v>
+      </c>
+      <c r="FZ2" t="n">
+        <v>1213589</v>
+      </c>
+      <c r="GA2" t="n">
+        <v>365845</v>
+      </c>
+      <c r="GB2" t="n">
+        <v>539013</v>
+      </c>
+      <c r="GC2" t="n">
+        <v>535565</v>
+      </c>
+      <c r="GD2" t="n">
+        <v>617101</v>
+      </c>
+      <c r="GE2" t="n">
+        <v>302821</v>
+      </c>
+      <c r="GF2" t="n">
+        <v>561405</v>
+      </c>
+      <c r="GG2" t="n">
+        <v>838387</v>
+      </c>
+      <c r="GH2" t="n">
+        <v>847013</v>
+      </c>
+      <c r="GI2" t="n">
+        <v>507434</v>
+      </c>
+      <c r="GJ2" t="n">
+        <v>864849</v>
+      </c>
+      <c r="GK2" t="n">
+        <v>1117214</v>
+      </c>
+      <c r="GL2" t="n">
+        <v>1193058</v>
+      </c>
+      <c r="GM2" t="n">
+        <v>830422</v>
+      </c>
+      <c r="GN2" t="n">
+        <v>1216256</v>
+      </c>
+      <c r="GO2" t="n">
+        <v>912868</v>
+      </c>
+      <c r="GP2" t="n">
+        <v>1105348</v>
+      </c>
+      <c r="GQ2" t="n">
+        <v>48815</v>
+      </c>
+      <c r="GR2" t="n">
+        <v>125982</v>
+      </c>
+      <c r="GS2" t="n">
+        <v>448829</v>
+      </c>
+      <c r="GT2" t="n">
+        <v>80391</v>
+      </c>
+      <c r="GU2" t="n">
+        <v>505622</v>
+      </c>
+      <c r="GV2" t="n">
+        <v>638734</v>
+      </c>
+      <c r="GW2" t="n">
+        <v>881663</v>
+      </c>
+      <c r="GX2" t="n">
+        <v>115842</v>
+      </c>
+      <c r="GY2" t="n">
+        <v>570627</v>
+      </c>
+      <c r="GZ2" t="n">
+        <v>740824</v>
+      </c>
+      <c r="HA2" t="n">
+        <v>488931</v>
+      </c>
+      <c r="HB2" t="n">
+        <v>881342</v>
+      </c>
+      <c r="HC2" t="n">
+        <v>861742</v>
+      </c>
+      <c r="HD2" t="n">
+        <v>1147582</v>
+      </c>
+      <c r="HE2" t="n">
+        <v>193765</v>
+      </c>
+      <c r="HF2" t="n">
+        <v>268918</v>
+      </c>
+      <c r="HG2" t="n">
+        <v>308293</v>
+      </c>
+      <c r="HH2" t="n">
+        <v>507973</v>
+      </c>
+      <c r="HI2" t="n">
+        <v>458828</v>
+      </c>
+      <c r="HJ2" t="n">
+        <v>1055302</v>
+      </c>
+      <c r="HK2" t="n">
+        <v>995798</v>
+      </c>
+      <c r="HL2" t="n">
+        <v>561665</v>
+      </c>
+      <c r="HM2" t="n">
+        <v>215068</v>
+      </c>
+      <c r="HN2" t="n">
+        <v>517193</v>
+      </c>
+      <c r="HO2" t="n">
+        <v>257923</v>
+      </c>
+      <c r="HP2" t="n">
+        <v>967836</v>
+      </c>
+      <c r="HQ2" t="n">
+        <v>209679</v>
+      </c>
+      <c r="HR2" t="n">
+        <v>1088983</v>
+      </c>
+      <c r="HS2" t="n">
+        <v>264414</v>
+      </c>
+      <c r="HT2" t="n">
+        <v>394256</v>
+      </c>
+      <c r="HU2" t="n">
+        <v>1183999</v>
+      </c>
+      <c r="HV2" t="n">
+        <v>821940</v>
+      </c>
+      <c r="HW2" t="n">
+        <v>714906</v>
+      </c>
+      <c r="HX2" t="n">
+        <v>369698</v>
+      </c>
+      <c r="HY2" t="n">
+        <v>374570</v>
+      </c>
+      <c r="HZ2" t="n">
+        <v>662464</v>
+      </c>
+      <c r="IA2" t="n">
+        <v>606363</v>
+      </c>
+      <c r="IB2" t="n">
+        <v>525975</v>
+      </c>
+      <c r="IC2" t="n">
+        <v>765749</v>
+      </c>
+      <c r="ID2" t="n">
+        <v>69397</v>
+      </c>
+      <c r="IE2" t="n">
+        <v>511838</v>
+      </c>
+      <c r="IF2" t="n">
+        <v>3824</v>
+      </c>
+      <c r="IG2" t="n">
+        <v>234097</v>
+      </c>
+      <c r="IH2" t="n">
+        <v>655663</v>
+      </c>
+      <c r="II2" t="n">
+        <v>517368</v>
+      </c>
+      <c r="IJ2" t="n">
+        <v>468323</v>
+      </c>
+      <c r="IK2" t="n">
+        <v>537368</v>
+      </c>
+      <c r="IL2" t="n">
+        <v>594689</v>
+      </c>
+      <c r="IM2" t="n">
+        <v>305167</v>
+      </c>
+      <c r="IN2" t="n">
+        <v>404711</v>
+      </c>
+      <c r="IO2" t="n">
+        <v>23840</v>
+      </c>
+      <c r="IP2" t="n">
+        <v>1013920</v>
+      </c>
+      <c r="IQ2" t="n">
+        <v>370957</v>
+      </c>
+      <c r="IR2" t="n">
+        <v>220404</v>
+      </c>
+      <c r="IS2" t="n">
+        <v>470309</v>
+      </c>
+      <c r="IT2" t="n">
+        <v>752482</v>
+      </c>
+      <c r="IU2" t="n">
+        <v>662313</v>
+      </c>
+      <c r="IV2" t="n">
+        <v>217152</v>
+      </c>
+      <c r="IW2" t="n">
+        <v>284466</v>
+      </c>
+      <c r="IX2" t="n">
+        <v>257435</v>
+      </c>
+      <c r="IY2" t="n">
+        <v>840478</v>
+      </c>
+      <c r="IZ2" t="n">
+        <v>357087</v>
+      </c>
+      <c r="JA2" t="n">
+        <v>878953</v>
+      </c>
+      <c r="JB2" t="n">
+        <v>994451</v>
+      </c>
+      <c r="JC2" t="n">
+        <v>121427</v>
+      </c>
+      <c r="JD2" t="n">
+        <v>819865</v>
+      </c>
+      <c r="JE2" t="n">
+        <v>735133</v>
+      </c>
+      <c r="JF2" t="n">
+        <v>20993</v>
+      </c>
+      <c r="JG2" t="n">
+        <v>476951</v>
+      </c>
+      <c r="JH2" t="n">
+        <v>1171499</v>
+      </c>
+      <c r="JI2" t="n">
+        <v>202287</v>
+      </c>
+      <c r="JJ2" t="n">
+        <v>317827</v>
+      </c>
+      <c r="JK2" t="n">
+        <v>1108361</v>
+      </c>
+      <c r="JL2" t="n">
+        <v>773377</v>
+      </c>
+      <c r="JM2" t="n">
+        <v>627850</v>
+      </c>
+      <c r="JN2" t="n">
+        <v>590567</v>
+      </c>
+      <c r="JO2" t="n">
+        <v>423857</v>
+      </c>
+      <c r="JP2" t="n">
+        <v>431808</v>
+      </c>
+      <c r="JQ2" t="n">
+        <v>96353</v>
+      </c>
+      <c r="JR2" t="n">
+        <v>220361</v>
+      </c>
+      <c r="JS2" t="n">
+        <v>194908</v>
+      </c>
+      <c r="JT2" t="n">
+        <v>490205</v>
+      </c>
+      <c r="JU2" t="n">
+        <v>1182843</v>
+      </c>
+      <c r="JV2" t="n">
+        <v>626942</v>
+      </c>
+      <c r="JW2" t="n">
+        <v>749689</v>
+      </c>
+      <c r="JX2" t="n">
+        <v>1136237</v>
+      </c>
+      <c r="JY2" t="n">
+        <v>805043</v>
+      </c>
+      <c r="JZ2" t="n">
+        <v>1115257</v>
+      </c>
+      <c r="KA2" t="n">
+        <v>312115</v>
+      </c>
+      <c r="KB2" t="n">
+        <v>263457</v>
+      </c>
+      <c r="KC2" t="n">
+        <v>438256</v>
+      </c>
+      <c r="KD2" t="n">
+        <v>1188257</v>
+      </c>
+      <c r="KE2" t="n">
+        <v>1190899</v>
+      </c>
+      <c r="KF2" t="n">
+        <v>485109</v>
+      </c>
+      <c r="KG2" t="n">
+        <v>633698</v>
+      </c>
+      <c r="KH2" t="n">
+        <v>104148</v>
+      </c>
+      <c r="KI2" t="n">
+        <v>891016</v>
+      </c>
+      <c r="KJ2" t="n">
+        <v>895629</v>
+      </c>
+      <c r="KK2" t="n">
+        <v>827116</v>
+      </c>
+      <c r="KL2" t="n">
+        <v>523777</v>
+      </c>
+      <c r="KM2" t="n">
+        <v>1102061</v>
+      </c>
+      <c r="KN2" t="n">
+        <v>586607</v>
+      </c>
+      <c r="KO2" t="n">
+        <v>588900</v>
+      </c>
+      <c r="KP2" t="n">
+        <v>565209</v>
+      </c>
+      <c r="KQ2" t="n">
+        <v>14719</v>
+      </c>
+      <c r="KR2" t="n">
+        <v>87437</v>
+      </c>
+      <c r="KS2" t="n">
+        <v>583494</v>
+      </c>
+      <c r="KT2" t="n">
+        <v>911260</v>
+      </c>
+      <c r="KU2" t="n">
+        <v>929491</v>
+      </c>
+      <c r="KV2" t="n">
+        <v>1005094</v>
+      </c>
+      <c r="KW2" t="n">
+        <v>1078408</v>
+      </c>
+      <c r="KX2" t="n">
+        <v>486450</v>
+      </c>
+      <c r="KY2" t="n">
+        <v>663052</v>
+      </c>
+      <c r="KZ2" t="n">
+        <v>1057639</v>
+      </c>
+      <c r="LA2" t="n">
+        <v>176555</v>
+      </c>
+      <c r="LB2" t="n">
+        <v>295007</v>
+      </c>
+      <c r="LC2" t="n">
+        <v>152693</v>
+      </c>
+      <c r="LD2" t="n">
+        <v>623134</v>
+      </c>
+      <c r="LE2" t="n">
+        <v>967306</v>
+      </c>
+      <c r="LF2" t="n">
+        <v>853819</v>
+      </c>
+      <c r="LG2" t="n">
+        <v>173705</v>
+      </c>
+      <c r="LH2" t="n">
+        <v>1126492</v>
+      </c>
+      <c r="LI2" t="n">
+        <v>744720</v>
+      </c>
+      <c r="LJ2" t="n">
+        <v>241484</v>
+      </c>
+      <c r="LK2" t="n">
+        <v>399213</v>
+      </c>
+      <c r="LL2" t="n">
+        <v>782490</v>
+      </c>
+      <c r="LM2" t="n">
+        <v>389890</v>
+      </c>
+      <c r="LN2" t="n">
+        <v>1143494</v>
+      </c>
+      <c r="LO2" t="n">
+        <v>383243</v>
+      </c>
+      <c r="LP2" t="n">
+        <v>53757</v>
+      </c>
+      <c r="LQ2" t="n">
+        <v>1031614</v>
+      </c>
+      <c r="LR2" t="n">
+        <v>531490</v>
+      </c>
+      <c r="LS2" t="n">
+        <v>403788</v>
+      </c>
+      <c r="LT2" t="n">
+        <v>18104</v>
+      </c>
+      <c r="LU2" t="n">
+        <v>900582</v>
+      </c>
+      <c r="LV2" t="n">
+        <v>711039</v>
+      </c>
+      <c r="LW2" t="n">
+        <v>298596</v>
+      </c>
+      <c r="LX2" t="n">
+        <v>926861</v>
+      </c>
+      <c r="LY2" t="n">
+        <v>819865</v>
+      </c>
+      <c r="LZ2" t="n">
+        <v>838741</v>
+      </c>
+      <c r="MA2" t="n">
+        <v>1113744</v>
+      </c>
+      <c r="MB2" t="n">
+        <v>1083316</v>
+      </c>
+      <c r="MC2" t="n">
+        <v>1188082</v>
+      </c>
+      <c r="MD2" t="n">
+        <v>39346</v>
+      </c>
+      <c r="ME2" t="n">
+        <v>961070</v>
+      </c>
+      <c r="MF2" t="n">
+        <v>279388</v>
+      </c>
+      <c r="MG2" t="n">
+        <v>377844</v>
+      </c>
+      <c r="MH2" t="n">
+        <v>894405</v>
+      </c>
+      <c r="MI2" t="n">
+        <v>987593</v>
+      </c>
+      <c r="MJ2" t="n">
+        <v>721737</v>
+      </c>
+      <c r="MK2" t="n">
+        <v>843961</v>
+      </c>
+      <c r="ML2" t="n">
+        <v>579655</v>
+      </c>
+      <c r="MM2" t="n">
+        <v>20591</v>
+      </c>
+      <c r="MN2" t="n">
+        <v>189686</v>
+      </c>
+      <c r="MO2" t="n">
+        <v>99717</v>
+      </c>
+      <c r="MP2" t="n">
+        <v>52090</v>
+      </c>
+      <c r="MQ2" t="n">
+        <v>377355</v>
+      </c>
+      <c r="MR2" t="n">
+        <v>573830</v>
+      </c>
+      <c r="MS2" t="n">
+        <v>1088728</v>
+      </c>
+      <c r="MT2" t="n">
+        <v>95840</v>
+      </c>
+      <c r="MU2" t="n">
+        <v>395884</v>
+      </c>
+      <c r="MV2" t="n">
+        <v>1007722</v>
+      </c>
+      <c r="MW2" t="n">
+        <v>74997</v>
+      </c>
+      <c r="MX2" t="n">
+        <v>261643</v>
+      </c>
+      <c r="MY2" t="n">
+        <v>5213</v>
+      </c>
+      <c r="MZ2" t="n">
+        <v>271172</v>
+      </c>
+      <c r="NA2" t="n">
+        <v>851902</v>
+      </c>
+      <c r="NB2" t="n">
+        <v>601134</v>
+      </c>
+      <c r="NC2" t="n">
+        <v>295951</v>
+      </c>
+      <c r="ND2" t="n">
+        <v>937010</v>
+      </c>
+      <c r="NE2" t="n">
+        <v>1166439</v>
+      </c>
+      <c r="NF2" t="n">
+        <v>339631</v>
+      </c>
+      <c r="NG2" t="n">
+        <v>983747</v>
+      </c>
+      <c r="NH2" t="n">
+        <v>435616</v>
+      </c>
+      <c r="NI2" t="n">
+        <v>650415</v>
+      </c>
+      <c r="NJ2" t="n">
+        <v>570157</v>
+      </c>
+      <c r="NK2" t="n">
+        <v>1098459</v>
+      </c>
+      <c r="NL2" t="n">
+        <v>334310</v>
+      </c>
+      <c r="NM2" t="n">
+        <v>1047485</v>
+      </c>
+      <c r="NN2" t="n">
+        <v>636404</v>
+      </c>
+      <c r="NO2" t="n">
+        <v>345084</v>
+      </c>
+      <c r="NP2" t="n">
+        <v>90323</v>
+      </c>
+      <c r="NQ2" t="n">
+        <v>1069484</v>
+      </c>
+      <c r="NR2" t="n">
+        <v>988046</v>
+      </c>
+      <c r="NS2" t="n">
+        <v>1037574</v>
+      </c>
+      <c r="NT2" t="n">
+        <v>876175</v>
+      </c>
+      <c r="NU2" t="n">
+        <v>61599</v>
+      </c>
+      <c r="NV2" t="n">
+        <v>346958</v>
+      </c>
+      <c r="NW2" t="n">
+        <v>26601</v>
+      </c>
+      <c r="NX2" t="n">
+        <v>9015</v>
+      </c>
+      <c r="NY2" t="n">
+        <v>36847</v>
+      </c>
+      <c r="NZ2" t="n">
+        <v>1071172</v>
+      </c>
+      <c r="OA2" t="n">
+        <v>360124</v>
+      </c>
+      <c r="OB2" t="n">
+        <v>129775</v>
+      </c>
+      <c r="OC2" t="n">
+        <v>99698</v>
+      </c>
+      <c r="OD2" t="n">
+        <v>841154</v>
+      </c>
+      <c r="OE2" t="n">
+        <v>1017544</v>
+      </c>
+      <c r="OF2" t="n">
+        <v>74535</v>
+      </c>
+      <c r="OG2" t="n">
+        <v>133939</v>
+      </c>
+      <c r="OH2" t="n">
+        <v>168870</v>
+      </c>
+      <c r="OI2" t="n">
+        <v>116978</v>
+      </c>
+      <c r="OJ2" t="n">
+        <v>81399</v>
+      </c>
+      <c r="OK2" t="n">
+        <v>583839</v>
+      </c>
+      <c r="OL2" t="n">
+        <v>499247</v>
+      </c>
+      <c r="OM2" t="n">
+        <v>633741</v>
+      </c>
+      <c r="ON2" t="n">
+        <v>646451</v>
+      </c>
+      <c r="OO2" t="n">
+        <v>911082</v>
+      </c>
+      <c r="OP2" t="n">
+        <v>267847</v>
+      </c>
+      <c r="OQ2" t="n">
+        <v>1165490</v>
+      </c>
+      <c r="OR2" t="n">
+        <v>644654</v>
+      </c>
+      <c r="OS2" t="n">
+        <v>642103</v>
+      </c>
+      <c r="OT2" t="n">
+        <v>402714</v>
+      </c>
+      <c r="OU2" t="n">
+        <v>1019825</v>
+      </c>
+      <c r="OV2" t="n">
+        <v>1073439</v>
+      </c>
+      <c r="OW2" t="n">
+        <v>1009839</v>
+      </c>
+      <c r="OX2" t="n">
+        <v>667545</v>
+      </c>
+      <c r="OY2" t="n">
+        <v>1166774</v>
+      </c>
+      <c r="OZ2" t="n">
+        <v>148283</v>
+      </c>
+      <c r="PA2" t="n">
+        <v>1025858</v>
+      </c>
+      <c r="PB2" t="n">
+        <v>567133</v>
+      </c>
+      <c r="PC2" t="n">
+        <v>507759</v>
+      </c>
+      <c r="PD2" t="n">
+        <v>1119650</v>
+      </c>
+      <c r="PE2" t="n">
+        <v>248043</v>
+      </c>
+      <c r="PF2" t="n">
+        <v>41765</v>
+      </c>
+      <c r="PG2" t="n">
+        <v>1148065</v>
+      </c>
+      <c r="PH2" t="n">
+        <v>1100947</v>
+      </c>
+      <c r="PI2" t="n">
+        <v>1204687</v>
+      </c>
+      <c r="PJ2" t="n">
+        <v>825899</v>
+      </c>
+      <c r="PK2" t="n">
+        <v>771438</v>
+      </c>
+      <c r="PL2" t="n">
+        <v>1002724</v>
+      </c>
+      <c r="PM2" t="n">
+        <v>424864</v>
+      </c>
+      <c r="PN2" t="n">
+        <v>35686</v>
+      </c>
+      <c r="PO2" t="n">
+        <v>776323</v>
+      </c>
+      <c r="PP2" t="n">
+        <v>604630</v>
+      </c>
+      <c r="PQ2" t="n">
+        <v>1054884</v>
+      </c>
+      <c r="PR2" t="n">
+        <v>439795</v>
+      </c>
+      <c r="PS2" t="n">
+        <v>977747</v>
+      </c>
+      <c r="PT2" t="n">
+        <v>1111637</v>
+      </c>
+      <c r="PU2" t="n">
+        <v>581084</v>
+      </c>
+      <c r="PV2" t="n">
+        <v>28059</v>
+      </c>
+      <c r="PW2" t="n">
+        <v>29236</v>
+      </c>
+      <c r="PX2" t="n">
+        <v>201848</v>
+      </c>
+      <c r="PY2" t="n">
+        <v>186955</v>
+      </c>
+      <c r="PZ2" t="n">
+        <v>336148</v>
+      </c>
+      <c r="QA2" t="n">
+        <v>806629</v>
+      </c>
+      <c r="QB2" t="n">
+        <v>1126554</v>
+      </c>
+      <c r="QC2" t="n">
+        <v>629243</v>
+      </c>
+      <c r="QD2" t="n">
+        <v>122945</v>
+      </c>
+      <c r="QE2" t="n">
+        <v>555430</v>
+      </c>
+      <c r="QF2" t="n">
+        <v>729818</v>
+      </c>
+      <c r="QG2" t="n">
+        <v>128828</v>
+      </c>
+      <c r="QH2" t="n">
+        <v>312001</v>
+      </c>
+      <c r="QI2" t="n">
+        <v>434064</v>
+      </c>
+      <c r="QJ2" t="n">
+        <v>146271</v>
+      </c>
+      <c r="QK2" t="n">
+        <v>351053</v>
+      </c>
+      <c r="QL2" t="n">
+        <v>657909</v>
+      </c>
+      <c r="QM2" t="n">
+        <v>500594</v>
+      </c>
+      <c r="QN2" t="n">
+        <v>935570</v>
+      </c>
+      <c r="QO2" t="n">
+        <v>1067727</v>
+      </c>
+      <c r="QP2" t="n">
+        <v>196315</v>
+      </c>
+      <c r="QQ2" t="n">
+        <v>989847</v>
+      </c>
+      <c r="QR2" t="n">
+        <v>1113571</v>
+      </c>
+      <c r="QS2" t="n">
+        <v>458091</v>
+      </c>
+      <c r="QT2" t="n">
+        <v>928996</v>
+      </c>
+      <c r="QU2" t="n">
+        <v>496227</v>
+      </c>
+      <c r="QV2" t="n">
+        <v>867839</v>
+      </c>
+      <c r="QW2" t="n">
+        <v>166670</v>
+      </c>
+      <c r="QX2" t="n">
+        <v>1016647</v>
+      </c>
+      <c r="QY2" t="n">
+        <v>917988</v>
+      </c>
+      <c r="QZ2" t="n">
+        <v>400884</v>
+      </c>
+      <c r="RA2" t="n">
+        <v>1106618</v>
+      </c>
+      <c r="RB2" t="n">
+        <v>169911</v>
+      </c>
+      <c r="RC2" t="n">
+        <v>14339</v>
+      </c>
+      <c r="RD2" t="n">
+        <v>973356</v>
+      </c>
+      <c r="RE2" t="n">
+        <v>90282</v>
+      </c>
+      <c r="RF2" t="n">
+        <v>523302</v>
+      </c>
+      <c r="RG2" t="n">
+        <v>1158531</v>
+      </c>
+      <c r="RH2" t="n">
+        <v>256504</v>
+      </c>
+      <c r="RI2" t="n">
+        <v>995518</v>
+      </c>
+      <c r="RJ2" t="n">
+        <v>999583</v>
+      </c>
+      <c r="RK2" t="n">
+        <v>216307</v>
+      </c>
+      <c r="RL2" t="n">
+        <v>360049</v>
+      </c>
+      <c r="RM2" t="n">
+        <v>185370</v>
+      </c>
+      <c r="RN2" t="n">
+        <v>271302</v>
+      </c>
+      <c r="RO2" t="n">
+        <v>1023703</v>
+      </c>
+      <c r="RP2" t="n">
+        <v>690251</v>
+      </c>
+      <c r="RQ2" t="n">
+        <v>513769</v>
+      </c>
+      <c r="RR2" t="n">
+        <v>931412</v>
+      </c>
+      <c r="RS2" t="n">
+        <v>290790</v>
+      </c>
+      <c r="RT2" t="n">
+        <v>10636</v>
+      </c>
+      <c r="RU2" t="n">
+        <v>228740</v>
+      </c>
+      <c r="RV2" t="n">
+        <v>625070</v>
+      </c>
+      <c r="RW2" t="n">
+        <v>36225</v>
+      </c>
+      <c r="RX2" t="n">
+        <v>1183887</v>
+      </c>
+      <c r="RY2" t="n">
+        <v>848862</v>
+      </c>
+      <c r="RZ2" t="n">
+        <v>203027</v>
+      </c>
+      <c r="SA2" t="n">
+        <v>1151037</v>
+      </c>
+      <c r="SB2" t="n">
+        <v>642283</v>
+      </c>
+      <c r="SC2" t="n">
+        <v>146918</v>
+      </c>
+      <c r="SD2" t="n">
+        <v>556508</v>
+      </c>
+      <c r="SE2" t="n">
+        <v>777725</v>
+      </c>
+      <c r="SF2" t="n">
+        <v>170617</v>
+      </c>
+      <c r="SG2" t="n">
+        <v>478722</v>
+      </c>
+      <c r="SH2" t="n">
+        <v>736758</v>
+      </c>
+      <c r="SI2" t="n">
+        <v>14168</v>
+      </c>
+      <c r="SJ2" t="n">
+        <v>205258</v>
+      </c>
+      <c r="SK2" t="n">
+        <v>481438</v>
+      </c>
+      <c r="SL2" t="n">
+        <v>890202</v>
+      </c>
+      <c r="SM2" t="n">
+        <v>921691</v>
+      </c>
+      <c r="SN2" t="n">
+        <v>940346</v>
+      </c>
+      <c r="SO2" t="n">
+        <v>1061722</v>
+      </c>
+      <c r="SP2" t="n">
+        <v>993599</v>
+      </c>
+      <c r="SQ2" t="n">
+        <v>632028</v>
+      </c>
+      <c r="SR2" t="n">
+        <v>315308</v>
+      </c>
+      <c r="SS2" t="n">
+        <v>707371</v>
+      </c>
+      <c r="ST2" t="n">
+        <v>443065</v>
+      </c>
+      <c r="SU2" t="n">
+        <v>755412</v>
+      </c>
+      <c r="SV2" t="n">
+        <v>417965</v>
+      </c>
+      <c r="SW2" t="n">
+        <v>1133494</v>
+      </c>
+      <c r="SX2" t="n">
+        <v>1068316</v>
+      </c>
+      <c r="SY2" t="n">
+        <v>684310</v>
+      </c>
+      <c r="SZ2" t="n">
+        <v>587641</v>
+      </c>
+      <c r="TA2" t="n">
+        <v>1207408</v>
+      </c>
+      <c r="TB2" t="n">
+        <v>167156</v>
+      </c>
+      <c r="TC2" t="n">
+        <v>344009</v>
+      </c>
+      <c r="TD2" t="n">
+        <v>67412</v>
+      </c>
+      <c r="TE2" t="n">
+        <v>426785</v>
+      </c>
+      <c r="TF2" t="n">
+        <v>140062</v>
+      </c>
+      <c r="TG2" t="n">
+        <v>586597</v>
+      </c>
+      <c r="TH2" t="n">
+        <v>808254</v>
+      </c>
+      <c r="TI2" t="n">
+        <v>413961</v>
+      </c>
+      <c r="TJ2" t="n">
+        <v>274588</v>
+      </c>
+      <c r="TK2" t="n">
+        <v>110566</v>
+      </c>
+      <c r="TL2" t="n">
+        <v>104863</v>
+      </c>
+      <c r="TM2" t="n">
+        <v>77524</v>
+      </c>
+      <c r="TN2" t="n">
+        <v>9198</v>
+      </c>
+      <c r="TO2" t="n">
+        <v>362204</v>
+      </c>
+      <c r="TP2" t="n">
+        <v>494978</v>
+      </c>
+      <c r="TQ2" t="n">
+        <v>619906</v>
+      </c>
+      <c r="TR2" t="n">
+        <v>7921</v>
+      </c>
+      <c r="TS2" t="n">
+        <v>243788</v>
+      </c>
+      <c r="TT2" t="n">
+        <v>807538</v>
+      </c>
+      <c r="TU2" t="n">
+        <v>486423</v>
+      </c>
+      <c r="TV2" t="n">
+        <v>1011153</v>
+      </c>
+      <c r="TW2" t="n">
+        <v>35290</v>
+      </c>
+      <c r="TX2" t="n">
+        <v>1049434</v>
+      </c>
+      <c r="TY2" t="n">
+        <v>285430</v>
+      </c>
+      <c r="TZ2" t="n">
+        <v>45873</v>
+      </c>
+      <c r="UA2" t="n">
+        <v>291259</v>
+      </c>
+      <c r="UB2" t="n">
+        <v>56888</v>
+      </c>
+      <c r="UC2" t="n">
+        <v>1156509</v>
+      </c>
+      <c r="UD2" t="n">
+        <v>121679</v>
+      </c>
+      <c r="UE2" t="n">
+        <v>860155</v>
+      </c>
+      <c r="UF2" t="n">
+        <v>935770</v>
+      </c>
+      <c r="UG2" t="n">
+        <v>608018</v>
+      </c>
+      <c r="UH2" t="n">
+        <v>610161</v>
+      </c>
+      <c r="UI2" t="n">
+        <v>441782</v>
+      </c>
+      <c r="UJ2" t="n">
+        <v>832832</v>
+      </c>
+      <c r="UK2" t="n">
+        <v>527984</v>
+      </c>
+      <c r="UL2" t="n">
+        <v>848505</v>
+      </c>
+      <c r="UM2" t="n">
+        <v>532853</v>
+      </c>
+      <c r="UN2" t="n">
+        <v>686947</v>
+      </c>
+      <c r="UO2" t="n">
+        <v>363125</v>
+      </c>
+      <c r="UP2" t="n">
+        <v>560056</v>
+      </c>
+      <c r="UQ2" t="n">
+        <v>665844</v>
+      </c>
+      <c r="UR2" t="n">
+        <v>1076886</v>
+      </c>
+      <c r="US2" t="n">
+        <v>23096</v>
+      </c>
+      <c r="UT2" t="n">
+        <v>722300</v>
+      </c>
+      <c r="UU2" t="n">
+        <v>961964</v>
+      </c>
+      <c r="UV2" t="n">
+        <v>1201784</v>
+      </c>
+      <c r="UW2" t="n">
+        <v>467110</v>
+      </c>
+      <c r="UX2" t="n">
+        <v>520041</v>
+      </c>
+      <c r="UY2" t="n">
+        <v>878698</v>
+      </c>
+      <c r="UZ2" t="n">
+        <v>211170</v>
+      </c>
+      <c r="VA2" t="n">
+        <v>767210</v>
+      </c>
+      <c r="VB2" t="n">
+        <v>132791</v>
+      </c>
+      <c r="VC2" t="n">
+        <v>408157</v>
+      </c>
+      <c r="VD2" t="n">
+        <v>331703</v>
+      </c>
+      <c r="VE2" t="n">
+        <v>887897</v>
+      </c>
+      <c r="VF2" t="n">
+        <v>270077</v>
+      </c>
+      <c r="VG2" t="n">
+        <v>530700</v>
+      </c>
+      <c r="VH2" t="n">
+        <v>473542</v>
+      </c>
+      <c r="VI2" t="n">
+        <v>410286</v>
+      </c>
+      <c r="VJ2" t="n">
+        <v>462632</v>
+      </c>
+      <c r="VK2" t="n">
+        <v>520171</v>
+      </c>
+      <c r="VL2" t="n">
+        <v>474570</v>
+      </c>
+      <c r="VM2" t="n">
+        <v>813695</v>
+      </c>
+      <c r="VN2" t="n">
+        <v>976164</v>
+      </c>
+      <c r="VO2" t="n">
+        <v>298233</v>
+      </c>
+      <c r="VP2" t="n">
+        <v>1021066</v>
+      </c>
+      <c r="VQ2" t="n">
+        <v>551808</v>
+      </c>
+      <c r="VR2" t="n">
+        <v>1065632</v>
+      </c>
+      <c r="VS2" t="n">
+        <v>509791</v>
+      </c>
+      <c r="VT2" t="n">
+        <v>700997</v>
+      </c>
+      <c r="VU2" t="n">
+        <v>647832</v>
+      </c>
+      <c r="VV2" t="n">
+        <v>621890</v>
+      </c>
+      <c r="VW2" t="n">
+        <v>1179767</v>
+      </c>
+      <c r="VX2" t="n">
+        <v>873735</v>
+      </c>
+      <c r="VY2" t="n">
+        <v>1108778</v>
+      </c>
+      <c r="VZ2" t="n">
+        <v>328237</v>
+      </c>
+      <c r="WA2" t="n">
+        <v>655251</v>
+      </c>
+      <c r="WB2" t="n">
+        <v>349955</v>
+      </c>
+      <c r="WC2" t="n">
+        <v>457546</v>
+      </c>
+      <c r="WD2" t="n">
+        <v>649037</v>
+      </c>
+      <c r="WE2" t="n">
+        <v>744593</v>
+      </c>
+      <c r="WF2" t="n">
+        <v>527502</v>
+      </c>
+      <c r="WG2" t="n">
+        <v>112194</v>
+      </c>
+      <c r="WH2" t="n">
+        <v>314591</v>
+      </c>
+      <c r="WI2" t="n">
+        <v>500577</v>
+      </c>
+      <c r="WJ2" t="n">
+        <v>1045208</v>
+      </c>
+      <c r="WK2" t="n">
+        <v>762888</v>
+      </c>
+      <c r="WL2" t="n">
+        <v>198888</v>
+      </c>
+      <c r="WM2" t="n">
+        <v>225446</v>
+      </c>
+      <c r="WN2" t="n">
+        <v>1043515</v>
+      </c>
+      <c r="WO2" t="n">
+        <v>558881</v>
+      </c>
+      <c r="WP2" t="n">
+        <v>1287</v>
+      </c>
+      <c r="WQ2" t="n">
+        <v>345930</v>
+      </c>
+      <c r="WR2" t="n">
+        <v>1058586</v>
+      </c>
+      <c r="WS2" t="n">
+        <v>233175</v>
+      </c>
+      <c r="WT2" t="n">
+        <v>255041</v>
+      </c>
+      <c r="WU2" t="n">
+        <v>477250</v>
+      </c>
+      <c r="WV2" t="n">
+        <v>338978</v>
+      </c>
+      <c r="WW2" t="n">
+        <v>81291</v>
+      </c>
+      <c r="WX2" t="n">
+        <v>566227</v>
+      </c>
+      <c r="WY2" t="n">
+        <v>87038</v>
+      </c>
+      <c r="WZ2" t="n">
+        <v>820466</v>
+      </c>
+      <c r="XA2" t="n">
+        <v>170751</v>
+      </c>
+      <c r="XB2" t="n">
+        <v>433928</v>
+      </c>
+      <c r="XC2" t="n">
+        <v>980535</v>
+      </c>
+      <c r="XD2" t="n">
+        <v>382287</v>
+      </c>
+      <c r="XE2" t="n">
+        <v>1094811</v>
+      </c>
+      <c r="XF2" t="n">
+        <v>57271</v>
+      </c>
+      <c r="XG2" t="n">
+        <v>251102</v>
+      </c>
+      <c r="XH2" t="n">
+        <v>289288</v>
+      </c>
+      <c r="XI2" t="n">
+        <v>352713</v>
+      </c>
+      <c r="XJ2" t="n">
+        <v>815742</v>
+      </c>
+      <c r="XK2" t="n">
+        <v>572914</v>
+      </c>
+      <c r="XL2" t="n">
+        <v>1032310</v>
+      </c>
+      <c r="XM2" t="n">
+        <v>49732</v>
+      </c>
+      <c r="XN2" t="n">
+        <v>82198</v>
+      </c>
+      <c r="XO2" t="n">
+        <v>59494</v>
+      </c>
+      <c r="XP2" t="n">
+        <v>597950</v>
+      </c>
+      <c r="XQ2" t="n">
+        <v>389587</v>
+      </c>
+      <c r="XR2" t="n">
+        <v>609491</v>
+      </c>
+      <c r="XS2" t="n">
+        <v>1033301</v>
+      </c>
+      <c r="XT2" t="n">
+        <v>754986</v>
+      </c>
+      <c r="XU2" t="n">
+        <v>1007367</v>
+      </c>
+      <c r="XV2" t="n">
+        <v>1096373</v>
+      </c>
+      <c r="XW2" t="n">
+        <v>1179622</v>
+      </c>
+      <c r="XX2" t="n">
+        <v>906232</v>
+      </c>
+      <c r="XY2" t="n">
+        <v>659767</v>
+      </c>
+      <c r="XZ2" t="n">
+        <v>33221</v>
+      </c>
+      <c r="YA2" t="n">
+        <v>903266</v>
+      </c>
+      <c r="YB2" t="n">
+        <v>674107</v>
+      </c>
+      <c r="YC2" t="n">
+        <v>474673</v>
+      </c>
+      <c r="YD2" t="n">
+        <v>697007</v>
+      </c>
+      <c r="YE2" t="n">
+        <v>3878</v>
+      </c>
+      <c r="YF2" t="n">
+        <v>575685</v>
+      </c>
+      <c r="YG2" t="n">
+        <v>211748</v>
+      </c>
+      <c r="YH2" t="n">
+        <v>322804</v>
+      </c>
+      <c r="YI2" t="n">
+        <v>442069</v>
+      </c>
+      <c r="YJ2" t="n">
+        <v>720361</v>
+      </c>
+      <c r="YK2" t="n">
+        <v>391</v>
+      </c>
+      <c r="YL2" t="n">
+        <v>729873</v>
+      </c>
+      <c r="YM2" t="n">
+        <v>138059</v>
+      </c>
+      <c r="YN2" t="n">
+        <v>455920</v>
+      </c>
+      <c r="YO2" t="n">
+        <v>1120896</v>
+      </c>
+      <c r="YP2" t="n">
+        <v>833985</v>
+      </c>
+      <c r="YQ2" t="n">
+        <v>227902</v>
+      </c>
+      <c r="YR2" t="n">
+        <v>65362</v>
+      </c>
+      <c r="YS2" t="n">
+        <v>1128074</v>
+      </c>
+      <c r="YT2" t="n">
+        <v>1071944</v>
+      </c>
+      <c r="YU2" t="n">
+        <v>644087</v>
+      </c>
+      <c r="YV2" t="n">
+        <v>628307</v>
+      </c>
+      <c r="YW2" t="n">
+        <v>277100</v>
+      </c>
+      <c r="YX2" t="n">
+        <v>786800</v>
+      </c>
+      <c r="YY2" t="n">
+        <v>1081234</v>
+      </c>
+      <c r="YZ2" t="n">
+        <v>684053</v>
+      </c>
+      <c r="ZA2" t="n">
+        <v>635899</v>
+      </c>
+      <c r="ZB2" t="n">
+        <v>747128</v>
+      </c>
+      <c r="ZC2" t="n">
+        <v>482170</v>
+      </c>
+      <c r="ZD2" t="n">
+        <v>1152227</v>
+      </c>
+      <c r="ZE2" t="n">
+        <v>159097</v>
+      </c>
+      <c r="ZF2" t="n">
+        <v>110481</v>
+      </c>
+      <c r="ZG2" t="n">
+        <v>1038096</v>
+      </c>
+      <c r="ZH2" t="n">
+        <v>824317</v>
+      </c>
+      <c r="ZI2" t="n">
+        <v>31184</v>
+      </c>
+      <c r="ZJ2" t="n">
+        <v>63224</v>
+      </c>
+      <c r="ZK2" t="n">
+        <v>612259</v>
+      </c>
+      <c r="ZL2" t="n">
+        <v>243234</v>
+      </c>
+      <c r="ZM2" t="n">
+        <v>303836</v>
+      </c>
+      <c r="ZN2" t="n">
+        <v>788097</v>
+      </c>
+      <c r="ZO2" t="n">
+        <v>254032</v>
+      </c>
+      <c r="ZP2" t="n">
+        <v>422287</v>
+      </c>
+      <c r="ZQ2" t="n">
+        <v>957326</v>
+      </c>
+      <c r="ZR2" t="n">
+        <v>451791</v>
+      </c>
+      <c r="ZS2" t="n">
+        <v>236568</v>
+      </c>
+      <c r="ZT2" t="n">
+        <v>1124378</v>
+      </c>
+      <c r="ZU2" t="n">
+        <v>141901</v>
+      </c>
+      <c r="ZV2" t="n">
+        <v>1138018</v>
+      </c>
+      <c r="ZW2" t="n">
+        <v>543410</v>
+      </c>
+      <c r="ZX2" t="n">
+        <v>106358</v>
+      </c>
+      <c r="ZY2" t="n">
+        <v>882318</v>
+      </c>
+      <c r="ZZ2" t="n">
+        <v>28260</v>
+      </c>
+      <c r="AAA2" t="n">
+        <v>1193565</v>
+      </c>
+      <c r="AAB2" t="n">
+        <v>550365</v>
+      </c>
+      <c r="AAC2" t="n">
+        <v>698600</v>
+      </c>
+      <c r="AAD2" t="n">
+        <v>790553</v>
+      </c>
+      <c r="AAE2" t="n">
+        <v>51010</v>
+      </c>
+      <c r="AAF2" t="n">
+        <v>160273</v>
+      </c>
+      <c r="AAG2" t="n">
+        <v>528690</v>
+      </c>
+      <c r="AAH2" t="n">
+        <v>108038</v>
+      </c>
+      <c r="AAI2" t="n">
+        <v>544013</v>
+      </c>
+      <c r="AAJ2" t="n">
+        <v>591408</v>
+      </c>
+      <c r="AAK2" t="n">
+        <v>760164</v>
+      </c>
+      <c r="AAL2" t="n">
+        <v>459946</v>
+      </c>
+      <c r="AAM2" t="n">
+        <v>980054</v>
+      </c>
+      <c r="AAN2" t="n">
+        <v>599395</v>
+      </c>
+      <c r="AAO2" t="n">
+        <v>463080</v>
+      </c>
+      <c r="AAP2" t="n">
+        <v>287249</v>
+      </c>
+      <c r="AAQ2" t="n">
+        <v>1154747</v>
+      </c>
+      <c r="AAR2" t="n">
+        <v>416549</v>
+      </c>
+      <c r="AAS2" t="n">
+        <v>916340</v>
+      </c>
+      <c r="AAT2" t="n">
+        <v>426607</v>
+      </c>
+      <c r="AAU2" t="n">
+        <v>970783</v>
+      </c>
+      <c r="AAV2" t="n">
+        <v>827058</v>
+      </c>
+      <c r="AAW2" t="n">
+        <v>667407</v>
+      </c>
+      <c r="AAX2" t="n">
+        <v>872126</v>
+      </c>
+      <c r="AAY2" t="n">
+        <v>343879</v>
+      </c>
+      <c r="AAZ2" t="n">
+        <v>1163861</v>
+      </c>
+      <c r="ABA2" t="n">
+        <v>55392</v>
+      </c>
+      <c r="ABB2" t="n">
+        <v>492187</v>
+      </c>
+      <c r="ABC2" t="n">
+        <v>273293</v>
+      </c>
+      <c r="ABD2" t="n">
+        <v>583406</v>
+      </c>
+      <c r="ABE2" t="n">
+        <v>870260</v>
+      </c>
+      <c r="ABF2" t="n">
+        <v>1060000</v>
+      </c>
+      <c r="ABG2" t="n">
+        <v>691210</v>
+      </c>
+      <c r="ABH2" t="n">
+        <v>336710</v>
+      </c>
+      <c r="ABI2" t="n">
+        <v>76085</v>
+      </c>
+      <c r="ABJ2" t="n">
+        <v>0</v>
+      </c>
+      <c r="ABK2" t="n">
+        <v>1044904</v>
+      </c>
+      <c r="ABL2" t="n">
+        <v>412493</v>
+      </c>
+      <c r="ABM2" t="n">
+        <v>153473</v>
+      </c>
+      <c r="ABN2" t="n">
+        <v>11136</v>
+      </c>
+      <c r="ABO2" t="n">
+        <v>738405</v>
+      </c>
+      <c r="ABP2" t="n">
+        <v>924831</v>
+      </c>
+      <c r="ABQ2" t="n">
+        <v>397440</v>
+      </c>
+      <c r="ABR2" t="n">
+        <v>681764</v>
+      </c>
+      <c r="ABS2" t="n">
+        <v>741865</v>
+      </c>
+      <c r="ABT2" t="n">
+        <v>213108</v>
+      </c>
+      <c r="ABU2" t="n">
+        <v>224744</v>
+      </c>
+      <c r="ABV2" t="n">
+        <v>34374</v>
+      </c>
+      <c r="ABW2" t="n">
+        <v>884367</v>
+      </c>
+      <c r="ABX2" t="n">
+        <v>55638</v>
+      </c>
+      <c r="ABY2" t="n">
+        <v>384395</v>
+      </c>
+      <c r="ABZ2" t="n">
+        <v>496435</v>
+      </c>
+      <c r="ACA2" t="n">
+        <v>386268</v>
+      </c>
+      <c r="ACB2" t="n">
+        <v>200042</v>
+      </c>
+      <c r="ACC2" t="n">
+        <v>401645</v>
+      </c>
+      <c r="ACD2" t="n">
+        <v>1140624</v>
+      </c>
+      <c r="ACE2" t="n">
+        <v>678297</v>
+      </c>
+      <c r="ACF2" t="n">
+        <v>165437</v>
+      </c>
+      <c r="ACG2" t="n">
+        <v>339979</v>
+      </c>
+      <c r="ACH2" t="n">
+        <v>1083546</v>
+      </c>
+      <c r="ACI2" t="n">
+        <v>925251</v>
+      </c>
+      <c r="ACJ2" t="n">
+        <v>858303</v>
+      </c>
+      <c r="ACK2" t="n">
+        <v>368561</v>
+      </c>
+      <c r="ACL2" t="n">
+        <v>1034591</v>
+      </c>
+      <c r="ACM2" t="n">
+        <v>1212617</v>
+      </c>
+      <c r="ACN2" t="n">
+        <v>780248</v>
+      </c>
+      <c r="ACO2" t="n">
+        <v>1028633</v>
+      </c>
+      <c r="ACP2" t="n">
+        <v>3079</v>
+      </c>
+      <c r="ACQ2" t="n">
+        <v>619879</v>
+      </c>
+      <c r="ACR2" t="n">
+        <v>66177</v>
+      </c>
+      <c r="ACS2" t="n">
+        <v>1055640</v>
+      </c>
+      <c r="ACT2" t="n">
+        <v>937582</v>
+      </c>
+      <c r="ACU2" t="n">
+        <v>150712</v>
+      </c>
+      <c r="ACV2" t="n">
+        <v>869705</v>
+      </c>
+      <c r="ACW2" t="n">
+        <v>1199815</v>
+      </c>
+      <c r="ACX2" t="n">
+        <v>43752</v>
+      </c>
+      <c r="ACY2" t="n">
+        <v>281777</v>
+      </c>
+      <c r="ACZ2" t="n">
+        <v>72701</v>
+      </c>
+      <c r="ADA2" t="n">
+        <v>606517</v>
+      </c>
+      <c r="ADB2" t="n">
+        <v>613973</v>
+      </c>
+      <c r="ADC2" t="n">
+        <v>95093</v>
+      </c>
+      <c r="ADD2" t="n">
+        <v>853409</v>
+      </c>
+      <c r="ADE2" t="n">
+        <v>221040</v>
+      </c>
+      <c r="ADF2" t="n">
+        <v>1203515</v>
+      </c>
+      <c r="ADG2" t="n">
+        <v>25595</v>
+      </c>
+      <c r="ADH2" t="n">
+        <v>91919</v>
+      </c>
+      <c r="ADI2" t="n">
+        <v>737129</v>
+      </c>
+      <c r="ADJ2" t="n">
+        <v>726305</v>
+      </c>
+      <c r="ADK2" t="n">
+        <v>921138</v>
+      </c>
+      <c r="ADL2" t="n">
+        <v>774301</v>
+      </c>
+      <c r="ADM2" t="n">
+        <v>1145348</v>
+      </c>
+      <c r="ADN2" t="n">
+        <v>227358</v>
+      </c>
+      <c r="ADO2" t="n">
+        <v>1007230</v>
+      </c>
+      <c r="ADP2" t="n">
+        <v>492500</v>
+      </c>
+      <c r="ADQ2" t="n">
+        <v>1191471</v>
+      </c>
+      <c r="ADR2" t="n">
+        <v>125222</v>
+      </c>
+      <c r="ADS2" t="n">
+        <v>107665</v>
+      </c>
+      <c r="ADT2" t="n">
+        <v>557511</v>
+      </c>
+      <c r="ADU2" t="n">
+        <v>908306</v>
+      </c>
+      <c r="ADV2" t="n">
+        <v>92127</v>
+      </c>
+      <c r="ADW2" t="n">
+        <v>118782</v>
+      </c>
+      <c r="ADX2" t="n">
+        <v>419906</v>
+      </c>
+      <c r="ADY2" t="n">
+        <v>864233</v>
+      </c>
+      <c r="ADZ2" t="n">
+        <v>231575</v>
+      </c>
+      <c r="AEA2" t="n">
+        <v>793377</v>
+      </c>
+      <c r="AEB2" t="n">
+        <v>802691</v>
+      </c>
+      <c r="AEC2" t="n">
+        <v>760309</v>
+      </c>
+      <c r="AED2" t="n">
+        <v>373288</v>
+      </c>
+      <c r="AEE2" t="n">
+        <v>109483</v>
+      </c>
+      <c r="AEF2" t="n">
+        <v>1084840</v>
+      </c>
+      <c r="AEG2" t="n">
+        <v>569409</v>
+      </c>
+      <c r="AEH2" t="n">
+        <v>257229</v>
+      </c>
+      <c r="AEI2" t="n">
+        <v>324991</v>
+      </c>
+      <c r="AEJ2" t="n">
+        <v>794925</v>
+      </c>
+      <c r="AEK2" t="n">
+        <v>162163</v>
+      </c>
+      <c r="AEL2" t="n">
+        <v>723690</v>
+      </c>
+      <c r="AEM2" t="n">
+        <v>246669</v>
+      </c>
+      <c r="AEN2" t="n">
+        <v>810703</v>
+      </c>
+      <c r="AEO2" t="n">
+        <v>406625</v>
+      </c>
+      <c r="AEP2" t="n">
+        <v>238502</v>
+      </c>
+      <c r="AEQ2" t="n">
+        <v>446116</v>
+      </c>
+      <c r="AER2" t="n">
+        <v>681331</v>
+      </c>
+      <c r="AES2" t="n">
+        <v>300809</v>
+      </c>
+      <c r="AET2" t="n">
+        <v>962553</v>
+      </c>
+      <c r="AEU2" t="n">
+        <v>574891</v>
+      </c>
+      <c r="AEV2" t="n">
+        <v>711846</v>
+      </c>
+      <c r="AEW2" t="n">
+        <v>93048</v>
+      </c>
+      <c r="AEX2" t="n">
+        <v>915536</v>
+      </c>
+      <c r="AEY2" t="n">
+        <v>38733</v>
+      </c>
+      <c r="AEZ2" t="n">
+        <v>948899</v>
+      </c>
+      <c r="AFA2" t="n">
+        <v>1141694</v>
+      </c>
+      <c r="AFB2" t="n">
+        <v>448065</v>
+      </c>
+      <c r="AFC2" t="n">
+        <v>175995</v>
+      </c>
+      <c r="AFD2" t="n">
+        <v>857767</v>
+      </c>
+      <c r="AFE2" t="n">
+        <v>437519</v>
+      </c>
+      <c r="AFF2" t="n">
+        <v>177106</v>
+      </c>
+      <c r="AFG2" t="n">
+        <v>51288</v>
+      </c>
+      <c r="AFH2" t="n">
+        <v>991120</v>
+      </c>
+      <c r="AFI2" t="n">
+        <v>320655</v>
+      </c>
+      <c r="AFJ2" t="n">
+        <v>616182</v>
+      </c>
+      <c r="AFK2" t="n">
+        <v>329223</v>
+      </c>
+      <c r="AFL2" t="n">
+        <v>865513</v>
+      </c>
+      <c r="AFM2" t="n">
+        <v>83364</v>
+      </c>
+      <c r="AFN2" t="n">
+        <v>1087814</v>
+      </c>
+      <c r="AFO2" t="n">
+        <v>417586</v>
+      </c>
+      <c r="AFP2" t="n">
+        <v>267572</v>
+      </c>
+      <c r="AFQ2" t="n">
+        <v>1018625</v>
+      </c>
+      <c r="AFR2" t="n">
+        <v>804558</v>
+      </c>
+      <c r="AFS2" t="n">
+        <v>118016</v>
+      </c>
+      <c r="AFT2" t="n">
+        <v>282568</v>
+      </c>
+      <c r="AFU2" t="n">
+        <v>967310</v>
+      </c>
+      <c r="AFV2" t="n">
+        <v>786308</v>
+      </c>
+      <c r="AFW2" t="n">
+        <v>1197105</v>
+      </c>
+      <c r="AFX2" t="n">
+        <v>954148</v>
+      </c>
+      <c r="AFY2" t="n">
+        <v>329154</v>
+      </c>
+      <c r="AFZ2" t="n">
+        <v>259018</v>
+      </c>
+      <c r="AGA2" t="n">
+        <v>718260</v>
+      </c>
+      <c r="AGB2" t="n">
+        <v>133201</v>
+      </c>
+      <c r="AGC2" t="n">
+        <v>1025678</v>
+      </c>
+      <c r="AGD2" t="n">
+        <v>978364</v>
+      </c>
+      <c r="AGE2" t="n">
+        <v>431343</v>
+      </c>
+      <c r="AGF2" t="n">
+        <v>452331</v>
+      </c>
+      <c r="AGG2" t="n">
+        <v>1015677</v>
+      </c>
+      <c r="AGH2" t="n">
+        <v>371239</v>
+      </c>
+      <c r="AGI2" t="n">
+        <v>333403</v>
+      </c>
+      <c r="AGJ2" t="n">
+        <v>375915</v>
+      </c>
+      <c r="AGK2" t="n">
+        <v>1054101</v>
+      </c>
+      <c r="AGL2" t="n">
+        <v>1199680</v>
+      </c>
+      <c r="AGM2" t="n">
+        <v>300894</v>
+      </c>
+      <c r="AGN2" t="n">
+        <v>885934</v>
+      </c>
+      <c r="AGO2" t="n">
+        <v>347714</v>
+      </c>
+      <c r="AGP2" t="n">
+        <v>1172417</v>
+      </c>
+      <c r="AGQ2" t="n">
+        <v>66396</v>
+      </c>
+      <c r="AGR2" t="n">
+        <v>703808</v>
+      </c>
+      <c r="AGS2" t="n">
+        <v>352690</v>
+      </c>
+      <c r="AGT2" t="n">
+        <v>944983</v>
+      </c>
+      <c r="AGU2" t="n">
+        <v>671150</v>
+      </c>
+      <c r="AGV2" t="n">
+        <v>554852</v>
+      </c>
+      <c r="AGW2" t="n">
+        <v>502829</v>
+      </c>
+      <c r="AGX2" t="n">
+        <v>544678</v>
+      </c>
+      <c r="AGY2" t="n">
+        <v>964474</v>
+      </c>
+      <c r="AGZ2" t="n">
+        <v>695645</v>
+      </c>
+      <c r="AHA2" t="n">
+        <v>276899</v>
+      </c>
+      <c r="AHB2" t="n">
+        <v>214</v>
+      </c>
+      <c r="AHC2" t="n">
+        <v>250600</v>
+      </c>
+      <c r="AHD2" t="n">
+        <v>471849</v>
+      </c>
+      <c r="AHE2" t="n">
+        <v>12846</v>
+      </c>
+      <c r="AHF2" t="n">
+        <v>603899</v>
+      </c>
+      <c r="AHG2" t="n">
+        <v>174420</v>
+      </c>
+      <c r="AHH2" t="n">
+        <v>639071</v>
+      </c>
+      <c r="AHI2" t="n">
+        <v>974677</v>
+      </c>
+      <c r="AHJ2" t="n">
+        <v>498879</v>
+      </c>
+      <c r="AHK2" t="n">
+        <v>1092286</v>
+      </c>
+      <c r="AHL2" t="n">
+        <v>796224</v>
+      </c>
+      <c r="AHM2" t="n">
+        <v>86428</v>
+      </c>
+      <c r="AHN2" t="n">
+        <v>815806</v>
+      </c>
+      <c r="AHO2" t="n">
+        <v>600506</v>
+      </c>
+      <c r="AHP2" t="n">
+        <v>206175</v>
+      </c>
+      <c r="AHQ2" t="n">
+        <v>935180</v>
+      </c>
+      <c r="AHR2" t="n">
+        <v>900107</v>
+      </c>
+      <c r="AHS2" t="n">
+        <v>117141</v>
+      </c>
+      <c r="AHT2" t="n">
+        <v>189998</v>
+      </c>
+      <c r="AHU2" t="n">
+        <v>851727</v>
+      </c>
+      <c r="AHV2" t="n">
+        <v>387471</v>
+      </c>
+      <c r="AHW2" t="n">
+        <v>727824</v>
+      </c>
+      <c r="AHX2" t="n">
+        <v>21336</v>
+      </c>
+      <c r="AHY2" t="n">
+        <v>1038632</v>
+      </c>
+      <c r="AHZ2" t="n">
+        <v>341975</v>
+      </c>
+      <c r="AIA2" t="n">
+        <v>1206936</v>
+      </c>
+      <c r="AIB2" t="n">
+        <v>818357</v>
+      </c>
+      <c r="AIC2" t="n">
+        <v>855901</v>
+      </c>
+      <c r="AID2" t="n">
+        <v>163100</v>
+      </c>
+      <c r="AIE2" t="n">
+        <v>810857</v>
+      </c>
+      <c r="AIF2" t="n">
+        <v>71115</v>
+      </c>
+      <c r="AIG2" t="n">
+        <v>1063404</v>
+      </c>
+      <c r="AIH2" t="n">
+        <v>1162031</v>
+      </c>
+      <c r="AII2" t="n">
+        <v>54908</v>
+      </c>
+      <c r="AIJ2" t="n">
+        <v>396602</v>
+      </c>
+      <c r="AIK2" t="n">
+        <v>919691</v>
+      </c>
+      <c r="AIL2" t="n">
+        <v>79258</v>
+      </c>
+      <c r="AIM2" t="n">
+        <v>513436</v>
+      </c>
+      <c r="AIN2" t="n">
+        <v>136161</v>
+      </c>
+      <c r="AIO2" t="n">
+        <v>677109</v>
+      </c>
+      <c r="AIP2" t="n">
+        <v>207166</v>
+      </c>
+      <c r="AIQ2" t="n">
+        <v>1022865</v>
+      </c>
+      <c r="AIR2" t="n">
+        <v>1103532</v>
+      </c>
+      <c r="AIS2" t="n">
+        <v>455824</v>
+      </c>
+      <c r="AIT2" t="n">
+        <v>1063580</v>
+      </c>
+      <c r="AIU2" t="n">
+        <v>956084</v>
+      </c>
+      <c r="AIV2" t="n">
+        <v>1050341</v>
+      </c>
+      <c r="AIW2" t="n">
+        <v>9841</v>
+      </c>
+      <c r="AIX2" t="n">
+        <v>235791</v>
+      </c>
+      <c r="AIY2" t="n">
+        <v>941333</v>
+      </c>
+      <c r="AIZ2" t="n">
+        <v>1098809</v>
+      </c>
+      <c r="AJA2" t="n">
+        <v>1184890</v>
+      </c>
+      <c r="AJB2" t="n">
+        <v>688511</v>
+      </c>
+      <c r="AJC2" t="n">
+        <v>579482</v>
+      </c>
+      <c r="AJD2" t="n">
+        <v>1075036</v>
+      </c>
+      <c r="AJE2" t="n">
+        <v>1177145</v>
+      </c>
+      <c r="AJF2" t="n">
+        <v>325501</v>
+      </c>
+      <c r="AJG2" t="n">
+        <v>831081</v>
+      </c>
+      <c r="AJH2" t="n">
+        <v>358468</v>
+      </c>
+      <c r="AJI2" t="n">
+        <v>439023</v>
+      </c>
+      <c r="AJJ2" t="n">
+        <v>1110091</v>
+      </c>
+      <c r="AJK2" t="n">
+        <v>739283</v>
+      </c>
+      <c r="AJL2" t="n">
+        <v>465627</v>
+      </c>
+      <c r="AJM2" t="n">
+        <v>181902</v>
+      </c>
+      <c r="AJN2" t="n">
+        <v>445914</v>
+      </c>
+      <c r="AJO2" t="n">
+        <v>612714</v>
+      </c>
+      <c r="AJP2" t="n">
+        <v>731937</v>
+      </c>
+      <c r="AJQ2" t="n">
+        <v>392770</v>
+      </c>
+      <c r="AJR2" t="n">
+        <v>366677</v>
+      </c>
+      <c r="AJS2" t="n">
+        <v>674161</v>
+      </c>
+      <c r="AJT2" t="n">
+        <v>40865</v>
+      </c>
+      <c r="AJU2" t="n">
+        <v>142397</v>
+      </c>
+      <c r="AJV2" t="n">
+        <v>384575</v>
+      </c>
+      <c r="AJW2" t="n">
+        <v>765387</v>
+      </c>
+      <c r="AJX2" t="n">
+        <v>286783</v>
+      </c>
+      <c r="AJY2" t="n">
+        <v>31358</v>
+      </c>
+      <c r="AJZ2" t="n">
+        <v>524406</v>
+      </c>
+      <c r="AKA2" t="n">
+        <v>186592</v>
+      </c>
+      <c r="AKB2" t="n">
+        <v>702184</v>
+      </c>
+      <c r="AKC2" t="n">
+        <v>972341</v>
+      </c>
+      <c r="AKD2" t="n">
+        <v>240038</v>
+      </c>
+      <c r="AKE2" t="n">
+        <v>466203</v>
+      </c>
+      <c r="AKF2" t="n">
+        <v>768216</v>
+      </c>
+      <c r="AKG2" t="n">
+        <v>1137755</v>
+      </c>
+      <c r="AKH2" t="n">
+        <v>1144146</v>
+      </c>
+      <c r="AKI2" t="n">
+        <v>732715</v>
+      </c>
+      <c r="AKJ2" t="n">
+        <v>516605</v>
+      </c>
+      <c r="AKK2" t="n">
+        <v>831330</v>
+      </c>
+      <c r="AKL2" t="n">
+        <v>239478</v>
+      </c>
+      <c r="AKM2" t="n">
+        <v>941874</v>
+      </c>
+      <c r="AKN2" t="n">
+        <v>548790</v>
+      </c>
+      <c r="AKO2" t="n">
+        <v>552633</v>
+      </c>
+      <c r="AKP2" t="n">
+        <v>324147</v>
+      </c>
+      <c r="AKQ2" t="n">
+        <v>846116</v>
+      </c>
+      <c r="AKR2" t="n">
+        <v>751315</v>
+      </c>
+      <c r="AKS2" t="n">
+        <v>1170872</v>
+      </c>
+      <c r="AKT2" t="n">
+        <v>650602</v>
+      </c>
+      <c r="AKU2" t="n">
+        <v>103510</v>
+      </c>
+      <c r="AKV2" t="n">
+        <v>949004</v>
+      </c>
+      <c r="AKW2" t="n">
+        <v>16572</v>
+      </c>
+      <c r="AKX2" t="n">
+        <v>594620</v>
+      </c>
+      <c r="AKY2" t="n">
+        <v>749434</v>
+      </c>
+      <c r="AKZ2" t="n">
+        <v>144077</v>
+      </c>
+      <c r="ALA2" t="n">
+        <v>802579</v>
+      </c>
+      <c r="ALB2" t="n">
+        <v>431807</v>
+      </c>
+      <c r="ALC2" t="n">
+        <v>262444</v>
+      </c>
+      <c r="ALD2" t="n">
+        <v>1136666</v>
+      </c>
+      <c r="ALE2" t="n">
+        <v>364436</v>
+      </c>
+      <c r="ALF2" t="n">
+        <v>717447</v>
+      </c>
+      <c r="ALG2" t="n">
+        <v>276251</v>
+      </c>
+      <c r="ALH2" t="n">
+        <v>330340</v>
+      </c>
+      <c r="ALI2" t="n">
+        <v>308668</v>
+      </c>
+      <c r="ALJ2" t="n">
+        <v>539503</v>
+      </c>
+      <c r="ALK2" t="n">
+        <v>1161384</v>
+      </c>
+      <c r="ALL2" t="n">
+        <v>1175652</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:ALL2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="n">
+        <v>577323433</v>
+      </c>
+      <c r="B1" t="n">
+        <v>3645547</v>
+      </c>
+      <c r="C1" t="inlineStr"/>
+      <c r="D1" t="inlineStr"/>
+      <c r="E1" t="inlineStr"/>
+      <c r="F1" t="inlineStr"/>
+      <c r="G1" t="inlineStr"/>
+      <c r="H1" t="inlineStr"/>
+      <c r="I1" t="inlineStr"/>
+      <c r="J1" t="inlineStr"/>
+      <c r="K1" t="inlineStr"/>
+      <c r="L1" t="inlineStr"/>
+      <c r="M1" t="inlineStr"/>
+      <c r="N1" t="inlineStr"/>
+      <c r="O1" t="inlineStr"/>
+      <c r="P1" t="inlineStr"/>
+      <c r="Q1" t="inlineStr"/>
+      <c r="R1" t="inlineStr"/>
+      <c r="S1" t="inlineStr"/>
+      <c r="T1" t="inlineStr"/>
+      <c r="U1" t="inlineStr"/>
+      <c r="V1" t="inlineStr"/>
+      <c r="W1" t="inlineStr"/>
+      <c r="X1" t="inlineStr"/>
+      <c r="Y1" t="inlineStr"/>
+      <c r="Z1" t="inlineStr"/>
+      <c r="AA1" t="inlineStr"/>
+      <c r="AB1" t="inlineStr"/>
+      <c r="AC1" t="inlineStr"/>
+      <c r="AD1" t="inlineStr"/>
+      <c r="AE1" t="inlineStr"/>
+      <c r="AF1" t="inlineStr"/>
+      <c r="AG1" t="inlineStr"/>
+      <c r="AH1" t="inlineStr"/>
+      <c r="AI1" t="inlineStr"/>
+      <c r="AJ1" t="inlineStr"/>
+      <c r="AK1" t="inlineStr"/>
+      <c r="AL1" t="inlineStr"/>
+      <c r="AM1" t="inlineStr"/>
+      <c r="AN1" t="inlineStr"/>
+      <c r="AO1" t="inlineStr"/>
+      <c r="AP1" t="inlineStr"/>
+      <c r="AQ1" t="inlineStr"/>
+      <c r="AR1" t="inlineStr"/>
+      <c r="AS1" t="inlineStr"/>
+      <c r="AT1" t="inlineStr"/>
+      <c r="AU1" t="inlineStr"/>
+      <c r="AV1" t="inlineStr"/>
+      <c r="AW1" t="inlineStr"/>
+      <c r="AX1" t="inlineStr"/>
+      <c r="AY1" t="inlineStr"/>
+      <c r="AZ1" t="inlineStr"/>
+      <c r="BA1" t="inlineStr"/>
+      <c r="BB1" t="inlineStr"/>
+      <c r="BC1" t="inlineStr"/>
+      <c r="BD1" t="inlineStr"/>
+      <c r="BE1" t="inlineStr"/>
+      <c r="BF1" t="inlineStr"/>
+      <c r="BG1" t="inlineStr"/>
+      <c r="BH1" t="inlineStr"/>
+      <c r="BI1" t="inlineStr"/>
+      <c r="BJ1" t="inlineStr"/>
+      <c r="BK1" t="inlineStr"/>
+      <c r="BL1" t="inlineStr"/>
+      <c r="BM1" t="inlineStr"/>
+      <c r="BN1" t="inlineStr"/>
+      <c r="BO1" t="inlineStr"/>
+      <c r="BP1" t="inlineStr"/>
+      <c r="BQ1" t="inlineStr"/>
+      <c r="BR1" t="inlineStr"/>
+      <c r="BS1" t="inlineStr"/>
+      <c r="BT1" t="inlineStr"/>
+      <c r="BU1" t="inlineStr"/>
+      <c r="BV1" t="inlineStr"/>
+      <c r="BW1" t="inlineStr"/>
+      <c r="BX1" t="inlineStr"/>
+      <c r="BY1" t="inlineStr"/>
+      <c r="BZ1" t="inlineStr"/>
+      <c r="CA1" t="inlineStr"/>
+      <c r="CB1" t="inlineStr"/>
+      <c r="CC1" t="inlineStr"/>
+      <c r="CD1" t="inlineStr"/>
+      <c r="CE1" t="inlineStr"/>
+      <c r="CF1" t="inlineStr"/>
+      <c r="CG1" t="inlineStr"/>
+      <c r="CH1" t="inlineStr"/>
+      <c r="CI1" t="inlineStr"/>
+      <c r="CJ1" t="inlineStr"/>
+      <c r="CK1" t="inlineStr"/>
+      <c r="CL1" t="inlineStr"/>
+      <c r="CM1" t="inlineStr"/>
+      <c r="CN1" t="inlineStr"/>
+      <c r="CO1" t="inlineStr"/>
+      <c r="CP1" t="inlineStr"/>
+      <c r="CQ1" t="inlineStr"/>
+      <c r="CR1" t="inlineStr"/>
+      <c r="CS1" t="inlineStr"/>
+      <c r="CT1" t="inlineStr"/>
+      <c r="CU1" t="inlineStr"/>
+      <c r="CV1" t="inlineStr"/>
+      <c r="CW1" t="inlineStr"/>
+      <c r="CX1" t="inlineStr"/>
+      <c r="CY1" t="inlineStr"/>
+      <c r="CZ1" t="inlineStr"/>
+      <c r="DA1" t="inlineStr"/>
+      <c r="DB1" t="inlineStr"/>
+      <c r="DC1" t="inlineStr"/>
+      <c r="DD1" t="inlineStr"/>
+      <c r="DE1" t="inlineStr"/>
+      <c r="DF1" t="inlineStr"/>
+      <c r="DG1" t="inlineStr"/>
+      <c r="DH1" t="inlineStr"/>
+      <c r="DI1" t="inlineStr"/>
+      <c r="DJ1" t="inlineStr"/>
+      <c r="DK1" t="inlineStr"/>
+      <c r="DL1" t="inlineStr"/>
+      <c r="DM1" t="inlineStr"/>
+      <c r="DN1" t="inlineStr"/>
+      <c r="DO1" t="inlineStr"/>
+      <c r="DP1" t="inlineStr"/>
+      <c r="DQ1" t="inlineStr"/>
+      <c r="DR1" t="inlineStr"/>
+      <c r="DS1" t="inlineStr"/>
+      <c r="DT1" t="inlineStr"/>
+      <c r="DU1" t="inlineStr"/>
+      <c r="DV1" t="inlineStr"/>
+      <c r="DW1" t="inlineStr"/>
+      <c r="DX1" t="inlineStr"/>
+      <c r="DY1" t="inlineStr"/>
+      <c r="DZ1" t="inlineStr"/>
+      <c r="EA1" t="inlineStr"/>
+      <c r="EB1" t="inlineStr"/>
+      <c r="EC1" t="inlineStr"/>
+      <c r="ED1" t="inlineStr"/>
+      <c r="EE1" t="inlineStr"/>
+      <c r="EF1" t="inlineStr"/>
+      <c r="EG1" t="inlineStr"/>
+      <c r="EH1" t="inlineStr"/>
+      <c r="EI1" t="inlineStr"/>
+      <c r="EJ1" t="inlineStr"/>
+      <c r="EK1" t="inlineStr"/>
+      <c r="EL1" t="inlineStr"/>
+      <c r="EM1" t="inlineStr"/>
+      <c r="EN1" t="inlineStr"/>
+      <c r="EO1" t="inlineStr"/>
+      <c r="EP1" t="inlineStr"/>
+      <c r="EQ1" t="inlineStr"/>
+      <c r="ER1" t="inlineStr"/>
+      <c r="ES1" t="inlineStr"/>
+      <c r="ET1" t="inlineStr"/>
+      <c r="EU1" t="inlineStr"/>
+      <c r="EV1" t="inlineStr"/>
+      <c r="EW1" t="inlineStr"/>
+      <c r="EX1" t="inlineStr"/>
+      <c r="EY1" t="inlineStr"/>
+      <c r="EZ1" t="inlineStr"/>
+      <c r="FA1" t="inlineStr"/>
+      <c r="FB1" t="inlineStr"/>
+      <c r="FC1" t="inlineStr"/>
+      <c r="FD1" t="inlineStr"/>
+      <c r="FE1" t="inlineStr"/>
+      <c r="FF1" t="inlineStr"/>
+      <c r="FG1" t="inlineStr"/>
+      <c r="FH1" t="inlineStr"/>
+      <c r="FI1" t="inlineStr"/>
+      <c r="FJ1" t="inlineStr"/>
+      <c r="FK1" t="inlineStr"/>
+      <c r="FL1" t="inlineStr"/>
+      <c r="FM1" t="inlineStr"/>
+      <c r="FN1" t="inlineStr"/>
+      <c r="FO1" t="inlineStr"/>
+      <c r="FP1" t="inlineStr"/>
+      <c r="FQ1" t="inlineStr"/>
+      <c r="FR1" t="inlineStr"/>
+      <c r="FS1" t="inlineStr"/>
+      <c r="FT1" t="inlineStr"/>
+      <c r="FU1" t="inlineStr"/>
+      <c r="FV1" t="inlineStr"/>
+      <c r="FW1" t="inlineStr"/>
+      <c r="FX1" t="inlineStr"/>
+      <c r="FY1" t="inlineStr"/>
+      <c r="FZ1" t="inlineStr"/>
+      <c r="GA1" t="inlineStr"/>
+      <c r="GB1" t="inlineStr"/>
+      <c r="GC1" t="inlineStr"/>
+      <c r="GD1" t="inlineStr"/>
+      <c r="GE1" t="inlineStr"/>
+      <c r="GF1" t="inlineStr"/>
+      <c r="GG1" t="inlineStr"/>
+      <c r="GH1" t="inlineStr"/>
+      <c r="GI1" t="inlineStr"/>
+      <c r="GJ1" t="inlineStr"/>
+      <c r="GK1" t="inlineStr"/>
+      <c r="GL1" t="inlineStr"/>
+      <c r="GM1" t="inlineStr"/>
+      <c r="GN1" t="inlineStr"/>
+      <c r="GO1" t="inlineStr"/>
+      <c r="GP1" t="inlineStr"/>
+      <c r="GQ1" t="inlineStr"/>
+      <c r="GR1" t="inlineStr"/>
+      <c r="GS1" t="inlineStr"/>
+      <c r="GT1" t="inlineStr"/>
+      <c r="GU1" t="inlineStr"/>
+      <c r="GV1" t="inlineStr"/>
+      <c r="GW1" t="inlineStr"/>
+      <c r="GX1" t="inlineStr"/>
+      <c r="GY1" t="inlineStr"/>
+      <c r="GZ1" t="inlineStr"/>
+      <c r="HA1" t="inlineStr"/>
+      <c r="HB1" t="inlineStr"/>
+      <c r="HC1" t="inlineStr"/>
+      <c r="HD1" t="inlineStr"/>
+      <c r="HE1" t="inlineStr"/>
+      <c r="HF1" t="inlineStr"/>
+      <c r="HG1" t="inlineStr"/>
+      <c r="HH1" t="inlineStr"/>
+      <c r="HI1" t="inlineStr"/>
+      <c r="HJ1" t="inlineStr"/>
+      <c r="HK1" t="inlineStr"/>
+      <c r="HL1" t="inlineStr"/>
+      <c r="HM1" t="inlineStr"/>
+      <c r="HN1" t="inlineStr"/>
+      <c r="HO1" t="inlineStr"/>
+      <c r="HP1" t="inlineStr"/>
+      <c r="HQ1" t="inlineStr"/>
+      <c r="HR1" t="inlineStr"/>
+      <c r="HS1" t="inlineStr"/>
+      <c r="HT1" t="inlineStr"/>
+      <c r="HU1" t="inlineStr"/>
+      <c r="HV1" t="inlineStr"/>
+      <c r="HW1" t="inlineStr"/>
+      <c r="HX1" t="inlineStr"/>
+      <c r="HY1" t="inlineStr"/>
+      <c r="HZ1" t="inlineStr"/>
+      <c r="IA1" t="inlineStr"/>
+      <c r="IB1" t="inlineStr"/>
+      <c r="IC1" t="inlineStr"/>
+      <c r="ID1" t="inlineStr"/>
+      <c r="IE1" t="inlineStr"/>
+      <c r="IF1" t="inlineStr"/>
+      <c r="IG1" t="inlineStr"/>
+      <c r="IH1" t="inlineStr"/>
+      <c r="II1" t="inlineStr"/>
+      <c r="IJ1" t="inlineStr"/>
+      <c r="IK1" t="inlineStr"/>
+      <c r="IL1" t="inlineStr"/>
+      <c r="IM1" t="inlineStr"/>
+      <c r="IN1" t="inlineStr"/>
+      <c r="IO1" t="inlineStr"/>
+      <c r="IP1" t="inlineStr"/>
+      <c r="IQ1" t="inlineStr"/>
+      <c r="IR1" t="inlineStr"/>
+      <c r="IS1" t="inlineStr"/>
+      <c r="IT1" t="inlineStr"/>
+      <c r="IU1" t="inlineStr"/>
+      <c r="IV1" t="inlineStr"/>
+      <c r="IW1" t="inlineStr"/>
+      <c r="IX1" t="inlineStr"/>
+      <c r="IY1" t="inlineStr"/>
+      <c r="IZ1" t="inlineStr"/>
+      <c r="JA1" t="inlineStr"/>
+      <c r="JB1" t="inlineStr"/>
+      <c r="JC1" t="inlineStr"/>
+      <c r="JD1" t="inlineStr"/>
+      <c r="JE1" t="inlineStr"/>
+      <c r="JF1" t="inlineStr"/>
+      <c r="JG1" t="inlineStr"/>
+      <c r="JH1" t="inlineStr"/>
+      <c r="JI1" t="inlineStr"/>
+      <c r="JJ1" t="inlineStr"/>
+      <c r="JK1" t="inlineStr"/>
+      <c r="JL1" t="inlineStr"/>
+      <c r="JM1" t="inlineStr"/>
+      <c r="JN1" t="inlineStr"/>
+      <c r="JO1" t="inlineStr"/>
+      <c r="JP1" t="inlineStr"/>
+      <c r="JQ1" t="inlineStr"/>
+      <c r="JR1" t="inlineStr"/>
+      <c r="JS1" t="inlineStr"/>
+      <c r="JT1" t="inlineStr"/>
+      <c r="JU1" t="inlineStr"/>
+      <c r="JV1" t="inlineStr"/>
+      <c r="JW1" t="inlineStr"/>
+      <c r="JX1" t="inlineStr"/>
+      <c r="JY1" t="inlineStr"/>
+      <c r="JZ1" t="inlineStr"/>
+      <c r="KA1" t="inlineStr"/>
+      <c r="KB1" t="inlineStr"/>
+      <c r="KC1" t="inlineStr"/>
+      <c r="KD1" t="inlineStr"/>
+      <c r="KE1" t="inlineStr"/>
+      <c r="KF1" t="inlineStr"/>
+      <c r="KG1" t="inlineStr"/>
+      <c r="KH1" t="inlineStr"/>
+      <c r="KI1" t="inlineStr"/>
+      <c r="KJ1" t="inlineStr"/>
+      <c r="KK1" t="inlineStr"/>
+      <c r="KL1" t="inlineStr"/>
+      <c r="KM1" t="inlineStr"/>
+      <c r="KN1" t="inlineStr"/>
+      <c r="KO1" t="inlineStr"/>
+      <c r="KP1" t="inlineStr"/>
+      <c r="KQ1" t="inlineStr"/>
+      <c r="KR1" t="inlineStr"/>
+      <c r="KS1" t="inlineStr"/>
+      <c r="KT1" t="inlineStr"/>
+      <c r="KU1" t="inlineStr"/>
+      <c r="KV1" t="inlineStr"/>
+      <c r="KW1" t="inlineStr"/>
+      <c r="KX1" t="inlineStr"/>
+      <c r="KY1" t="inlineStr"/>
+      <c r="KZ1" t="inlineStr"/>
+      <c r="LA1" t="inlineStr"/>
+      <c r="LB1" t="inlineStr"/>
+      <c r="LC1" t="inlineStr"/>
+      <c r="LD1" t="inlineStr"/>
+      <c r="LE1" t="inlineStr"/>
+      <c r="LF1" t="inlineStr"/>
+      <c r="LG1" t="inlineStr"/>
+      <c r="LH1" t="inlineStr"/>
+      <c r="LI1" t="inlineStr"/>
+      <c r="LJ1" t="inlineStr"/>
+      <c r="LK1" t="inlineStr"/>
+      <c r="LL1" t="inlineStr"/>
+      <c r="LM1" t="inlineStr"/>
+      <c r="LN1" t="inlineStr"/>
+      <c r="LO1" t="inlineStr"/>
+      <c r="LP1" t="inlineStr"/>
+      <c r="LQ1" t="inlineStr"/>
+      <c r="LR1" t="inlineStr"/>
+      <c r="LS1" t="inlineStr"/>
+      <c r="LT1" t="inlineStr"/>
+      <c r="LU1" t="inlineStr"/>
+      <c r="LV1" t="inlineStr"/>
+      <c r="LW1" t="inlineStr"/>
+      <c r="LX1" t="inlineStr"/>
+      <c r="LY1" t="inlineStr"/>
+      <c r="LZ1" t="inlineStr"/>
+      <c r="MA1" t="inlineStr"/>
+      <c r="MB1" t="inlineStr"/>
+      <c r="MC1" t="inlineStr"/>
+      <c r="MD1" t="inlineStr"/>
+      <c r="ME1" t="inlineStr"/>
+      <c r="MF1" t="inlineStr"/>
+      <c r="MG1" t="inlineStr"/>
+      <c r="MH1" t="inlineStr"/>
+      <c r="MI1" t="inlineStr"/>
+      <c r="MJ1" t="inlineStr"/>
+      <c r="MK1" t="inlineStr"/>
+      <c r="ML1" t="inlineStr"/>
+      <c r="MM1" t="inlineStr"/>
+      <c r="MN1" t="inlineStr"/>
+      <c r="MO1" t="inlineStr"/>
+      <c r="MP1" t="inlineStr"/>
+      <c r="MQ1" t="inlineStr"/>
+      <c r="MR1" t="inlineStr"/>
+      <c r="MS1" t="inlineStr"/>
+      <c r="MT1" t="inlineStr"/>
+      <c r="MU1" t="inlineStr"/>
+      <c r="MV1" t="inlineStr"/>
+      <c r="MW1" t="inlineStr"/>
+      <c r="MX1" t="inlineStr"/>
+      <c r="MY1" t="inlineStr"/>
+      <c r="MZ1" t="inlineStr"/>
+      <c r="NA1" t="inlineStr"/>
+      <c r="NB1" t="inlineStr"/>
+      <c r="NC1" t="inlineStr"/>
+      <c r="ND1" t="inlineStr"/>
+      <c r="NE1" t="inlineStr"/>
+      <c r="NF1" t="inlineStr"/>
+      <c r="NG1" t="inlineStr"/>
+      <c r="NH1" t="inlineStr"/>
+      <c r="NI1" t="inlineStr"/>
+      <c r="NJ1" t="inlineStr"/>
+      <c r="NK1" t="inlineStr"/>
+      <c r="NL1" t="inlineStr"/>
+      <c r="NM1" t="inlineStr"/>
+      <c r="NN1" t="inlineStr"/>
+      <c r="NO1" t="inlineStr"/>
+      <c r="NP1" t="inlineStr"/>
+      <c r="NQ1" t="inlineStr"/>
+      <c r="NR1" t="inlineStr"/>
+      <c r="NS1" t="inlineStr"/>
+      <c r="NT1" t="inlineStr"/>
+      <c r="NU1" t="inlineStr"/>
+      <c r="NV1" t="inlineStr"/>
+      <c r="NW1" t="inlineStr"/>
+      <c r="NX1" t="inlineStr"/>
+      <c r="NY1" t="inlineStr"/>
+      <c r="NZ1" t="inlineStr"/>
+      <c r="OA1" t="inlineStr"/>
+      <c r="OB1" t="inlineStr"/>
+      <c r="OC1" t="inlineStr"/>
+      <c r="OD1" t="inlineStr"/>
+      <c r="OE1" t="inlineStr"/>
+      <c r="OF1" t="inlineStr"/>
+      <c r="OG1" t="inlineStr"/>
+      <c r="OH1" t="inlineStr"/>
+      <c r="OI1" t="inlineStr"/>
+      <c r="OJ1" t="inlineStr"/>
+      <c r="OK1" t="inlineStr"/>
+      <c r="OL1" t="inlineStr"/>
+      <c r="OM1" t="inlineStr"/>
+      <c r="ON1" t="inlineStr"/>
+      <c r="OO1" t="inlineStr"/>
+      <c r="OP1" t="inlineStr"/>
+      <c r="OQ1" t="inlineStr"/>
+      <c r="OR1" t="inlineStr"/>
+      <c r="OS1" t="inlineStr"/>
+      <c r="OT1" t="inlineStr"/>
+      <c r="OU1" t="inlineStr"/>
+      <c r="OV1" t="inlineStr"/>
+      <c r="OW1" t="inlineStr"/>
+      <c r="OX1" t="inlineStr"/>
+      <c r="OY1" t="inlineStr"/>
+      <c r="OZ1" t="inlineStr"/>
+      <c r="PA1" t="inlineStr"/>
+      <c r="PB1" t="inlineStr"/>
+      <c r="PC1" t="inlineStr"/>
+      <c r="PD1" t="inlineStr"/>
+      <c r="PE1" t="inlineStr"/>
+      <c r="PF1" t="inlineStr"/>
+      <c r="PG1" t="inlineStr"/>
+      <c r="PH1" t="inlineStr"/>
+      <c r="PI1" t="inlineStr"/>
+      <c r="PJ1" t="inlineStr"/>
+      <c r="PK1" t="inlineStr"/>
+      <c r="PL1" t="inlineStr"/>
+      <c r="PM1" t="inlineStr"/>
+      <c r="PN1" t="inlineStr"/>
+      <c r="PO1" t="inlineStr"/>
+      <c r="PP1" t="inlineStr"/>
+      <c r="PQ1" t="inlineStr"/>
+      <c r="PR1" t="inlineStr"/>
+      <c r="PS1" t="inlineStr"/>
+      <c r="PT1" t="inlineStr"/>
+      <c r="PU1" t="inlineStr"/>
+      <c r="PV1" t="inlineStr"/>
+      <c r="PW1" t="inlineStr"/>
+      <c r="PX1" t="inlineStr"/>
+      <c r="PY1" t="inlineStr"/>
+      <c r="PZ1" t="inlineStr"/>
+      <c r="QA1" t="inlineStr"/>
+      <c r="QB1" t="inlineStr"/>
+      <c r="QC1" t="inlineStr"/>
+      <c r="QD1" t="inlineStr"/>
+      <c r="QE1" t="inlineStr"/>
+      <c r="QF1" t="inlineStr"/>
+      <c r="QG1" t="inlineStr"/>
+      <c r="QH1" t="inlineStr"/>
+      <c r="QI1" t="inlineStr"/>
+      <c r="QJ1" t="inlineStr"/>
+      <c r="QK1" t="inlineStr"/>
+      <c r="QL1" t="inlineStr"/>
+      <c r="QM1" t="inlineStr"/>
+      <c r="QN1" t="inlineStr"/>
+      <c r="QO1" t="inlineStr"/>
+      <c r="QP1" t="inlineStr"/>
+      <c r="QQ1" t="inlineStr"/>
+      <c r="QR1" t="inlineStr"/>
+      <c r="QS1" t="inlineStr"/>
+      <c r="QT1" t="inlineStr"/>
+      <c r="QU1" t="inlineStr"/>
+      <c r="QV1" t="inlineStr"/>
+      <c r="QW1" t="inlineStr"/>
+      <c r="QX1" t="inlineStr"/>
+      <c r="QY1" t="inlineStr"/>
+      <c r="QZ1" t="inlineStr"/>
+      <c r="RA1" t="inlineStr"/>
+      <c r="RB1" t="inlineStr"/>
+      <c r="RC1" t="inlineStr"/>
+      <c r="RD1" t="inlineStr"/>
+      <c r="RE1" t="inlineStr"/>
+      <c r="RF1" t="inlineStr"/>
+      <c r="RG1" t="inlineStr"/>
+      <c r="RH1" t="inlineStr"/>
+      <c r="RI1" t="inlineStr"/>
+      <c r="RJ1" t="inlineStr"/>
+      <c r="RK1" t="inlineStr"/>
+      <c r="RL1" t="inlineStr"/>
+      <c r="RM1" t="inlineStr"/>
+      <c r="RN1" t="inlineStr"/>
+      <c r="RO1" t="inlineStr"/>
+      <c r="RP1" t="inlineStr"/>
+      <c r="RQ1" t="inlineStr"/>
+      <c r="RR1" t="inlineStr"/>
+      <c r="RS1" t="inlineStr"/>
+      <c r="RT1" t="inlineStr"/>
+      <c r="RU1" t="inlineStr"/>
+      <c r="RV1" t="inlineStr"/>
+      <c r="RW1" t="inlineStr"/>
+      <c r="RX1" t="inlineStr"/>
+      <c r="RY1" t="inlineStr"/>
+      <c r="RZ1" t="inlineStr"/>
+      <c r="SA1" t="inlineStr"/>
+      <c r="SB1" t="inlineStr"/>
+      <c r="SC1" t="inlineStr"/>
+      <c r="SD1" t="inlineStr"/>
+      <c r="SE1" t="inlineStr"/>
+      <c r="SF1" t="inlineStr"/>
+      <c r="SG1" t="inlineStr"/>
+      <c r="SH1" t="inlineStr"/>
+      <c r="SI1" t="inlineStr"/>
+      <c r="SJ1" t="inlineStr"/>
+      <c r="SK1" t="inlineStr"/>
+      <c r="SL1" t="inlineStr"/>
+      <c r="SM1" t="inlineStr"/>
+      <c r="SN1" t="inlineStr"/>
+      <c r="SO1" t="inlineStr"/>
+      <c r="SP1" t="inlineStr"/>
+      <c r="SQ1" t="inlineStr"/>
+      <c r="SR1" t="inlineStr"/>
+      <c r="SS1" t="inlineStr"/>
+      <c r="ST1" t="inlineStr"/>
+      <c r="SU1" t="inlineStr"/>
+      <c r="SV1" t="inlineStr"/>
+      <c r="SW1" t="inlineStr"/>
+      <c r="SX1" t="inlineStr"/>
+      <c r="SY1" t="inlineStr"/>
+      <c r="SZ1" t="inlineStr"/>
+      <c r="TA1" t="inlineStr"/>
+      <c r="TB1" t="inlineStr"/>
+      <c r="TC1" t="inlineStr"/>
+      <c r="TD1" t="inlineStr"/>
+      <c r="TE1" t="inlineStr"/>
+      <c r="TF1" t="inlineStr"/>
+      <c r="TG1" t="inlineStr"/>
+      <c r="TH1" t="inlineStr"/>
+      <c r="TI1" t="inlineStr"/>
+      <c r="TJ1" t="inlineStr"/>
+      <c r="TK1" t="inlineStr"/>
+      <c r="TL1" t="inlineStr"/>
+      <c r="TM1" t="inlineStr"/>
+      <c r="TN1" t="inlineStr"/>
+      <c r="TO1" t="inlineStr"/>
+      <c r="TP1" t="inlineStr"/>
+      <c r="TQ1" t="inlineStr"/>
+      <c r="TR1" t="inlineStr"/>
+      <c r="TS1" t="inlineStr"/>
+      <c r="TT1" t="inlineStr"/>
+      <c r="TU1" t="inlineStr"/>
+      <c r="TV1" t="inlineStr"/>
+      <c r="TW1" t="inlineStr"/>
+      <c r="TX1" t="inlineStr"/>
+      <c r="TY1" t="inlineStr"/>
+      <c r="TZ1" t="inlineStr"/>
+      <c r="UA1" t="inlineStr"/>
+      <c r="UB1" t="inlineStr"/>
+      <c r="UC1" t="inlineStr"/>
+      <c r="UD1" t="inlineStr"/>
+      <c r="UE1" t="inlineStr"/>
+      <c r="UF1" t="inlineStr"/>
+      <c r="UG1" t="inlineStr"/>
+      <c r="UH1" t="inlineStr"/>
+      <c r="UI1" t="inlineStr"/>
+      <c r="UJ1" t="inlineStr"/>
+      <c r="UK1" t="inlineStr"/>
+      <c r="UL1" t="inlineStr"/>
+      <c r="UM1" t="inlineStr"/>
+      <c r="UN1" t="inlineStr"/>
+      <c r="UO1" t="inlineStr"/>
+      <c r="UP1" t="inlineStr"/>
+      <c r="UQ1" t="inlineStr"/>
+      <c r="UR1" t="inlineStr"/>
+      <c r="US1" t="inlineStr"/>
+      <c r="UT1" t="inlineStr"/>
+      <c r="UU1" t="inlineStr"/>
+      <c r="UV1" t="inlineStr"/>
+      <c r="UW1" t="inlineStr"/>
+      <c r="UX1" t="inlineStr"/>
+      <c r="UY1" t="inlineStr"/>
+      <c r="UZ1" t="inlineStr"/>
+      <c r="VA1" t="inlineStr"/>
+      <c r="VB1" t="inlineStr"/>
+      <c r="VC1" t="inlineStr"/>
+      <c r="VD1" t="inlineStr"/>
+      <c r="VE1" t="inlineStr"/>
+      <c r="VF1" t="inlineStr"/>
+      <c r="VG1" t="inlineStr"/>
+      <c r="VH1" t="inlineStr"/>
+      <c r="VI1" t="inlineStr"/>
+      <c r="VJ1" t="inlineStr"/>
+      <c r="VK1" t="inlineStr"/>
+      <c r="VL1" t="inlineStr"/>
+      <c r="VM1" t="inlineStr"/>
+      <c r="VN1" t="inlineStr"/>
+      <c r="VO1" t="inlineStr"/>
+      <c r="VP1" t="inlineStr"/>
+      <c r="VQ1" t="inlineStr"/>
+      <c r="VR1" t="inlineStr"/>
+      <c r="VS1" t="inlineStr"/>
+      <c r="VT1" t="inlineStr"/>
+      <c r="VU1" t="inlineStr"/>
+      <c r="VV1" t="inlineStr"/>
+      <c r="VW1" t="inlineStr"/>
+      <c r="VX1" t="inlineStr"/>
+      <c r="VY1" t="inlineStr"/>
+      <c r="VZ1" t="inlineStr"/>
+      <c r="WA1" t="inlineStr"/>
+      <c r="WB1" t="inlineStr"/>
+      <c r="WC1" t="inlineStr"/>
+      <c r="WD1" t="inlineStr"/>
+      <c r="WE1" t="inlineStr"/>
+      <c r="WF1" t="inlineStr"/>
+      <c r="WG1" t="inlineStr"/>
+      <c r="WH1" t="inlineStr"/>
+      <c r="WI1" t="inlineStr"/>
+      <c r="WJ1" t="inlineStr"/>
+      <c r="WK1" t="inlineStr"/>
+      <c r="WL1" t="inlineStr"/>
+      <c r="WM1" t="inlineStr"/>
+      <c r="WN1" t="inlineStr"/>
+      <c r="WO1" t="inlineStr"/>
+      <c r="WP1" t="inlineStr"/>
+      <c r="WQ1" t="inlineStr"/>
+      <c r="WR1" t="inlineStr"/>
+      <c r="WS1" t="inlineStr"/>
+      <c r="WT1" t="inlineStr"/>
+      <c r="WU1" t="inlineStr"/>
+      <c r="WV1" t="inlineStr"/>
+      <c r="WW1" t="inlineStr"/>
+      <c r="WX1" t="inlineStr"/>
+      <c r="WY1" t="inlineStr"/>
+      <c r="WZ1" t="inlineStr"/>
+      <c r="XA1" t="inlineStr"/>
+      <c r="XB1" t="inlineStr"/>
+      <c r="XC1" t="inlineStr"/>
+      <c r="XD1" t="inlineStr"/>
+      <c r="XE1" t="inlineStr"/>
+      <c r="XF1" t="inlineStr"/>
+      <c r="XG1" t="inlineStr"/>
+      <c r="XH1" t="inlineStr"/>
+      <c r="XI1" t="inlineStr"/>
+      <c r="XJ1" t="inlineStr"/>
+      <c r="XK1" t="inlineStr"/>
+      <c r="XL1" t="inlineStr"/>
+      <c r="XM1" t="inlineStr"/>
+      <c r="XN1" t="inlineStr"/>
+      <c r="XO1" t="inlineStr"/>
+      <c r="XP1" t="inlineStr"/>
+      <c r="XQ1" t="inlineStr"/>
+      <c r="XR1" t="inlineStr"/>
+      <c r="XS1" t="inlineStr"/>
+      <c r="XT1" t="inlineStr"/>
+      <c r="XU1" t="inlineStr"/>
+      <c r="XV1" t="inlineStr"/>
+      <c r="XW1" t="inlineStr"/>
+      <c r="XX1" t="inlineStr"/>
+      <c r="XY1" t="inlineStr"/>
+      <c r="XZ1" t="inlineStr"/>
+      <c r="YA1" t="inlineStr"/>
+      <c r="YB1" t="inlineStr"/>
+      <c r="YC1" t="inlineStr"/>
+      <c r="YD1" t="inlineStr"/>
+      <c r="YE1" t="inlineStr"/>
+      <c r="YF1" t="inlineStr"/>
+      <c r="YG1" t="inlineStr"/>
+      <c r="YH1" t="inlineStr"/>
+      <c r="YI1" t="inlineStr"/>
+      <c r="YJ1" t="inlineStr"/>
+      <c r="YK1" t="inlineStr"/>
+      <c r="YL1" t="inlineStr"/>
+      <c r="YM1" t="inlineStr"/>
+      <c r="YN1" t="inlineStr"/>
+      <c r="YO1" t="inlineStr"/>
+      <c r="YP1" t="inlineStr"/>
+      <c r="YQ1" t="inlineStr"/>
+      <c r="YR1" t="inlineStr"/>
+      <c r="YS1" t="inlineStr"/>
+      <c r="YT1" t="inlineStr"/>
+      <c r="YU1" t="inlineStr"/>
+      <c r="YV1" t="inlineStr"/>
+      <c r="YW1" t="inlineStr"/>
+      <c r="YX1" t="inlineStr"/>
+      <c r="YY1" t="inlineStr"/>
+      <c r="YZ1" t="inlineStr"/>
+      <c r="ZA1" t="inlineStr"/>
+      <c r="ZB1" t="inlineStr"/>
+      <c r="ZC1" t="inlineStr"/>
+      <c r="ZD1" t="inlineStr"/>
+      <c r="ZE1" t="inlineStr"/>
+      <c r="ZF1" t="inlineStr"/>
+      <c r="ZG1" t="inlineStr"/>
+      <c r="ZH1" t="inlineStr"/>
+      <c r="ZI1" t="inlineStr"/>
+      <c r="ZJ1" t="inlineStr"/>
+      <c r="ZK1" t="inlineStr"/>
+      <c r="ZL1" t="inlineStr"/>
+      <c r="ZM1" t="inlineStr"/>
+      <c r="ZN1" t="inlineStr"/>
+      <c r="ZO1" t="inlineStr"/>
+      <c r="ZP1" t="inlineStr"/>
+      <c r="ZQ1" t="inlineStr"/>
+      <c r="ZR1" t="inlineStr"/>
+      <c r="ZS1" t="inlineStr"/>
+      <c r="ZT1" t="inlineStr"/>
+      <c r="ZU1" t="inlineStr"/>
+      <c r="ZV1" t="inlineStr"/>
+      <c r="ZW1" t="inlineStr"/>
+      <c r="ZX1" t="inlineStr"/>
+      <c r="ZY1" t="inlineStr"/>
+      <c r="ZZ1" t="inlineStr"/>
+      <c r="AAA1" t="inlineStr"/>
+      <c r="AAB1" t="inlineStr"/>
+      <c r="AAC1" t="inlineStr"/>
+      <c r="AAD1" t="inlineStr"/>
+      <c r="AAE1" t="inlineStr"/>
+      <c r="AAF1" t="inlineStr"/>
+      <c r="AAG1" t="inlineStr"/>
+      <c r="AAH1" t="inlineStr"/>
+      <c r="AAI1" t="inlineStr"/>
+      <c r="AAJ1" t="inlineStr"/>
+      <c r="AAK1" t="inlineStr"/>
+      <c r="AAL1" t="inlineStr"/>
+      <c r="AAM1" t="inlineStr"/>
+      <c r="AAN1" t="inlineStr"/>
+      <c r="AAO1" t="inlineStr"/>
+      <c r="AAP1" t="inlineStr"/>
+      <c r="AAQ1" t="inlineStr"/>
+      <c r="AAR1" t="inlineStr"/>
+      <c r="AAS1" t="inlineStr"/>
+      <c r="AAT1" t="inlineStr"/>
+      <c r="AAU1" t="inlineStr"/>
+      <c r="AAV1" t="inlineStr"/>
+      <c r="AAW1" t="inlineStr"/>
+      <c r="AAX1" t="inlineStr"/>
+      <c r="AAY1" t="inlineStr"/>
+      <c r="AAZ1" t="inlineStr"/>
+      <c r="ABA1" t="inlineStr"/>
+      <c r="ABB1" t="inlineStr"/>
+      <c r="ABC1" t="inlineStr"/>
+      <c r="ABD1" t="inlineStr"/>
+      <c r="ABE1" t="inlineStr"/>
+      <c r="ABF1" t="inlineStr"/>
+      <c r="ABG1" t="inlineStr"/>
+      <c r="ABH1" t="inlineStr"/>
+      <c r="ABI1" t="inlineStr"/>
+      <c r="ABJ1" t="inlineStr"/>
+      <c r="ABK1" t="inlineStr"/>
+      <c r="ABL1" t="inlineStr"/>
+      <c r="ABM1" t="inlineStr"/>
+      <c r="ABN1" t="inlineStr"/>
+      <c r="ABO1" t="inlineStr"/>
+      <c r="ABP1" t="inlineStr"/>
+      <c r="ABQ1" t="inlineStr"/>
+      <c r="ABR1" t="inlineStr"/>
+      <c r="ABS1" t="inlineStr"/>
+      <c r="ABT1" t="inlineStr"/>
+      <c r="ABU1" t="inlineStr"/>
+      <c r="ABV1" t="inlineStr"/>
+      <c r="ABW1" t="inlineStr"/>
+      <c r="ABX1" t="inlineStr"/>
+      <c r="ABY1" t="inlineStr"/>
+      <c r="ABZ1" t="inlineStr"/>
+      <c r="ACA1" t="inlineStr"/>
+      <c r="ACB1" t="inlineStr"/>
+      <c r="ACC1" t="inlineStr"/>
+      <c r="ACD1" t="inlineStr"/>
+      <c r="ACE1" t="inlineStr"/>
+      <c r="ACF1" t="inlineStr"/>
+      <c r="ACG1" t="inlineStr"/>
+      <c r="ACH1" t="inlineStr"/>
+      <c r="ACI1" t="inlineStr"/>
+      <c r="ACJ1" t="inlineStr"/>
+      <c r="ACK1" t="inlineStr"/>
+      <c r="ACL1" t="inlineStr"/>
+      <c r="ACM1" t="inlineStr"/>
+      <c r="ACN1" t="inlineStr"/>
+      <c r="ACO1" t="inlineStr"/>
+      <c r="ACP1" t="inlineStr"/>
+      <c r="ACQ1" t="inlineStr"/>
+      <c r="ACR1" t="inlineStr"/>
+      <c r="ACS1" t="inlineStr"/>
+      <c r="ACT1" t="inlineStr"/>
+      <c r="ACU1" t="inlineStr"/>
+      <c r="ACV1" t="inlineStr"/>
+      <c r="ACW1" t="inlineStr"/>
+      <c r="ACX1" t="inlineStr"/>
+      <c r="ACY1" t="inlineStr"/>
+      <c r="ACZ1" t="inlineStr"/>
+      <c r="ADA1" t="inlineStr"/>
+      <c r="ADB1" t="inlineStr"/>
+      <c r="ADC1" t="inlineStr"/>
+      <c r="ADD1" t="inlineStr"/>
+      <c r="ADE1" t="inlineStr"/>
+      <c r="ADF1" t="inlineStr"/>
+      <c r="ADG1" t="inlineStr"/>
+      <c r="ADH1" t="inlineStr"/>
+      <c r="ADI1" t="inlineStr"/>
+      <c r="ADJ1" t="inlineStr"/>
+      <c r="ADK1" t="inlineStr"/>
+      <c r="ADL1" t="inlineStr"/>
+      <c r="ADM1" t="inlineStr"/>
+      <c r="ADN1" t="inlineStr"/>
+      <c r="ADO1" t="inlineStr"/>
+      <c r="ADP1" t="inlineStr"/>
+      <c r="ADQ1" t="inlineStr"/>
+      <c r="ADR1" t="inlineStr"/>
+      <c r="ADS1" t="inlineStr"/>
+      <c r="ADT1" t="inlineStr"/>
+      <c r="ADU1" t="inlineStr"/>
+      <c r="ADV1" t="inlineStr"/>
+      <c r="ADW1" t="inlineStr"/>
+      <c r="ADX1" t="inlineStr"/>
+      <c r="ADY1" t="inlineStr"/>
+      <c r="ADZ1" t="inlineStr"/>
+      <c r="AEA1" t="inlineStr"/>
+      <c r="AEB1" t="inlineStr"/>
+      <c r="AEC1" t="inlineStr"/>
+      <c r="AED1" t="inlineStr"/>
+      <c r="AEE1" t="inlineStr"/>
+      <c r="AEF1" t="inlineStr"/>
+      <c r="AEG1" t="inlineStr"/>
+      <c r="AEH1" t="inlineStr"/>
+      <c r="AEI1" t="inlineStr"/>
+      <c r="AEJ1" t="inlineStr"/>
+      <c r="AEK1" t="inlineStr"/>
+      <c r="AEL1" t="inlineStr"/>
+      <c r="AEM1" t="inlineStr"/>
+      <c r="AEN1" t="inlineStr"/>
+      <c r="AEO1" t="inlineStr"/>
+      <c r="AEP1" t="inlineStr"/>
+      <c r="AEQ1" t="inlineStr"/>
+      <c r="AER1" t="inlineStr"/>
+      <c r="AES1" t="inlineStr"/>
+      <c r="AET1" t="inlineStr"/>
+      <c r="AEU1" t="inlineStr"/>
+      <c r="AEV1" t="inlineStr"/>
+      <c r="AEW1" t="inlineStr"/>
+      <c r="AEX1" t="inlineStr"/>
+      <c r="AEY1" t="inlineStr"/>
+      <c r="AEZ1" t="inlineStr"/>
+      <c r="AFA1" t="inlineStr"/>
+      <c r="AFB1" t="inlineStr"/>
+      <c r="AFC1" t="inlineStr"/>
+      <c r="AFD1" t="inlineStr"/>
+      <c r="AFE1" t="inlineStr"/>
+      <c r="AFF1" t="inlineStr"/>
+      <c r="AFG1" t="inlineStr"/>
+      <c r="AFH1" t="inlineStr"/>
+      <c r="AFI1" t="inlineStr"/>
+      <c r="AFJ1" t="inlineStr"/>
+      <c r="AFK1" t="inlineStr"/>
+      <c r="AFL1" t="inlineStr"/>
+      <c r="AFM1" t="inlineStr"/>
+      <c r="AFN1" t="inlineStr"/>
+      <c r="AFO1" t="inlineStr"/>
+      <c r="AFP1" t="inlineStr"/>
+      <c r="AFQ1" t="inlineStr"/>
+      <c r="AFR1" t="inlineStr"/>
+      <c r="AFS1" t="inlineStr"/>
+      <c r="AFT1" t="inlineStr"/>
+      <c r="AFU1" t="inlineStr"/>
+      <c r="AFV1" t="inlineStr"/>
+      <c r="AFW1" t="inlineStr"/>
+      <c r="AFX1" t="inlineStr"/>
+      <c r="AFY1" t="inlineStr"/>
+      <c r="AFZ1" t="inlineStr"/>
+      <c r="AGA1" t="inlineStr"/>
+      <c r="AGB1" t="inlineStr"/>
+      <c r="AGC1" t="inlineStr"/>
+      <c r="AGD1" t="inlineStr"/>
+      <c r="AGE1" t="inlineStr"/>
+      <c r="AGF1" t="inlineStr"/>
+      <c r="AGG1" t="inlineStr"/>
+      <c r="AGH1" t="inlineStr"/>
+      <c r="AGI1" t="inlineStr"/>
+      <c r="AGJ1" t="inlineStr"/>
+      <c r="AGK1" t="inlineStr"/>
+      <c r="AGL1" t="inlineStr"/>
+      <c r="AGM1" t="inlineStr"/>
+      <c r="AGN1" t="inlineStr"/>
+      <c r="AGO1" t="inlineStr"/>
+      <c r="AGP1" t="inlineStr"/>
+      <c r="AGQ1" t="inlineStr"/>
+      <c r="AGR1" t="inlineStr"/>
+      <c r="AGS1" t="inlineStr"/>
+      <c r="AGT1" t="inlineStr"/>
+      <c r="AGU1" t="inlineStr"/>
+      <c r="AGV1" t="inlineStr"/>
+      <c r="AGW1" t="inlineStr"/>
+      <c r="AGX1" t="inlineStr"/>
+      <c r="AGY1" t="inlineStr"/>
+      <c r="AGZ1" t="inlineStr"/>
+      <c r="AHA1" t="inlineStr"/>
+      <c r="AHB1" t="inlineStr"/>
+      <c r="AHC1" t="inlineStr"/>
+      <c r="AHD1" t="inlineStr"/>
+      <c r="AHE1" t="inlineStr"/>
+      <c r="AHF1" t="inlineStr"/>
+      <c r="AHG1" t="inlineStr"/>
+      <c r="AHH1" t="inlineStr"/>
+      <c r="AHI1" t="inlineStr"/>
+      <c r="AHJ1" t="inlineStr"/>
+      <c r="AHK1" t="inlineStr"/>
+      <c r="AHL1" t="inlineStr"/>
+      <c r="AHM1" t="inlineStr"/>
+      <c r="AHN1" t="inlineStr"/>
+      <c r="AHO1" t="inlineStr"/>
+      <c r="AHP1" t="inlineStr"/>
+      <c r="AHQ1" t="inlineStr"/>
+      <c r="AHR1" t="inlineStr"/>
+      <c r="AHS1" t="inlineStr"/>
+      <c r="AHT1" t="inlineStr"/>
+      <c r="AHU1" t="inlineStr"/>
+      <c r="AHV1" t="inlineStr"/>
+      <c r="AHW1" t="inlineStr"/>
+      <c r="AHX1" t="inlineStr"/>
+      <c r="AHY1" t="inlineStr"/>
+      <c r="AHZ1" t="inlineStr"/>
+      <c r="AIA1" t="inlineStr"/>
+      <c r="AIB1" t="inlineStr"/>
+      <c r="AIC1" t="inlineStr"/>
+      <c r="AID1" t="inlineStr"/>
+      <c r="AIE1" t="inlineStr"/>
+      <c r="AIF1" t="inlineStr"/>
+      <c r="AIG1" t="inlineStr"/>
+      <c r="AIH1" t="inlineStr"/>
+      <c r="AII1" t="inlineStr"/>
+      <c r="AIJ1" t="inlineStr"/>
+      <c r="AIK1" t="inlineStr"/>
+      <c r="AIL1" t="inlineStr"/>
+      <c r="AIM1" t="inlineStr"/>
+      <c r="AIN1" t="inlineStr"/>
+      <c r="AIO1" t="inlineStr"/>
+      <c r="AIP1" t="inlineStr"/>
+      <c r="AIQ1" t="inlineStr"/>
+      <c r="AIR1" t="inlineStr"/>
+      <c r="AIS1" t="inlineStr"/>
+      <c r="AIT1" t="inlineStr"/>
+      <c r="AIU1" t="inlineStr"/>
+      <c r="AIV1" t="inlineStr"/>
+      <c r="AIW1" t="inlineStr"/>
+      <c r="AIX1" t="inlineStr"/>
+      <c r="AIY1" t="inlineStr"/>
+      <c r="AIZ1" t="inlineStr"/>
+      <c r="AJA1" t="inlineStr"/>
+      <c r="AJB1" t="inlineStr"/>
+      <c r="AJC1" t="inlineStr"/>
+      <c r="AJD1" t="inlineStr"/>
+      <c r="AJE1" t="inlineStr"/>
+      <c r="AJF1" t="inlineStr"/>
+      <c r="AJG1" t="inlineStr"/>
+      <c r="AJH1" t="inlineStr"/>
+      <c r="AJI1" t="inlineStr"/>
+      <c r="AJJ1" t="inlineStr"/>
+      <c r="AJK1" t="inlineStr"/>
+      <c r="AJL1" t="inlineStr"/>
+      <c r="AJM1" t="inlineStr"/>
+      <c r="AJN1" t="inlineStr"/>
+      <c r="AJO1" t="inlineStr"/>
+      <c r="AJP1" t="inlineStr"/>
+      <c r="AJQ1" t="inlineStr"/>
+      <c r="AJR1" t="inlineStr"/>
+      <c r="AJS1" t="inlineStr"/>
+      <c r="AJT1" t="inlineStr"/>
+      <c r="AJU1" t="inlineStr"/>
+      <c r="AJV1" t="inlineStr"/>
+      <c r="AJW1" t="inlineStr"/>
+      <c r="AJX1" t="inlineStr"/>
+      <c r="AJY1" t="inlineStr"/>
+      <c r="AJZ1" t="inlineStr"/>
+      <c r="AKA1" t="inlineStr"/>
+      <c r="AKB1" t="inlineStr"/>
+      <c r="AKC1" t="inlineStr"/>
+      <c r="AKD1" t="inlineStr"/>
+      <c r="AKE1" t="inlineStr"/>
+      <c r="AKF1" t="inlineStr"/>
+      <c r="AKG1" t="inlineStr"/>
+      <c r="AKH1" t="inlineStr"/>
+      <c r="AKI1" t="inlineStr"/>
+      <c r="AKJ1" t="inlineStr"/>
+      <c r="AKK1" t="inlineStr"/>
+      <c r="AKL1" t="inlineStr"/>
+      <c r="AKM1" t="inlineStr"/>
+      <c r="AKN1" t="inlineStr"/>
+      <c r="AKO1" t="inlineStr"/>
+      <c r="AKP1" t="inlineStr"/>
+      <c r="AKQ1" t="inlineStr"/>
+      <c r="AKR1" t="inlineStr"/>
+      <c r="AKS1" t="inlineStr"/>
+      <c r="AKT1" t="inlineStr"/>
+      <c r="AKU1" t="inlineStr"/>
+      <c r="AKV1" t="inlineStr"/>
+      <c r="AKW1" t="inlineStr"/>
+      <c r="AKX1" t="inlineStr"/>
+      <c r="AKY1" t="inlineStr"/>
+      <c r="AKZ1" t="inlineStr"/>
+      <c r="ALA1" t="inlineStr"/>
+      <c r="ALB1" t="inlineStr"/>
+      <c r="ALC1" t="inlineStr"/>
+      <c r="ALD1" t="inlineStr"/>
+      <c r="ALE1" t="inlineStr"/>
+      <c r="ALF1" t="inlineStr"/>
+      <c r="ALG1" t="inlineStr"/>
+      <c r="ALH1" t="inlineStr"/>
+      <c r="ALI1" t="inlineStr"/>
+      <c r="ALJ1" t="inlineStr"/>
+      <c r="ALK1" t="inlineStr"/>
+      <c r="ALL1" t="inlineStr"/>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>988896</v>
+      </c>
+      <c r="B2" t="n">
+        <v>27556</v>
+      </c>
+      <c r="C2" t="n">
+        <v>725973</v>
+      </c>
+      <c r="D2" t="n">
+        <v>99596</v>
+      </c>
+      <c r="E2" t="n">
+        <v>455119</v>
+      </c>
+      <c r="F2" t="n">
+        <v>699732</v>
+      </c>
+      <c r="G2" t="n">
+        <v>1121078</v>
+      </c>
+      <c r="H2" t="n">
+        <v>6125</v>
+      </c>
+      <c r="I2" t="n">
+        <v>577014</v>
+      </c>
+      <c r="J2" t="n">
+        <v>460698</v>
+      </c>
+      <c r="K2" t="n">
+        <v>27310</v>
+      </c>
+      <c r="L2" t="n">
+        <v>569134</v>
+      </c>
+      <c r="M2" t="n">
+        <v>229841</v>
+      </c>
+      <c r="N2" t="n">
+        <v>151504</v>
+      </c>
+      <c r="O2" t="n">
+        <v>923182</v>
+      </c>
+      <c r="P2" t="n">
+        <v>1021630</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>759951</v>
+      </c>
+      <c r="R2" t="n">
+        <v>140664</v>
+      </c>
+      <c r="S2" t="n">
+        <v>650189</v>
+      </c>
+      <c r="T2" t="n">
+        <v>1116665</v>
+      </c>
+      <c r="U2" t="n">
+        <v>179406</v>
+      </c>
+      <c r="V2" t="n">
+        <v>1095882</v>
+      </c>
+      <c r="W2" t="n">
+        <v>1071102</v>
+      </c>
+      <c r="X2" t="n">
+        <v>1117233</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>596689</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>1101068</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>440421</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>1017492</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>1084219</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>175722</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>418243</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>1038879</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>346495</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>849485</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>383233</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>551858</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>20684</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>928092</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>257655</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>499661</v>
+      </c>
+      <c r="AO2" t="n">
+        <v>842345</v>
+      </c>
+      <c r="AP2" t="n">
+        <v>114721</v>
+      </c>
+      <c r="AQ2" t="n">
+        <v>612567</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>4773</v>
+      </c>
+      <c r="AS2" t="n">
+        <v>11874</v>
+      </c>
+      <c r="AT2" t="n">
+        <v>303773</v>
+      </c>
+      <c r="AU2" t="n">
+        <v>1027059</v>
+      </c>
+      <c r="AV2" t="n">
+        <v>4484</v>
+      </c>
+      <c r="AW2" t="n">
+        <v>824593</v>
+      </c>
+      <c r="AX2" t="n">
+        <v>175285</v>
+      </c>
+      <c r="AY2" t="n">
+        <v>541124</v>
+      </c>
+      <c r="AZ2" t="n">
+        <v>342351</v>
+      </c>
+      <c r="BA2" t="n">
+        <v>1188642</v>
+      </c>
+      <c r="BB2" t="n">
+        <v>460651</v>
+      </c>
+      <c r="BC2" t="n">
+        <v>964101</v>
+      </c>
+      <c r="BD2" t="n">
+        <v>226521</v>
+      </c>
+      <c r="BE2" t="n">
+        <v>73581</v>
+      </c>
+      <c r="BF2" t="n">
+        <v>802395</v>
+      </c>
+      <c r="BG2" t="n">
+        <v>919456</v>
+      </c>
+      <c r="BH2" t="n">
+        <v>525274</v>
+      </c>
+      <c r="BI2" t="n">
+        <v>496907</v>
+      </c>
+      <c r="BJ2" t="n">
+        <v>1011639</v>
+      </c>
+      <c r="BK2" t="n">
+        <v>806373</v>
+      </c>
+      <c r="BL2" t="n">
+        <v>191605</v>
+      </c>
+      <c r="BM2" t="n">
+        <v>323207</v>
+      </c>
+      <c r="BN2" t="n">
+        <v>343032</v>
+      </c>
+      <c r="BO2" t="n">
+        <v>346073</v>
+      </c>
+      <c r="BP2" t="n">
+        <v>809605</v>
+      </c>
+      <c r="BQ2" t="n">
+        <v>354342</v>
+      </c>
+      <c r="BR2" t="n">
+        <v>647542</v>
+      </c>
+      <c r="BS2" t="n">
+        <v>1060</v>
+      </c>
+      <c r="BT2" t="n">
+        <v>1111179</v>
+      </c>
+      <c r="BU2" t="n">
+        <v>192183</v>
+      </c>
+      <c r="BV2" t="n">
+        <v>79235</v>
+      </c>
+      <c r="BW2" t="n">
+        <v>4337</v>
+      </c>
+      <c r="BX2" t="n">
+        <v>1048914</v>
+      </c>
+      <c r="BY2" t="n">
+        <v>542125</v>
+      </c>
+      <c r="BZ2" t="n">
+        <v>877156</v>
+      </c>
+      <c r="CA2" t="n">
+        <v>208717</v>
+      </c>
+      <c r="CB2" t="n">
+        <v>747326</v>
+      </c>
+      <c r="CC2" t="n">
+        <v>703044</v>
+      </c>
+      <c r="CD2" t="n">
+        <v>376361</v>
+      </c>
+      <c r="CE2" t="n">
+        <v>205361</v>
+      </c>
+      <c r="CF2" t="n">
+        <v>29242</v>
+      </c>
+      <c r="CG2" t="n">
+        <v>539062</v>
+      </c>
+      <c r="CH2" t="n">
+        <v>674792</v>
+      </c>
+      <c r="CI2" t="n">
+        <v>777975</v>
+      </c>
+      <c r="CJ2" t="n">
+        <v>477564</v>
+      </c>
+      <c r="CK2" t="n">
+        <v>673150</v>
+      </c>
+      <c r="CL2" t="n">
+        <v>1005299</v>
+      </c>
+      <c r="CM2" t="n">
+        <v>921494</v>
+      </c>
+      <c r="CN2" t="n">
+        <v>1211496</v>
+      </c>
+      <c r="CO2" t="n">
+        <v>737950</v>
+      </c>
+      <c r="CP2" t="n">
+        <v>875321</v>
+      </c>
+      <c r="CQ2" t="n">
+        <v>1076584</v>
+      </c>
+      <c r="CR2" t="n">
+        <v>887349</v>
+      </c>
+      <c r="CS2" t="n">
+        <v>266035</v>
+      </c>
+      <c r="CT2" t="n">
+        <v>972478</v>
+      </c>
+      <c r="CU2" t="n">
+        <v>770002</v>
+      </c>
+      <c r="CV2" t="n">
+        <v>1209862</v>
+      </c>
+      <c r="CW2" t="n">
+        <v>511266</v>
+      </c>
+      <c r="CX2" t="n">
+        <v>784594</v>
+      </c>
+      <c r="CY2" t="n">
+        <v>961107</v>
+      </c>
+      <c r="CZ2" t="n">
+        <v>907904</v>
+      </c>
+      <c r="DA2" t="n">
+        <v>953790</v>
+      </c>
+      <c r="DB2" t="n">
+        <v>295018</v>
+      </c>
+      <c r="DC2" t="n">
+        <v>528766</v>
+      </c>
+      <c r="DD2" t="n">
+        <v>754744</v>
+      </c>
+      <c r="DE2" t="n">
+        <v>569752</v>
+      </c>
+      <c r="DF2" t="n">
+        <v>316943</v>
+      </c>
+      <c r="DG2" t="n">
+        <v>1155898</v>
+      </c>
+      <c r="DH2" t="n">
+        <v>815415</v>
+      </c>
+      <c r="DI2" t="n">
+        <v>266155</v>
+      </c>
+      <c r="DJ2" t="n">
+        <v>678869</v>
+      </c>
+      <c r="DK2" t="n">
+        <v>482767</v>
+      </c>
+      <c r="DL2" t="n">
+        <v>963325</v>
+      </c>
+      <c r="DM2" t="n">
+        <v>662324</v>
+      </c>
+      <c r="DN2" t="n">
+        <v>831668</v>
+      </c>
+      <c r="DO2" t="n">
+        <v>358362</v>
+      </c>
+      <c r="DP2" t="n">
+        <v>193801</v>
+      </c>
+      <c r="DQ2" t="n">
+        <v>763992</v>
+      </c>
+      <c r="DR2" t="n">
+        <v>698115</v>
+      </c>
+      <c r="DS2" t="n">
+        <v>1136683</v>
+      </c>
+      <c r="DT2" t="n">
+        <v>741431</v>
+      </c>
+      <c r="DU2" t="n">
+        <v>407820</v>
+      </c>
+      <c r="DV2" t="n">
+        <v>1162806</v>
+      </c>
+      <c r="DW2" t="n">
+        <v>458727</v>
+      </c>
+      <c r="DX2" t="n">
+        <v>796397</v>
+      </c>
+      <c r="DY2" t="n">
+        <v>351081</v>
+      </c>
+      <c r="DZ2" t="n">
+        <v>1110236</v>
+      </c>
+      <c r="EA2" t="n">
+        <v>976399</v>
+      </c>
+      <c r="EB2" t="n">
+        <v>921385</v>
+      </c>
+      <c r="EC2" t="n">
+        <v>13999</v>
+      </c>
+      <c r="ED2" t="n">
+        <v>180010</v>
+      </c>
+      <c r="EE2" t="n">
+        <v>333101</v>
+      </c>
+      <c r="EF2" t="n">
+        <v>312003</v>
+      </c>
+      <c r="EG2" t="n">
+        <v>895416</v>
+      </c>
+      <c r="EH2" t="n">
+        <v>641023</v>
+      </c>
+      <c r="EI2" t="n">
+        <v>594902</v>
+      </c>
+      <c r="EJ2" t="n">
+        <v>964663</v>
+      </c>
+      <c r="EK2" t="n">
+        <v>250196</v>
+      </c>
+      <c r="EL2" t="n">
+        <v>57269</v>
+      </c>
+      <c r="EM2" t="n">
+        <v>512647</v>
+      </c>
+      <c r="EN2" t="n">
+        <v>558125</v>
+      </c>
+      <c r="EO2" t="n">
+        <v>584102</v>
+      </c>
+      <c r="EP2" t="n">
+        <v>86176</v>
+      </c>
+      <c r="EQ2" t="n">
+        <v>1166518</v>
+      </c>
+      <c r="ER2" t="n">
+        <v>689809</v>
+      </c>
+      <c r="ES2" t="n">
+        <v>429897</v>
+      </c>
+      <c r="ET2" t="n">
+        <v>186615</v>
+      </c>
+      <c r="EU2" t="n">
+        <v>1231764</v>
+      </c>
+      <c r="EV2" t="n">
+        <v>215920</v>
+      </c>
+      <c r="EW2" t="n">
+        <v>451971</v>
+      </c>
+      <c r="EX2" t="n">
+        <v>675727</v>
+      </c>
+      <c r="EY2" t="n">
+        <v>626510</v>
+      </c>
+      <c r="EZ2" t="n">
+        <v>615130</v>
+      </c>
+      <c r="FA2" t="n">
+        <v>633768</v>
+      </c>
+      <c r="FB2" t="n">
+        <v>288651</v>
+      </c>
+      <c r="FC2" t="n">
+        <v>552710</v>
+      </c>
+      <c r="FD2" t="n">
+        <v>1138460</v>
+      </c>
+      <c r="FE2" t="n">
+        <v>841224</v>
+      </c>
+      <c r="FF2" t="n">
+        <v>104532</v>
+      </c>
+      <c r="FG2" t="n">
+        <v>1045185</v>
+      </c>
+      <c r="FH2" t="n">
+        <v>803419</v>
+      </c>
+      <c r="FI2" t="n">
+        <v>813507</v>
+      </c>
+      <c r="FJ2" t="n">
+        <v>352616</v>
+      </c>
+      <c r="FK2" t="n">
+        <v>136171</v>
+      </c>
+      <c r="FL2" t="n">
+        <v>239416</v>
+      </c>
+      <c r="FM2" t="n">
+        <v>440164</v>
+      </c>
+      <c r="FN2" t="n">
+        <v>172299</v>
+      </c>
+      <c r="FO2" t="n">
+        <v>1233391</v>
+      </c>
+      <c r="FP2" t="n">
+        <v>223662</v>
+      </c>
+      <c r="FQ2" t="n">
+        <v>33869</v>
+      </c>
+      <c r="FR2" t="n">
+        <v>702928</v>
+      </c>
+      <c r="FS2" t="n">
+        <v>163250</v>
+      </c>
+      <c r="FT2" t="n">
+        <v>632352</v>
+      </c>
+      <c r="FU2" t="n">
+        <v>131887</v>
+      </c>
+      <c r="FV2" t="n">
+        <v>586290</v>
+      </c>
+      <c r="FW2" t="n">
+        <v>866880</v>
+      </c>
+      <c r="FX2" t="n">
+        <v>503330</v>
+      </c>
+      <c r="FY2" t="n">
+        <v>913511</v>
+      </c>
+      <c r="FZ2" t="n">
+        <v>1128538</v>
+      </c>
+      <c r="GA2" t="n">
+        <v>98126</v>
+      </c>
+      <c r="GB2" t="n">
+        <v>279329</v>
+      </c>
+      <c r="GC2" t="n">
+        <v>366813</v>
+      </c>
+      <c r="GD2" t="n">
+        <v>448670</v>
+      </c>
+      <c r="GE2" t="n">
+        <v>1066731</v>
+      </c>
+      <c r="GF2" t="n">
+        <v>897116</v>
+      </c>
+      <c r="GG2" t="n">
+        <v>565781</v>
+      </c>
+      <c r="GH2" t="n">
+        <v>1134636</v>
+      </c>
+      <c r="GI2" t="n">
+        <v>474024</v>
+      </c>
+      <c r="GJ2" t="n">
+        <v>188139</v>
+      </c>
+      <c r="GK2" t="n">
+        <v>736012</v>
+      </c>
+      <c r="GL2" t="n">
+        <v>300109</v>
+      </c>
+      <c r="GM2" t="n">
+        <v>1225142</v>
+      </c>
+      <c r="GN2" t="n">
+        <v>529156</v>
+      </c>
+      <c r="GO2" t="n">
+        <v>42309</v>
+      </c>
+      <c r="GP2" t="n">
+        <v>602149</v>
+      </c>
+      <c r="GQ2" t="n">
+        <v>285208</v>
+      </c>
+      <c r="GR2" t="n">
+        <v>291377</v>
+      </c>
+      <c r="GS2" t="n">
+        <v>1076016</v>
+      </c>
+      <c r="GT2" t="n">
+        <v>914630</v>
+      </c>
+      <c r="GU2" t="n">
+        <v>443546</v>
+      </c>
+      <c r="GV2" t="n">
+        <v>941783</v>
+      </c>
+      <c r="GW2" t="n">
+        <v>437141</v>
+      </c>
+      <c r="GX2" t="n">
+        <v>554356</v>
+      </c>
+      <c r="GY2" t="n">
+        <v>913394</v>
+      </c>
+      <c r="GZ2" t="n">
+        <v>457949</v>
+      </c>
+      <c r="HA2" t="n">
+        <v>858935</v>
+      </c>
+      <c r="HB2" t="n">
+        <v>18718</v>
+      </c>
+      <c r="HC2" t="n">
+        <v>579368</v>
+      </c>
+      <c r="HD2" t="n">
+        <v>969462</v>
+      </c>
+      <c r="HE2" t="n">
+        <v>898278</v>
+      </c>
+      <c r="HF2" t="n">
+        <v>103755</v>
+      </c>
+      <c r="HG2" t="n">
+        <v>447865</v>
+      </c>
+      <c r="HH2" t="n">
+        <v>1198076</v>
+      </c>
+      <c r="HI2" t="n">
+        <v>1006402</v>
+      </c>
+      <c r="HJ2" t="n">
+        <v>932858</v>
+      </c>
+      <c r="HK2" t="n">
+        <v>119413</v>
+      </c>
+      <c r="HL2" t="n">
+        <v>72838</v>
+      </c>
+      <c r="HM2" t="n">
+        <v>388697</v>
+      </c>
+      <c r="HN2" t="n">
+        <v>526130</v>
+      </c>
+      <c r="HO2" t="n">
+        <v>956088</v>
+      </c>
+      <c r="HP2" t="n">
+        <v>574282</v>
+      </c>
+      <c r="HQ2" t="n">
+        <v>45946</v>
+      </c>
+      <c r="HR2" t="n">
+        <v>514584</v>
+      </c>
+      <c r="HS2" t="n">
+        <v>319165</v>
+      </c>
+      <c r="HT2" t="n">
+        <v>1172055</v>
+      </c>
+      <c r="HU2" t="n">
+        <v>371480</v>
+      </c>
+      <c r="HV2" t="n">
+        <v>776613</v>
+      </c>
+      <c r="HW2" t="n">
+        <v>336012</v>
+      </c>
+      <c r="HX2" t="n">
+        <v>959774</v>
+      </c>
+      <c r="HY2" t="n">
+        <v>61020</v>
+      </c>
+      <c r="HZ2" t="n">
+        <v>218313</v>
+      </c>
+      <c r="IA2" t="n">
+        <v>1046818</v>
+      </c>
+      <c r="IB2" t="n">
+        <v>989938</v>
+      </c>
+      <c r="IC2" t="n">
+        <v>862338</v>
+      </c>
+      <c r="ID2" t="n">
+        <v>683604</v>
+      </c>
+      <c r="IE2" t="n">
+        <v>1014003</v>
+      </c>
+      <c r="IF2" t="n">
+        <v>147447</v>
+      </c>
+      <c r="IG2" t="n">
+        <v>942</v>
+      </c>
+      <c r="IH2" t="n">
+        <v>930906</v>
+      </c>
+      <c r="II2" t="n">
+        <v>280254</v>
+      </c>
+      <c r="IJ2" t="n">
+        <v>874780</v>
+      </c>
+      <c r="IK2" t="n">
+        <v>1165400</v>
+      </c>
+      <c r="IL2" t="n">
+        <v>1004125</v>
+      </c>
+      <c r="IM2" t="n">
+        <v>244729</v>
+      </c>
+      <c r="IN2" t="n">
+        <v>121108</v>
+      </c>
+      <c r="IO2" t="n">
+        <v>367464</v>
+      </c>
+      <c r="IP2" t="n">
+        <v>748306</v>
+      </c>
+      <c r="IQ2" t="n">
+        <v>1093412</v>
+      </c>
+      <c r="IR2" t="n">
+        <v>809865</v>
+      </c>
+      <c r="IS2" t="n">
+        <v>1027837</v>
+      </c>
+      <c r="IT2" t="n">
+        <v>170598</v>
+      </c>
+      <c r="IU2" t="n">
+        <v>885236</v>
+      </c>
+      <c r="IV2" t="n">
+        <v>1144121</v>
+      </c>
+      <c r="IW2" t="n">
+        <v>406120</v>
+      </c>
+      <c r="IX2" t="n">
+        <v>106687</v>
+      </c>
+      <c r="IY2" t="n">
+        <v>472532</v>
+      </c>
+      <c r="IZ2" t="n">
+        <v>11097</v>
+      </c>
+      <c r="JA2" t="n">
+        <v>298316</v>
+      </c>
+      <c r="JB2" t="n">
+        <v>96245</v>
+      </c>
+      <c r="JC2" t="n">
+        <v>1067966</v>
+      </c>
+      <c r="JD2" t="n">
+        <v>710531</v>
+      </c>
+      <c r="JE2" t="n">
+        <v>218235</v>
+      </c>
+      <c r="JF2" t="n">
+        <v>167870</v>
+      </c>
+      <c r="JG2" t="n">
+        <v>226356</v>
+      </c>
+      <c r="JH2" t="n">
+        <v>162330</v>
+      </c>
+      <c r="JI2" t="n">
+        <v>377754</v>
+      </c>
+      <c r="JJ2" t="n">
+        <v>974716</v>
+      </c>
+      <c r="JK2" t="n">
+        <v>1209955</v>
+      </c>
+      <c r="JL2" t="n">
+        <v>542354</v>
+      </c>
+      <c r="JM2" t="n">
+        <v>64088</v>
+      </c>
+      <c r="JN2" t="n">
+        <v>981955</v>
+      </c>
+      <c r="JO2" t="n">
+        <v>722473</v>
+      </c>
+      <c r="JP2" t="n">
+        <v>563215</v>
+      </c>
+      <c r="JQ2" t="n">
+        <v>751730</v>
+      </c>
+      <c r="JR2" t="n">
+        <v>95150</v>
+      </c>
+      <c r="JS2" t="n">
+        <v>1105311</v>
+      </c>
+      <c r="JT2" t="n">
+        <v>1193545</v>
+      </c>
+      <c r="JU2" t="n">
+        <v>666870</v>
+      </c>
+      <c r="JV2" t="n">
+        <v>447064</v>
+      </c>
+      <c r="JW2" t="n">
+        <v>238896</v>
+      </c>
+      <c r="JX2" t="n">
+        <v>1030258</v>
+      </c>
+      <c r="JY2" t="n">
+        <v>1089479</v>
+      </c>
+      <c r="JZ2" t="n">
+        <v>436109</v>
+      </c>
+      <c r="KA2" t="n">
+        <v>488436</v>
+      </c>
+      <c r="KB2" t="n">
+        <v>242493</v>
+      </c>
+      <c r="KC2" t="n">
+        <v>16694</v>
+      </c>
+      <c r="KD2" t="n">
+        <v>283135</v>
+      </c>
+      <c r="KE2" t="n">
+        <v>1124241</v>
+      </c>
+      <c r="KF2" t="n">
+        <v>306899</v>
+      </c>
+      <c r="KG2" t="n">
+        <v>434259</v>
+      </c>
+      <c r="KH2" t="n">
+        <v>521685</v>
+      </c>
+      <c r="KI2" t="n">
+        <v>709018</v>
+      </c>
+      <c r="KJ2" t="n">
+        <v>1170551</v>
+      </c>
+      <c r="KK2" t="n">
+        <v>880675</v>
+      </c>
+      <c r="KL2" t="n">
+        <v>1043438</v>
+      </c>
+      <c r="KM2" t="n">
+        <v>1169794</v>
+      </c>
+      <c r="KN2" t="n">
+        <v>1021084</v>
+      </c>
+      <c r="KO2" t="n">
+        <v>1024373</v>
+      </c>
+      <c r="KP2" t="n">
+        <v>60467</v>
+      </c>
+      <c r="KQ2" t="n">
+        <v>549204</v>
+      </c>
+      <c r="KR2" t="n">
+        <v>425086</v>
+      </c>
+      <c r="KS2" t="n">
+        <v>583500</v>
+      </c>
+      <c r="KT2" t="n">
+        <v>1009998</v>
+      </c>
+      <c r="KU2" t="n">
+        <v>198779</v>
+      </c>
+      <c r="KV2" t="n">
+        <v>323234</v>
+      </c>
+      <c r="KW2" t="n">
+        <v>628047</v>
+      </c>
+      <c r="KX2" t="n">
+        <v>859843</v>
+      </c>
+      <c r="KY2" t="n">
+        <v>1097803</v>
+      </c>
+      <c r="KZ2" t="n">
+        <v>1038397</v>
+      </c>
+      <c r="LA2" t="n">
+        <v>38395</v>
+      </c>
+      <c r="LB2" t="n">
+        <v>691181</v>
+      </c>
+      <c r="LC2" t="n">
+        <v>505644</v>
+      </c>
+      <c r="LD2" t="n">
+        <v>947352</v>
+      </c>
+      <c r="LE2" t="n">
+        <v>658320</v>
+      </c>
+      <c r="LF2" t="n">
+        <v>857431</v>
+      </c>
+      <c r="LG2" t="n">
+        <v>851033</v>
+      </c>
+      <c r="LH2" t="n">
+        <v>413329</v>
+      </c>
+      <c r="LI2" t="n">
+        <v>1033171</v>
+      </c>
+      <c r="LJ2" t="n">
+        <v>978538</v>
+      </c>
+      <c r="LK2" t="n">
+        <v>1024287</v>
+      </c>
+      <c r="LL2" t="n">
+        <v>754055</v>
+      </c>
+      <c r="LM2" t="n">
+        <v>530647</v>
+      </c>
+      <c r="LN2" t="n">
+        <v>33841</v>
+      </c>
+      <c r="LO2" t="n">
+        <v>491495</v>
+      </c>
+      <c r="LP2" t="n">
+        <v>491299</v>
+      </c>
+      <c r="LQ2" t="n">
+        <v>769927</v>
+      </c>
+      <c r="LR2" t="n">
+        <v>37224</v>
+      </c>
+      <c r="LS2" t="n">
+        <v>484409</v>
+      </c>
+      <c r="LT2" t="n">
+        <v>177328</v>
+      </c>
+      <c r="LU2" t="n">
+        <v>1130189</v>
+      </c>
+      <c r="LV2" t="n">
+        <v>207050</v>
+      </c>
+      <c r="LW2" t="n">
+        <v>756037</v>
+      </c>
+      <c r="LX2" t="n">
+        <v>87403</v>
+      </c>
+      <c r="LY2" t="n">
+        <v>646572</v>
+      </c>
+      <c r="LZ2" t="n">
+        <v>320805</v>
+      </c>
+      <c r="MA2" t="n">
+        <v>413524</v>
+      </c>
+      <c r="MB2" t="n">
+        <v>392488</v>
+      </c>
+      <c r="MC2" t="n">
+        <v>255153</v>
+      </c>
+      <c r="MD2" t="n">
+        <v>387448</v>
+      </c>
+      <c r="ME2" t="n">
+        <v>81801</v>
+      </c>
+      <c r="MF2" t="n">
+        <v>514731</v>
+      </c>
+      <c r="MG2" t="n">
+        <v>655562</v>
+      </c>
+      <c r="MH2" t="n">
+        <v>944555</v>
+      </c>
+      <c r="MI2" t="n">
+        <v>544470</v>
+      </c>
+      <c r="MJ2" t="n">
+        <v>252832</v>
+      </c>
+      <c r="MK2" t="n">
+        <v>719438</v>
+      </c>
+      <c r="ML2" t="n">
+        <v>1049895</v>
+      </c>
+      <c r="MM2" t="n">
+        <v>546456</v>
+      </c>
+      <c r="MN2" t="n">
+        <v>1125334</v>
+      </c>
+      <c r="MO2" t="n">
+        <v>143397</v>
+      </c>
+      <c r="MP2" t="n">
+        <v>503132</v>
+      </c>
+      <c r="MQ2" t="n">
+        <v>854412</v>
+      </c>
+      <c r="MR2" t="n">
+        <v>37440</v>
+      </c>
+      <c r="MS2" t="n">
+        <v>312001</v>
+      </c>
+      <c r="MT2" t="n">
+        <v>334671</v>
+      </c>
+      <c r="MU2" t="n">
+        <v>17587</v>
+      </c>
+      <c r="MV2" t="n">
+        <v>427609</v>
+      </c>
+      <c r="MW2" t="n">
+        <v>684517</v>
+      </c>
+      <c r="MX2" t="n">
+        <v>162609</v>
+      </c>
+      <c r="MY2" t="n">
+        <v>289193</v>
+      </c>
+      <c r="MZ2" t="n">
+        <v>589702</v>
+      </c>
+      <c r="NA2" t="n">
+        <v>1219304</v>
+      </c>
+      <c r="NB2" t="n">
+        <v>105960</v>
+      </c>
+      <c r="NC2" t="n">
+        <v>1117309</v>
+      </c>
+      <c r="ND2" t="n">
+        <v>719946</v>
+      </c>
+      <c r="NE2" t="n">
+        <v>212290</v>
+      </c>
+      <c r="NF2" t="n">
+        <v>346701</v>
+      </c>
+      <c r="NG2" t="n">
+        <v>66221</v>
+      </c>
+      <c r="NH2" t="n">
+        <v>507611</v>
+      </c>
+      <c r="NI2" t="n">
+        <v>1037601</v>
+      </c>
+      <c r="NJ2" t="n">
+        <v>420072</v>
+      </c>
+      <c r="NK2" t="n">
+        <v>467246</v>
+      </c>
+      <c r="NL2" t="n">
+        <v>272416</v>
+      </c>
+      <c r="NM2" t="n">
+        <v>283944</v>
+      </c>
+      <c r="NN2" t="n">
+        <v>505312</v>
+      </c>
+      <c r="NO2" t="n">
+        <v>542950</v>
+      </c>
+      <c r="NP2" t="n">
+        <v>155790</v>
+      </c>
+      <c r="NQ2" t="n">
+        <v>212775</v>
+      </c>
+      <c r="NR2" t="n">
+        <v>1082369</v>
+      </c>
+      <c r="NS2" t="n">
+        <v>84099</v>
+      </c>
+      <c r="NT2" t="n">
+        <v>804121</v>
+      </c>
+      <c r="NU2" t="n">
+        <v>360196</v>
+      </c>
+      <c r="NV2" t="n">
+        <v>750633</v>
+      </c>
+      <c r="NW2" t="n">
+        <v>77469</v>
+      </c>
+      <c r="NX2" t="n">
+        <v>2339</v>
+      </c>
+      <c r="NY2" t="n">
+        <v>484874</v>
+      </c>
+      <c r="NZ2" t="n">
+        <v>274344</v>
+      </c>
+      <c r="OA2" t="n">
+        <v>620526</v>
+      </c>
+      <c r="OB2" t="n">
+        <v>550512</v>
+      </c>
+      <c r="OC2" t="n">
+        <v>259932</v>
+      </c>
+      <c r="OD2" t="n">
+        <v>41721</v>
+      </c>
+      <c r="OE2" t="n">
+        <v>904387</v>
+      </c>
+      <c r="OF2" t="n">
+        <v>982708</v>
+      </c>
+      <c r="OG2" t="n">
+        <v>69949</v>
+      </c>
+      <c r="OH2" t="n">
+        <v>362119</v>
+      </c>
+      <c r="OI2" t="n">
+        <v>750088</v>
+      </c>
+      <c r="OJ2" t="n">
+        <v>235140</v>
+      </c>
+      <c r="OK2" t="n">
+        <v>987397</v>
+      </c>
+      <c r="OL2" t="n">
+        <v>830006</v>
+      </c>
+      <c r="OM2" t="n">
+        <v>997153</v>
+      </c>
+      <c r="ON2" t="n">
+        <v>269770</v>
+      </c>
+      <c r="OO2" t="n">
+        <v>195872</v>
+      </c>
+      <c r="OP2" t="n">
+        <v>160871</v>
+      </c>
+      <c r="OQ2" t="n">
+        <v>815502</v>
+      </c>
+      <c r="OR2" t="n">
+        <v>1057247</v>
+      </c>
+      <c r="OS2" t="n">
+        <v>641412</v>
+      </c>
+      <c r="OT2" t="n">
+        <v>907822</v>
+      </c>
+      <c r="OU2" t="n">
+        <v>993648</v>
+      </c>
+      <c r="OV2" t="n">
+        <v>43991</v>
+      </c>
+      <c r="OW2" t="n">
+        <v>480399</v>
+      </c>
+      <c r="OX2" t="n">
+        <v>999068</v>
+      </c>
+      <c r="OY2" t="n">
+        <v>188994</v>
+      </c>
+      <c r="OZ2" t="n">
+        <v>870902</v>
+      </c>
+      <c r="PA2" t="n">
+        <v>1085657</v>
+      </c>
+      <c r="PB2" t="n">
+        <v>1146621</v>
+      </c>
+      <c r="PC2" t="n">
+        <v>445960</v>
+      </c>
+      <c r="PD2" t="n">
+        <v>1203129</v>
+      </c>
+      <c r="PE2" t="n">
+        <v>863343</v>
+      </c>
+      <c r="PF2" t="n">
+        <v>1020067</v>
+      </c>
+      <c r="PG2" t="n">
+        <v>202544</v>
+      </c>
+      <c r="PH2" t="n">
+        <v>625371</v>
+      </c>
+      <c r="PI2" t="n">
+        <v>1035327</v>
+      </c>
+      <c r="PJ2" t="n">
+        <v>263628</v>
+      </c>
+      <c r="PK2" t="n">
+        <v>704657</v>
+      </c>
+      <c r="PL2" t="n">
+        <v>556291</v>
+      </c>
+      <c r="PM2" t="n">
+        <v>1139908</v>
+      </c>
+      <c r="PN2" t="n">
+        <v>117</v>
+      </c>
+      <c r="PO2" t="n">
+        <v>535489</v>
+      </c>
+      <c r="PP2" t="n">
+        <v>443117</v>
+      </c>
+      <c r="PQ2" t="n">
+        <v>651772</v>
+      </c>
+      <c r="PR2" t="n">
+        <v>718800</v>
+      </c>
+      <c r="PS2" t="n">
+        <v>766757</v>
+      </c>
+      <c r="PT2" t="n">
+        <v>373047</v>
+      </c>
+      <c r="PU2" t="n">
+        <v>13100</v>
+      </c>
+      <c r="PV2" t="n">
+        <v>638012</v>
+      </c>
+      <c r="PW2" t="n">
+        <v>47326</v>
+      </c>
+      <c r="PX2" t="n">
+        <v>1012328</v>
+      </c>
+      <c r="PY2" t="n">
+        <v>77908</v>
+      </c>
+      <c r="PZ2" t="n">
+        <v>573777</v>
+      </c>
+      <c r="QA2" t="n">
+        <v>48849</v>
+      </c>
+      <c r="QB2" t="n">
+        <v>743094</v>
+      </c>
+      <c r="QC2" t="n">
+        <v>616185</v>
+      </c>
+      <c r="QD2" t="n">
+        <v>558913</v>
+      </c>
+      <c r="QE2" t="n">
+        <v>1152447</v>
+      </c>
+      <c r="QF2" t="n">
+        <v>149190</v>
+      </c>
+      <c r="QG2" t="n">
+        <v>570818</v>
+      </c>
+      <c r="QH2" t="n">
+        <v>449479</v>
+      </c>
+      <c r="QI2" t="n">
+        <v>604158</v>
+      </c>
+      <c r="QJ2" t="n">
+        <v>969549</v>
+      </c>
+      <c r="QK2" t="n">
+        <v>72702</v>
+      </c>
+      <c r="QL2" t="n">
+        <v>526509</v>
+      </c>
+      <c r="QM2" t="n">
+        <v>781444</v>
+      </c>
+      <c r="QN2" t="n">
+        <v>791374</v>
+      </c>
+      <c r="QO2" t="n">
+        <v>464389</v>
+      </c>
+      <c r="QP2" t="n">
+        <v>44800</v>
+      </c>
+      <c r="QQ2" t="n">
+        <v>736705</v>
+      </c>
+      <c r="QR2" t="n">
+        <v>773549</v>
+      </c>
+      <c r="QS2" t="n">
+        <v>1119978</v>
+      </c>
+      <c r="QT2" t="n">
+        <v>1174613</v>
+      </c>
+      <c r="QU2" t="n">
+        <v>1161509</v>
+      </c>
+      <c r="QV2" t="n">
+        <v>795956</v>
+      </c>
+      <c r="QW2" t="n">
+        <v>80492</v>
+      </c>
+      <c r="QX2" t="n">
+        <v>890063</v>
+      </c>
+      <c r="QY2" t="n">
+        <v>571837</v>
+      </c>
+      <c r="QZ2" t="n">
+        <v>1073780</v>
+      </c>
+      <c r="RA2" t="n">
+        <v>115935</v>
+      </c>
+      <c r="RB2" t="n">
+        <v>102020</v>
+      </c>
+      <c r="RC2" t="n">
+        <v>455233</v>
+      </c>
+      <c r="RD2" t="n">
+        <v>292343</v>
+      </c>
+      <c r="RE2" t="n">
+        <v>26501</v>
+      </c>
+      <c r="RF2" t="n">
+        <v>478500</v>
+      </c>
+      <c r="RG2" t="n">
+        <v>793555</v>
+      </c>
+      <c r="RH2" t="n">
+        <v>630319</v>
+      </c>
+      <c r="RI2" t="n">
+        <v>532638</v>
+      </c>
+      <c r="RJ2" t="n">
+        <v>121649</v>
+      </c>
+      <c r="RK2" t="n">
+        <v>1094785</v>
+      </c>
+      <c r="RL2" t="n">
+        <v>1064168</v>
+      </c>
+      <c r="RM2" t="n">
+        <v>506763</v>
+      </c>
+      <c r="RN2" t="n">
+        <v>839036</v>
+      </c>
+      <c r="RO2" t="n">
+        <v>427074</v>
+      </c>
+      <c r="RP2" t="n">
+        <v>958815</v>
+      </c>
+      <c r="RQ2" t="n">
+        <v>318625</v>
+      </c>
+      <c r="RR2" t="n">
+        <v>1118848</v>
+      </c>
+      <c r="RS2" t="n">
+        <v>659026</v>
+      </c>
+      <c r="RT2" t="n">
+        <v>355716</v>
+      </c>
+      <c r="RU2" t="n">
+        <v>148750</v>
+      </c>
+      <c r="RV2" t="n">
+        <v>207455</v>
+      </c>
+      <c r="RW2" t="n">
+        <v>523052</v>
+      </c>
+      <c r="RX2" t="n">
+        <v>409680</v>
+      </c>
+      <c r="RY2" t="n">
+        <v>1099978</v>
+      </c>
+      <c r="RZ2" t="n">
+        <v>944983</v>
+      </c>
+      <c r="SA2" t="n">
+        <v>456349</v>
+      </c>
+      <c r="SB2" t="n">
+        <v>934449</v>
+      </c>
+      <c r="SC2" t="n">
+        <v>734640</v>
+      </c>
+      <c r="SD2" t="n">
+        <v>731855</v>
+      </c>
+      <c r="SE2" t="n">
+        <v>1035407</v>
+      </c>
+      <c r="SF2" t="n">
+        <v>363866</v>
+      </c>
+      <c r="SG2" t="n">
+        <v>581243</v>
+      </c>
+      <c r="SH2" t="n">
+        <v>453436</v>
+      </c>
+      <c r="SI2" t="n">
+        <v>213865</v>
+      </c>
+      <c r="SJ2" t="n">
+        <v>942516</v>
+      </c>
+      <c r="SK2" t="n">
+        <v>157750</v>
+      </c>
+      <c r="SL2" t="n">
+        <v>1012401</v>
+      </c>
+      <c r="SM2" t="n">
+        <v>406078</v>
+      </c>
+      <c r="SN2" t="n">
+        <v>400560</v>
+      </c>
+      <c r="SO2" t="n">
+        <v>501333</v>
+      </c>
+      <c r="SP2" t="n">
+        <v>566301</v>
+      </c>
+      <c r="SQ2" t="n">
+        <v>1176252</v>
+      </c>
+      <c r="SR2" t="n">
+        <v>828718</v>
+      </c>
+      <c r="SS2" t="n">
+        <v>211447</v>
+      </c>
+      <c r="ST2" t="n">
+        <v>341452</v>
+      </c>
+      <c r="SU2" t="n">
+        <v>93954</v>
+      </c>
+      <c r="SV2" t="n">
+        <v>1190723</v>
+      </c>
+      <c r="SW2" t="n">
+        <v>853457</v>
+      </c>
+      <c r="SX2" t="n">
+        <v>1200855</v>
+      </c>
+      <c r="SY2" t="n">
+        <v>655248</v>
+      </c>
+      <c r="SZ2" t="n">
+        <v>1002578</v>
+      </c>
+      <c r="TA2" t="n">
+        <v>150847</v>
+      </c>
+      <c r="TB2" t="n">
+        <v>381611</v>
+      </c>
+      <c r="TC2" t="n">
+        <v>6930</v>
+      </c>
+      <c r="TD2" t="n">
+        <v>111742</v>
+      </c>
+      <c r="TE2" t="n">
+        <v>284857</v>
+      </c>
+      <c r="TF2" t="n">
+        <v>127967</v>
+      </c>
+      <c r="TG2" t="n">
+        <v>715859</v>
+      </c>
+      <c r="TH2" t="n">
+        <v>708611</v>
+      </c>
+      <c r="TI2" t="n">
+        <v>779045</v>
+      </c>
+      <c r="TJ2" t="n">
+        <v>246137</v>
+      </c>
+      <c r="TK2" t="n">
+        <v>598463</v>
+      </c>
+      <c r="TL2" t="n">
+        <v>175178</v>
+      </c>
+      <c r="TM2" t="n">
+        <v>272549</v>
+      </c>
+      <c r="TN2" t="n">
+        <v>375637</v>
+      </c>
+      <c r="TO2" t="n">
+        <v>846200</v>
+      </c>
+      <c r="TP2" t="n">
+        <v>725973</v>
+      </c>
+      <c r="TQ2" t="n">
+        <v>441354</v>
+      </c>
+      <c r="TR2" t="n">
+        <v>463108</v>
+      </c>
+      <c r="TS2" t="n">
+        <v>51227</v>
+      </c>
+      <c r="TT2" t="n">
+        <v>327599</v>
+      </c>
+      <c r="TU2" t="n">
+        <v>207631</v>
+      </c>
+      <c r="TV2" t="n">
+        <v>977032</v>
+      </c>
+      <c r="TW2" t="n">
+        <v>857471</v>
+      </c>
+      <c r="TX2" t="n">
+        <v>290860</v>
+      </c>
+      <c r="TY2" t="n">
+        <v>41880</v>
+      </c>
+      <c r="TZ2" t="n">
+        <v>628476</v>
+      </c>
+      <c r="UA2" t="n">
+        <v>787919</v>
+      </c>
+      <c r="UB2" t="n">
+        <v>308044</v>
+      </c>
+      <c r="UC2" t="n">
+        <v>1051941</v>
+      </c>
+      <c r="UD2" t="n">
+        <v>786453</v>
+      </c>
+      <c r="UE2" t="n">
+        <v>582745</v>
+      </c>
+      <c r="UF2" t="n">
+        <v>250334</v>
+      </c>
+      <c r="UG2" t="n">
+        <v>489453</v>
+      </c>
+      <c r="UH2" t="n">
+        <v>675512</v>
+      </c>
+      <c r="UI2" t="n">
+        <v>765849</v>
+      </c>
+      <c r="UJ2" t="n">
+        <v>321031</v>
+      </c>
+      <c r="UK2" t="n">
+        <v>597996</v>
+      </c>
+      <c r="UL2" t="n">
+        <v>60514</v>
+      </c>
+      <c r="UM2" t="n">
+        <v>53723</v>
+      </c>
+      <c r="UN2" t="n">
+        <v>302466</v>
+      </c>
+      <c r="UO2" t="n">
+        <v>1069619</v>
+      </c>
+      <c r="UP2" t="n">
+        <v>916768</v>
+      </c>
+      <c r="UQ2" t="n">
+        <v>977193</v>
+      </c>
+      <c r="UR2" t="n">
+        <v>950973</v>
+      </c>
+      <c r="US2" t="n">
+        <v>87788</v>
+      </c>
+      <c r="UT2" t="n">
+        <v>868062</v>
+      </c>
+      <c r="UU2" t="n">
+        <v>82695</v>
+      </c>
+      <c r="UV2" t="n">
+        <v>764742</v>
+      </c>
+      <c r="UW2" t="n">
+        <v>239149</v>
+      </c>
+      <c r="UX2" t="n">
+        <v>1063578</v>
+      </c>
+      <c r="UY2" t="n">
+        <v>112259</v>
+      </c>
+      <c r="UZ2" t="n">
+        <v>327832</v>
+      </c>
+      <c r="VA2" t="n">
+        <v>1103384</v>
+      </c>
+      <c r="VB2" t="n">
+        <v>470221</v>
+      </c>
+      <c r="VC2" t="n">
+        <v>221636</v>
+      </c>
+      <c r="VD2" t="n">
+        <v>1126520</v>
+      </c>
+      <c r="VE2" t="n">
+        <v>468385</v>
+      </c>
+      <c r="VF2" t="n">
+        <v>1017417</v>
+      </c>
+      <c r="VG2" t="n">
+        <v>653799</v>
+      </c>
+      <c r="VH2" t="n">
+        <v>118103</v>
+      </c>
+      <c r="VI2" t="n">
+        <v>1159647</v>
+      </c>
+      <c r="VJ2" t="n">
+        <v>149721</v>
+      </c>
+      <c r="VK2" t="n">
+        <v>30734</v>
+      </c>
+      <c r="VL2" t="n">
+        <v>384752</v>
+      </c>
+      <c r="VM2" t="n">
+        <v>1061691</v>
+      </c>
+      <c r="VN2" t="n">
+        <v>136686</v>
+      </c>
+      <c r="VO2" t="n">
+        <v>707828</v>
+      </c>
+      <c r="VP2" t="n">
+        <v>1157058</v>
+      </c>
+      <c r="VQ2" t="n">
+        <v>830267</v>
+      </c>
+      <c r="VR2" t="n">
+        <v>1054718</v>
+      </c>
+      <c r="VS2" t="n">
+        <v>132011</v>
+      </c>
+      <c r="VT2" t="n">
+        <v>1218074</v>
+      </c>
+      <c r="VU2" t="n">
+        <v>286832</v>
+      </c>
+      <c r="VV2" t="n">
+        <v>653606</v>
+      </c>
+      <c r="VW2" t="n">
+        <v>1115002</v>
+      </c>
+      <c r="VX2" t="n">
+        <v>794837</v>
+      </c>
+      <c r="VY2" t="n">
+        <v>356547</v>
+      </c>
+      <c r="VZ2" t="n">
+        <v>230346</v>
+      </c>
+      <c r="WA2" t="n">
+        <v>772912</v>
+      </c>
+      <c r="WB2" t="n">
+        <v>798088</v>
+      </c>
+      <c r="WC2" t="n">
+        <v>497148</v>
+      </c>
+      <c r="WD2" t="n">
+        <v>1229042</v>
+      </c>
+      <c r="WE2" t="n">
+        <v>910565</v>
+      </c>
+      <c r="WF2" t="n">
+        <v>882677</v>
+      </c>
+      <c r="WG2" t="n">
+        <v>885658</v>
+      </c>
+      <c r="WH2" t="n">
+        <v>157350</v>
+      </c>
+      <c r="WI2" t="n">
+        <v>348466</v>
+      </c>
+      <c r="WJ2" t="n">
+        <v>304882</v>
+      </c>
+      <c r="WK2" t="n">
+        <v>1106710</v>
+      </c>
+      <c r="WL2" t="n">
+        <v>538068</v>
+      </c>
+      <c r="WM2" t="n">
+        <v>12236</v>
+      </c>
+      <c r="WN2" t="n">
+        <v>898113</v>
+      </c>
+      <c r="WO2" t="n">
+        <v>70054</v>
+      </c>
+      <c r="WP2" t="n">
+        <v>327336</v>
+      </c>
+      <c r="WQ2" t="n">
+        <v>31279</v>
+      </c>
+      <c r="WR2" t="n">
+        <v>234524</v>
+      </c>
+      <c r="WS2" t="n">
+        <v>822091</v>
+      </c>
+      <c r="WT2" t="n">
+        <v>950638</v>
+      </c>
+      <c r="WU2" t="n">
+        <v>952756</v>
+      </c>
+      <c r="WV2" t="n">
+        <v>525008</v>
+      </c>
+      <c r="WW2" t="n">
+        <v>760641</v>
+      </c>
+      <c r="WX2" t="n">
+        <v>616376</v>
+      </c>
+      <c r="WY2" t="n">
+        <v>463813</v>
+      </c>
+      <c r="WZ2" t="n">
+        <v>546549</v>
+      </c>
+      <c r="XA2" t="n">
+        <v>126111</v>
+      </c>
+      <c r="XB2" t="n">
+        <v>422004</v>
+      </c>
+      <c r="XC2" t="n">
+        <v>770747</v>
+      </c>
+      <c r="XD2" t="n">
+        <v>717803</v>
+      </c>
+      <c r="XE2" t="n">
+        <v>411498</v>
+      </c>
+      <c r="XF2" t="n">
+        <v>557635</v>
+      </c>
+      <c r="XG2" t="n">
+        <v>621162</v>
+      </c>
+      <c r="XH2" t="n">
+        <v>645318</v>
+      </c>
+      <c r="XI2" t="n">
+        <v>405972</v>
+      </c>
+      <c r="XJ2" t="n">
+        <v>691184</v>
+      </c>
+      <c r="XK2" t="n">
+        <v>916292</v>
+      </c>
+      <c r="XL2" t="n">
+        <v>599938</v>
+      </c>
+      <c r="XM2" t="n">
+        <v>610941</v>
+      </c>
+      <c r="XN2" t="n">
+        <v>814170</v>
+      </c>
+      <c r="XO2" t="n">
+        <v>936989</v>
+      </c>
+      <c r="XP2" t="n">
+        <v>910642</v>
+      </c>
+      <c r="XQ2" t="n">
+        <v>880236</v>
+      </c>
+      <c r="XR2" t="n">
+        <v>712765</v>
+      </c>
+      <c r="XS2" t="n">
+        <v>378374</v>
+      </c>
+      <c r="XT2" t="n">
+        <v>1149977</v>
+      </c>
+      <c r="XU2" t="n">
+        <v>325285</v>
+      </c>
+      <c r="XV2" t="n">
+        <v>364096</v>
+      </c>
+      <c r="XW2" t="n">
+        <v>862731</v>
+      </c>
+      <c r="XX2" t="n">
+        <v>29343</v>
+      </c>
+      <c r="XY2" t="n">
+        <v>927050</v>
+      </c>
+      <c r="XZ2" t="n">
+        <v>143672</v>
+      </c>
+      <c r="YA2" t="n">
+        <v>1179367</v>
+      </c>
+      <c r="YB2" t="n">
+        <v>762395</v>
+      </c>
+      <c r="YC2" t="n">
+        <v>966361</v>
+      </c>
+      <c r="YD2" t="n">
+        <v>618058</v>
+      </c>
+      <c r="YE2" t="n">
+        <v>91321</v>
+      </c>
+      <c r="YF2" t="n">
+        <v>1168933</v>
+      </c>
+      <c r="YG2" t="n">
+        <v>855895</v>
+      </c>
+      <c r="YH2" t="n">
+        <v>429332</v>
+      </c>
+      <c r="YI2" t="n">
+        <v>137920</v>
+      </c>
+      <c r="YJ2" t="n">
+        <v>433934</v>
+      </c>
+      <c r="YK2" t="n">
+        <v>466476</v>
+      </c>
+      <c r="YL2" t="n">
+        <v>1176047</v>
+      </c>
+      <c r="YM2" t="n">
+        <v>1080339</v>
+      </c>
+      <c r="YN2" t="n">
+        <v>495906</v>
+      </c>
+      <c r="YO2" t="n">
+        <v>267779</v>
+      </c>
+      <c r="YP2" t="n">
+        <v>110251</v>
+      </c>
+      <c r="YQ2" t="n">
+        <v>21136</v>
+      </c>
+      <c r="YR2" t="n">
+        <v>109692</v>
+      </c>
+      <c r="YS2" t="n">
+        <v>756907</v>
+      </c>
+      <c r="YT2" t="n">
+        <v>850191</v>
+      </c>
+      <c r="YU2" t="n">
+        <v>535148</v>
+      </c>
+      <c r="YV2" t="n">
+        <v>360766</v>
+      </c>
+      <c r="YW2" t="n">
+        <v>923132</v>
+      </c>
+      <c r="YX2" t="n">
+        <v>740612</v>
+      </c>
+      <c r="YY2" t="n">
+        <v>891825</v>
+      </c>
+      <c r="YZ2" t="n">
+        <v>1221936</v>
+      </c>
+      <c r="ZA2" t="n">
+        <v>515786</v>
+      </c>
+      <c r="ZB2" t="n">
+        <v>988268</v>
+      </c>
+      <c r="ZC2" t="n">
+        <v>75080</v>
+      </c>
+      <c r="ZD2" t="n">
+        <v>1227714</v>
+      </c>
+      <c r="ZE2" t="n">
+        <v>276375</v>
+      </c>
+      <c r="ZF2" t="n">
+        <v>264362</v>
+      </c>
+      <c r="ZG2" t="n">
+        <v>837042</v>
+      </c>
+      <c r="ZH2" t="n">
+        <v>785866</v>
+      </c>
+      <c r="ZI2" t="n">
+        <v>79142</v>
+      </c>
+      <c r="ZJ2" t="n">
+        <v>510102</v>
+      </c>
+      <c r="ZK2" t="n">
+        <v>367943</v>
+      </c>
+      <c r="ZL2" t="n">
+        <v>865265</v>
+      </c>
+      <c r="ZM2" t="n">
+        <v>401524</v>
+      </c>
+      <c r="ZN2" t="n">
+        <v>746440</v>
+      </c>
+      <c r="ZO2" t="n">
+        <v>619181</v>
+      </c>
+      <c r="ZP2" t="n">
+        <v>397566</v>
+      </c>
+      <c r="ZQ2" t="n">
+        <v>606593</v>
+      </c>
+      <c r="ZR2" t="n">
+        <v>381536</v>
+      </c>
+      <c r="ZS2" t="n">
+        <v>891819</v>
+      </c>
+      <c r="ZT2" t="n">
+        <v>223769</v>
+      </c>
+      <c r="ZU2" t="n">
+        <v>129806</v>
+      </c>
+      <c r="ZV2" t="n">
+        <v>586111</v>
+      </c>
+      <c r="ZW2" t="n">
+        <v>609709</v>
+      </c>
+      <c r="ZX2" t="n">
+        <v>705531</v>
+      </c>
+      <c r="ZY2" t="n">
+        <v>691943</v>
+      </c>
+      <c r="ZZ2" t="n">
+        <v>404280</v>
+      </c>
+      <c r="AAA2" t="n">
+        <v>1140290</v>
+      </c>
+      <c r="AAB2" t="n">
+        <v>605803</v>
+      </c>
+      <c r="AAC2" t="n">
+        <v>984410</v>
+      </c>
+      <c r="AAD2" t="n">
+        <v>108454</v>
+      </c>
+      <c r="AAE2" t="n">
+        <v>826752</v>
+      </c>
+      <c r="AAF2" t="n">
+        <v>680716</v>
+      </c>
+      <c r="AAG2" t="n">
+        <v>373182</v>
+      </c>
+      <c r="AAH2" t="n">
+        <v>995389</v>
+      </c>
+      <c r="AAI2" t="n">
+        <v>665059</v>
+      </c>
+      <c r="AAJ2" t="n">
+        <v>588683</v>
+      </c>
+      <c r="AAK2" t="n">
+        <v>217367</v>
+      </c>
+      <c r="AAL2" t="n">
+        <v>142718</v>
+      </c>
+      <c r="AAM2" t="n">
+        <v>254332</v>
+      </c>
+      <c r="AAN2" t="n">
+        <v>643322</v>
+      </c>
+      <c r="AAO2" t="n">
+        <v>171419</v>
+      </c>
+      <c r="AAP2" t="n">
+        <v>181314</v>
+      </c>
+      <c r="AAQ2" t="n">
+        <v>1060224</v>
+      </c>
+      <c r="AAR2" t="n">
+        <v>425745</v>
+      </c>
+      <c r="AAS2" t="n">
+        <v>192659</v>
+      </c>
+      <c r="AAT2" t="n">
+        <v>255118</v>
+      </c>
+      <c r="AAU2" t="n">
+        <v>1092448</v>
+      </c>
+      <c r="AAV2" t="n">
+        <v>277546</v>
+      </c>
+      <c r="AAW2" t="n">
+        <v>820208</v>
+      </c>
+      <c r="AAX2" t="n">
+        <v>100328</v>
+      </c>
+      <c r="AAY2" t="n">
+        <v>242690</v>
+      </c>
+      <c r="AAZ2" t="n">
+        <v>498302</v>
+      </c>
+      <c r="ABA2" t="n">
+        <v>101502</v>
+      </c>
+      <c r="ABB2" t="n">
+        <v>518606</v>
+      </c>
+      <c r="ABC2" t="n">
+        <v>819086</v>
+      </c>
+      <c r="ABD2" t="n">
+        <v>220283</v>
+      </c>
+      <c r="ABE2" t="n">
+        <v>91235</v>
+      </c>
+      <c r="ABF2" t="n">
+        <v>518142</v>
+      </c>
+      <c r="ABG2" t="n">
+        <v>997003</v>
+      </c>
+      <c r="ABH2" t="n">
+        <v>100485</v>
+      </c>
+      <c r="ABI2" t="n">
+        <v>8574</v>
+      </c>
+      <c r="ABJ2" t="n">
+        <v>198253</v>
+      </c>
+      <c r="ABK2" t="n">
+        <v>900967</v>
+      </c>
+      <c r="ABL2" t="n">
+        <v>1203950</v>
+      </c>
+      <c r="ABM2" t="n">
+        <v>1148845</v>
+      </c>
+      <c r="ABN2" t="n">
+        <v>247340</v>
+      </c>
+      <c r="ABO2" t="n">
+        <v>222958</v>
+      </c>
+      <c r="ABP2" t="n">
+        <v>216745</v>
+      </c>
+      <c r="ABQ2" t="n">
+        <v>546718</v>
+      </c>
+      <c r="ABR2" t="n">
+        <v>236540</v>
+      </c>
+      <c r="ABS2" t="n">
+        <v>311426</v>
+      </c>
+      <c r="ABT2" t="n">
+        <v>389228</v>
+      </c>
+      <c r="ABU2" t="n">
+        <v>521066</v>
+      </c>
+      <c r="ABV2" t="n">
+        <v>157368</v>
+      </c>
+      <c r="ABW2" t="n">
+        <v>1182363</v>
+      </c>
+      <c r="ABX2" t="n">
+        <v>761251</v>
+      </c>
+      <c r="ABY2" t="n">
+        <v>742671</v>
+      </c>
+      <c r="ABZ2" t="n">
+        <v>533593</v>
+      </c>
+      <c r="ACA2" t="n">
+        <v>1099396</v>
+      </c>
+      <c r="ACB2" t="n">
+        <v>123733</v>
+      </c>
+      <c r="ACC2" t="n">
+        <v>941653</v>
+      </c>
+      <c r="ACD2" t="n">
+        <v>874131</v>
+      </c>
+      <c r="ACE2" t="n">
+        <v>17740</v>
+      </c>
+      <c r="ACF2" t="n">
+        <v>938393</v>
+      </c>
+      <c r="ACG2" t="n">
+        <v>493518</v>
+      </c>
+      <c r="ACH2" t="n">
+        <v>488965</v>
+      </c>
+      <c r="ACI2" t="n">
+        <v>590898</v>
+      </c>
+      <c r="ACJ2" t="n">
+        <v>474129</v>
+      </c>
+      <c r="ACK2" t="n">
+        <v>635480</v>
+      </c>
+      <c r="ACL2" t="n">
+        <v>1023758</v>
+      </c>
+      <c r="ACM2" t="n">
+        <v>398496</v>
+      </c>
+      <c r="ACN2" t="n">
+        <v>199757</v>
+      </c>
+      <c r="ACO2" t="n">
+        <v>781386</v>
+      </c>
+      <c r="ACP2" t="n">
+        <v>2994</v>
+      </c>
+      <c r="ACQ2" t="n">
+        <v>90812</v>
+      </c>
+      <c r="ACR2" t="n">
+        <v>91710</v>
+      </c>
+      <c r="ACS2" t="n">
+        <v>1045531</v>
+      </c>
+      <c r="ACT2" t="n">
+        <v>1039699</v>
+      </c>
+      <c r="ACU2" t="n">
+        <v>592059</v>
+      </c>
+      <c r="ACV2" t="n">
+        <v>308807</v>
+      </c>
+      <c r="ACW2" t="n">
+        <v>24712</v>
+      </c>
+      <c r="ACX2" t="n">
+        <v>253416</v>
+      </c>
+      <c r="ACY2" t="n">
+        <v>836282</v>
+      </c>
+      <c r="ACZ2" t="n">
+        <v>677416</v>
+      </c>
+      <c r="ADA2" t="n">
+        <v>199507</v>
+      </c>
+      <c r="ADB2" t="n">
+        <v>356726</v>
+      </c>
+      <c r="ADC2" t="n">
+        <v>561863</v>
+      </c>
+      <c r="ADD2" t="n">
+        <v>393182</v>
+      </c>
+      <c r="ADE2" t="n">
+        <v>416656</v>
+      </c>
+      <c r="ADF2" t="n">
+        <v>473375</v>
+      </c>
+      <c r="ADG2" t="n">
+        <v>420905</v>
+      </c>
+      <c r="ADH2" t="n">
+        <v>231923</v>
+      </c>
+      <c r="ADI2" t="n">
+        <v>316396</v>
+      </c>
+      <c r="ADJ2" t="n">
+        <v>828430</v>
+      </c>
+      <c r="ADK2" t="n">
+        <v>51280</v>
+      </c>
+      <c r="ADL2" t="n">
+        <v>495391</v>
+      </c>
+      <c r="ADM2" t="n">
+        <v>694869</v>
+      </c>
+      <c r="ADN2" t="n">
+        <v>204180</v>
+      </c>
+      <c r="ADO2" t="n">
+        <v>185358</v>
+      </c>
+      <c r="ADP2" t="n">
+        <v>818149</v>
+      </c>
+      <c r="ADQ2" t="n">
+        <v>1057807</v>
+      </c>
+      <c r="ADR2" t="n">
+        <v>1065785</v>
+      </c>
+      <c r="ADS2" t="n">
+        <v>331471</v>
+      </c>
+      <c r="ADT2" t="n">
+        <v>68684</v>
+      </c>
+      <c r="ADU2" t="n">
+        <v>1176413</v>
+      </c>
+      <c r="ADV2" t="n">
+        <v>487268</v>
+      </c>
+      <c r="ADW2" t="n">
+        <v>438375</v>
+      </c>
+      <c r="ADX2" t="n">
+        <v>1207370</v>
+      </c>
+      <c r="ADY2" t="n">
+        <v>8041</v>
+      </c>
+      <c r="ADZ2" t="n">
+        <v>400306</v>
+      </c>
+      <c r="AEA2" t="n">
+        <v>415218</v>
+      </c>
+      <c r="AEB2" t="n">
+        <v>550912</v>
+      </c>
+      <c r="AEC2" t="n">
+        <v>669375</v>
+      </c>
+      <c r="AED2" t="n">
+        <v>1109673</v>
+      </c>
+      <c r="AEE2" t="n">
+        <v>329416</v>
+      </c>
+      <c r="AEF2" t="n">
+        <v>418551</v>
+      </c>
+      <c r="AEG2" t="n">
+        <v>802093</v>
+      </c>
+      <c r="AEH2" t="n">
+        <v>120294</v>
+      </c>
+      <c r="AEI2" t="n">
+        <v>926694</v>
+      </c>
+      <c r="AEJ2" t="n">
+        <v>649208</v>
+      </c>
+      <c r="AEK2" t="n">
+        <v>308902</v>
+      </c>
+      <c r="AEL2" t="n">
+        <v>339951</v>
+      </c>
+      <c r="AEM2" t="n">
+        <v>258139</v>
+      </c>
+      <c r="AEN2" t="n">
+        <v>175551</v>
+      </c>
+      <c r="AEO2" t="n">
+        <v>434361</v>
+      </c>
+      <c r="AEP2" t="n">
+        <v>32796</v>
+      </c>
+      <c r="AEQ2" t="n">
+        <v>1158676</v>
+      </c>
+      <c r="AER2" t="n">
+        <v>391381</v>
+      </c>
+      <c r="AES2" t="n">
+        <v>1215600</v>
+      </c>
+      <c r="AET2" t="n">
+        <v>182402</v>
+      </c>
+      <c r="AEU2" t="n">
+        <v>395202</v>
+      </c>
+      <c r="AEV2" t="n">
+        <v>798533</v>
+      </c>
+      <c r="AEW2" t="n">
+        <v>229114</v>
+      </c>
+      <c r="AEX2" t="n">
+        <v>1016265</v>
+      </c>
+      <c r="AEY2" t="n">
+        <v>846865</v>
+      </c>
+      <c r="AEZ2" t="n">
+        <v>844434</v>
+      </c>
+      <c r="AFA2" t="n">
+        <v>687027</v>
+      </c>
+      <c r="AFB2" t="n">
+        <v>1186257</v>
+      </c>
+      <c r="AFC2" t="n">
+        <v>349484</v>
+      </c>
+      <c r="AFD2" t="n">
+        <v>203591</v>
+      </c>
+      <c r="AFE2" t="n">
+        <v>819902</v>
+      </c>
+      <c r="AFF2" t="n">
+        <v>1079179</v>
+      </c>
+      <c r="AFG2" t="n">
+        <v>189700</v>
+      </c>
+      <c r="AFH2" t="n">
+        <v>133724</v>
+      </c>
+      <c r="AFI2" t="n">
+        <v>579172</v>
+      </c>
+      <c r="AFJ2" t="n">
+        <v>1056231</v>
+      </c>
+      <c r="AFK2" t="n">
+        <v>596055</v>
+      </c>
+      <c r="AFL2" t="n">
+        <v>1222546</v>
+      </c>
+      <c r="AFM2" t="n">
+        <v>422254</v>
+      </c>
+      <c r="AFN2" t="n">
+        <v>643258</v>
+      </c>
+      <c r="AFO2" t="n">
+        <v>1043590</v>
+      </c>
+      <c r="AFP2" t="n">
+        <v>635681</v>
+      </c>
+      <c r="AFQ2" t="n">
+        <v>288211</v>
+      </c>
+      <c r="AFR2" t="n">
+        <v>845843</v>
+      </c>
+      <c r="AFS2" t="n">
+        <v>80640</v>
+      </c>
+      <c r="AFT2" t="n">
+        <v>241309</v>
+      </c>
+      <c r="AFU2" t="n">
+        <v>22561</v>
+      </c>
+      <c r="AFV2" t="n">
+        <v>1182715</v>
+      </c>
+      <c r="AFW2" t="n">
+        <v>1083183</v>
+      </c>
+      <c r="AFX2" t="n">
+        <v>904698</v>
+      </c>
+      <c r="AFY2" t="n">
+        <v>469401</v>
+      </c>
+      <c r="AFZ2" t="n">
+        <v>34123</v>
+      </c>
+      <c r="AGA2" t="n">
+        <v>949521</v>
+      </c>
+      <c r="AGB2" t="n">
+        <v>137372</v>
+      </c>
+      <c r="AGC2" t="n">
+        <v>699426</v>
+      </c>
+      <c r="AGD2" t="n">
+        <v>293176</v>
+      </c>
+      <c r="AGE2" t="n">
+        <v>663580</v>
+      </c>
+      <c r="AGF2" t="n">
+        <v>152895</v>
+      </c>
+      <c r="AGG2" t="n">
+        <v>528671</v>
+      </c>
+      <c r="AGH2" t="n">
+        <v>880986</v>
+      </c>
+      <c r="AGI2" t="n">
+        <v>9294</v>
+      </c>
+      <c r="AGJ2" t="n">
+        <v>59422</v>
+      </c>
+      <c r="AGK2" t="n">
+        <v>1075254</v>
+      </c>
+      <c r="AGL2" t="n">
+        <v>123656</v>
+      </c>
+      <c r="AGM2" t="n">
+        <v>269538</v>
+      </c>
+      <c r="AGN2" t="n">
+        <v>731172</v>
+      </c>
+      <c r="AGO2" t="n">
+        <v>260268</v>
+      </c>
+      <c r="AGP2" t="n">
+        <v>790350</v>
+      </c>
+      <c r="AGQ2" t="n">
+        <v>278751</v>
+      </c>
+      <c r="AGR2" t="n">
+        <v>1154355</v>
+      </c>
+      <c r="AGS2" t="n">
+        <v>300044</v>
+      </c>
+      <c r="AGT2" t="n">
+        <v>281304</v>
+      </c>
+      <c r="AGU2" t="n">
+        <v>1023649</v>
+      </c>
+      <c r="AGV2" t="n">
+        <v>633810</v>
+      </c>
+      <c r="AGW2" t="n">
+        <v>776386</v>
+      </c>
+      <c r="AGX2" t="n">
+        <v>116482</v>
+      </c>
+      <c r="AGY2" t="n">
+        <v>808868</v>
+      </c>
+      <c r="AGZ2" t="n">
+        <v>713093</v>
+      </c>
+      <c r="AHA2" t="n">
+        <v>293846</v>
+      </c>
+      <c r="AHB2" t="n">
+        <v>24666</v>
+      </c>
+      <c r="AHC2" t="n">
+        <v>808317</v>
+      </c>
+      <c r="AHD2" t="n">
+        <v>89770</v>
+      </c>
+      <c r="AHE2" t="n">
+        <v>154995</v>
+      </c>
+      <c r="AHF2" t="n">
+        <v>1129955</v>
+      </c>
+      <c r="AHG2" t="n">
+        <v>331743</v>
+      </c>
+      <c r="AHH2" t="n">
+        <v>1088828</v>
+      </c>
+      <c r="AHI2" t="n">
+        <v>165227</v>
+      </c>
+      <c r="AHJ2" t="n">
+        <v>729794</v>
+      </c>
+      <c r="AHK2" t="n">
+        <v>39906</v>
+      </c>
+      <c r="AHL2" t="n">
+        <v>402886</v>
+      </c>
+      <c r="AHM2" t="n">
+        <v>127357</v>
+      </c>
+      <c r="AHN2" t="n">
+        <v>167325</v>
+      </c>
+      <c r="AHO2" t="n">
+        <v>140164</v>
+      </c>
+      <c r="AHP2" t="n">
+        <v>669687</v>
+      </c>
+      <c r="AHQ2" t="n">
+        <v>888367</v>
+      </c>
+      <c r="AHR2" t="n">
+        <v>984842</v>
+      </c>
+      <c r="AHS2" t="n">
+        <v>561520</v>
+      </c>
+      <c r="AHT2" t="n">
+        <v>130965</v>
+      </c>
+      <c r="AHU2" t="n">
+        <v>270065</v>
+      </c>
+      <c r="AHV2" t="n">
+        <v>127521</v>
+      </c>
+      <c r="AHW2" t="n">
+        <v>337548</v>
+      </c>
+      <c r="AHX2" t="n">
+        <v>113758</v>
+      </c>
+      <c r="AHY2" t="n">
+        <v>95725</v>
+      </c>
+      <c r="AHZ2" t="n">
+        <v>296959</v>
+      </c>
+      <c r="AIA2" t="n">
+        <v>899720</v>
+      </c>
+      <c r="AIB2" t="n">
+        <v>680969</v>
+      </c>
+      <c r="AIC2" t="n">
+        <v>1089122</v>
+      </c>
+      <c r="AID2" t="n">
+        <v>605739</v>
+      </c>
+      <c r="AIE2" t="n">
+        <v>1111892</v>
+      </c>
+      <c r="AIF2" t="n">
+        <v>687334</v>
+      </c>
+      <c r="AIG2" t="n">
+        <v>342889</v>
+      </c>
+      <c r="AIH2" t="n">
+        <v>992459</v>
+      </c>
+      <c r="AII2" t="n">
+        <v>967080</v>
+      </c>
+      <c r="AIJ2" t="n">
+        <v>672114</v>
+      </c>
+      <c r="AIK2" t="n">
+        <v>53176</v>
+      </c>
+      <c r="AIL2" t="n">
+        <v>201622</v>
+      </c>
+      <c r="AIM2" t="n">
+        <v>714437</v>
+      </c>
+      <c r="AIN2" t="n">
+        <v>696760</v>
+      </c>
+      <c r="AIO2" t="n">
+        <v>48674</v>
+      </c>
+      <c r="AIP2" t="n">
+        <v>385866</v>
+      </c>
+      <c r="AIQ2" t="n">
+        <v>55283</v>
+      </c>
+      <c r="AIR2" t="n">
+        <v>1142275</v>
+      </c>
+      <c r="AIS2" t="n">
+        <v>1001334</v>
+      </c>
+      <c r="AIT2" t="n">
+        <v>607659</v>
+      </c>
+      <c r="AIU2" t="n">
+        <v>229203</v>
+      </c>
+      <c r="AIV2" t="n">
+        <v>249810</v>
+      </c>
+      <c r="AIW2" t="n">
+        <v>432153</v>
+      </c>
+      <c r="AIX2" t="n">
+        <v>824707</v>
+      </c>
+      <c r="AIY2" t="n">
+        <v>1202125</v>
+      </c>
+      <c r="AIZ2" t="n">
+        <v>668406</v>
+      </c>
+      <c r="AJA2" t="n">
+        <v>2707</v>
+      </c>
+      <c r="AJB2" t="n">
+        <v>939433</v>
+      </c>
+      <c r="AJC2" t="n">
+        <v>623545</v>
+      </c>
+      <c r="AJD2" t="n">
+        <v>936317</v>
+      </c>
+      <c r="AJE2" t="n">
+        <v>697027</v>
+      </c>
+      <c r="AJF2" t="n">
+        <v>166647</v>
+      </c>
+      <c r="AJG2" t="n">
+        <v>958016</v>
+      </c>
+      <c r="AJH2" t="n">
+        <v>409340</v>
+      </c>
+      <c r="AJI2" t="n">
+        <v>145429</v>
+      </c>
+      <c r="AJJ2" t="n">
+        <v>840747</v>
+      </c>
+      <c r="AJK2" t="n">
+        <v>935213</v>
+      </c>
+      <c r="AJL2" t="n">
+        <v>184656</v>
+      </c>
+      <c r="AJM2" t="n">
+        <v>378640</v>
+      </c>
+      <c r="AJN2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJO2" t="n">
+        <v>460072</v>
+      </c>
+      <c r="AJP2" t="n">
+        <v>1197875</v>
+      </c>
+      <c r="AJQ2" t="n">
+        <v>725754</v>
+      </c>
+      <c r="AJR2" t="n">
+        <v>67414</v>
+      </c>
+      <c r="AJS2" t="n">
+        <v>450503</v>
+      </c>
+      <c r="AJT2" t="n">
+        <v>15140</v>
+      </c>
+      <c r="AJU2" t="n">
+        <v>739273</v>
+      </c>
+      <c r="AJV2" t="n">
+        <v>869296</v>
+      </c>
+      <c r="AJW2" t="n">
+        <v>832765</v>
+      </c>
+      <c r="AJX2" t="n">
+        <v>834445</v>
+      </c>
+      <c r="AJY2" t="n">
+        <v>26747</v>
+      </c>
+      <c r="AJZ2" t="n">
+        <v>661142</v>
+      </c>
+      <c r="AKA2" t="n">
+        <v>262552</v>
+      </c>
+      <c r="AKB2" t="n">
+        <v>360360</v>
+      </c>
+      <c r="AKC2" t="n">
+        <v>769166</v>
+      </c>
+      <c r="AKD2" t="n">
+        <v>780195</v>
+      </c>
+      <c r="AKE2" t="n">
+        <v>572883</v>
+      </c>
+      <c r="AKF2" t="n">
+        <v>1195308</v>
+      </c>
+      <c r="AKG2" t="n">
+        <v>178591</v>
+      </c>
+      <c r="AKH2" t="n">
+        <v>464595</v>
+      </c>
+      <c r="AKI2" t="n">
+        <v>728697</v>
+      </c>
+      <c r="AKJ2" t="n">
+        <v>315240</v>
+      </c>
+      <c r="AKK2" t="n">
+        <v>902382</v>
+      </c>
+      <c r="AKL2" t="n">
+        <v>337049</v>
+      </c>
+      <c r="AKM2" t="n">
+        <v>590324</v>
+      </c>
+      <c r="AKN2" t="n">
+        <v>928264</v>
+      </c>
+      <c r="AKO2" t="n">
+        <v>62915</v>
+      </c>
+      <c r="AKP2" t="n">
+        <v>600119</v>
+      </c>
+      <c r="AKQ2" t="n">
+        <v>712414</v>
+      </c>
+      <c r="AKR2" t="n">
+        <v>169431</v>
+      </c>
+      <c r="AKS2" t="n">
+        <v>1148631</v>
+      </c>
+      <c r="AKT2" t="n">
+        <v>1222458</v>
+      </c>
+      <c r="AKU2" t="n">
+        <v>667351</v>
+      </c>
+      <c r="AKV2" t="n">
+        <v>1132384</v>
+      </c>
+      <c r="AKW2" t="n">
+        <v>145084</v>
+      </c>
+      <c r="AKX2" t="n">
+        <v>1032179</v>
+      </c>
+      <c r="AKY2" t="n">
+        <v>733803</v>
+      </c>
+      <c r="AKZ2" t="n">
+        <v>972811</v>
+      </c>
+      <c r="ALA2" t="n">
+        <v>623879</v>
+      </c>
+      <c r="ALB2" t="n">
+        <v>22551</v>
+      </c>
+      <c r="ALC2" t="n">
+        <v>870325</v>
+      </c>
+      <c r="ALD2" t="n">
+        <v>132689</v>
+      </c>
+      <c r="ALE2" t="n">
+        <v>563899</v>
+      </c>
+      <c r="ALF2" t="n">
+        <v>908265</v>
+      </c>
+      <c r="ALG2" t="n">
+        <v>612581</v>
+      </c>
+      <c r="ALH2" t="n">
+        <v>369622</v>
+      </c>
+      <c r="ALI2" t="n">
+        <v>638967</v>
+      </c>
+      <c r="ALJ2" t="n">
+        <v>484243</v>
+      </c>
+      <c r="ALK2" t="n">
+        <v>1050138</v>
+      </c>
+      <c r="ALL2" t="n">
+        <v>477610</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
@@ -619,24 +8646,6 @@
       <c r="B1" t="n">
         <v>3600000</v>
       </c>
-      <c r="C1" t="inlineStr"/>
-      <c r="D1" t="inlineStr"/>
-      <c r="E1" t="inlineStr"/>
-      <c r="F1" t="inlineStr"/>
-      <c r="G1" t="inlineStr"/>
-      <c r="H1" t="inlineStr"/>
-      <c r="I1" t="inlineStr"/>
-      <c r="J1" t="inlineStr"/>
-      <c r="K1" t="inlineStr"/>
-      <c r="L1" t="inlineStr"/>
-      <c r="M1" t="inlineStr"/>
-      <c r="N1" t="inlineStr"/>
-      <c r="O1" t="inlineStr"/>
-      <c r="P1" t="inlineStr"/>
-      <c r="Q1" t="inlineStr"/>
-      <c r="R1" t="inlineStr"/>
-      <c r="S1" t="inlineStr"/>
-      <c r="T1" t="inlineStr"/>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -698,6 +8707,522 @@
       </c>
       <c r="T2" t="n">
         <v>299</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:T2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="n">
+        <v>18858</v>
+      </c>
+      <c r="B1" t="n">
+        <v>3600000</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>7</v>
+      </c>
+      <c r="B2" t="n">
+        <v>1450</v>
+      </c>
+      <c r="C2" t="n">
+        <v>525</v>
+      </c>
+      <c r="D2" t="n">
+        <v>1001</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2" t="n">
+        <v>170</v>
+      </c>
+      <c r="G2" t="n">
+        <v>366</v>
+      </c>
+      <c r="H2" t="n">
+        <v>1101</v>
+      </c>
+      <c r="I2" t="n">
+        <v>1561</v>
+      </c>
+      <c r="J2" t="n">
+        <v>806</v>
+      </c>
+      <c r="K2" t="n">
+        <v>640</v>
+      </c>
+      <c r="L2" t="n">
+        <v>311</v>
+      </c>
+      <c r="M2" t="n">
+        <v>1310</v>
+      </c>
+      <c r="N2" t="n">
+        <v>560</v>
+      </c>
+      <c r="O2" t="n">
+        <v>1210</v>
+      </c>
+      <c r="P2" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>1227</v>
+      </c>
+      <c r="R2" t="n">
+        <v>805</v>
+      </c>
+      <c r="S2" t="n">
+        <v>440</v>
+      </c>
+      <c r="T2" t="n">
+        <v>74</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:J2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="n">
+        <v>100444</v>
+      </c>
+      <c r="B1" t="n">
+        <v>1324891</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>0</v>
+      </c>
+      <c r="B2" t="n">
+        <v>118</v>
+      </c>
+      <c r="C2" t="n">
+        <v>4829</v>
+      </c>
+      <c r="D2" t="n">
+        <v>6855</v>
+      </c>
+      <c r="E2" t="n">
+        <v>10147</v>
+      </c>
+      <c r="F2" t="n">
+        <v>11821</v>
+      </c>
+      <c r="G2" t="n">
+        <v>3140</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2" t="n">
+        <v>6950</v>
+      </c>
+      <c r="J2" t="n">
+        <v>3829</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:J2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="n">
+        <v>98721</v>
+      </c>
+      <c r="B1" t="n">
+        <v>705075</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>801</v>
+      </c>
+      <c r="B2" t="n">
+        <v>1033</v>
+      </c>
+      <c r="C2" t="n">
+        <v>6539</v>
+      </c>
+      <c r="D2" t="n">
+        <v>8547</v>
+      </c>
+      <c r="E2" t="n">
+        <v>6914</v>
+      </c>
+      <c r="F2" t="n">
+        <v>9691</v>
+      </c>
+      <c r="G2" t="n">
+        <v>4850</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2" t="n">
+        <v>2070</v>
+      </c>
+      <c r="J2" t="n">
+        <v>5521</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:CV2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="n">
+        <v>7018823</v>
+      </c>
+      <c r="B1" t="n">
+        <v>3600215</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>3319</v>
+      </c>
+      <c r="B2" t="n">
+        <v>87756</v>
+      </c>
+      <c r="C2" t="n">
+        <v>71728</v>
+      </c>
+      <c r="D2" t="n">
+        <v>125294</v>
+      </c>
+      <c r="E2" t="n">
+        <v>30398</v>
+      </c>
+      <c r="F2" t="n">
+        <v>126522</v>
+      </c>
+      <c r="G2" t="n">
+        <v>88767</v>
+      </c>
+      <c r="H2" t="n">
+        <v>117938</v>
+      </c>
+      <c r="I2" t="n">
+        <v>123870</v>
+      </c>
+      <c r="J2" t="n">
+        <v>22377</v>
+      </c>
+      <c r="K2" t="n">
+        <v>101023</v>
+      </c>
+      <c r="L2" t="n">
+        <v>27366</v>
+      </c>
+      <c r="M2" t="n">
+        <v>133606</v>
+      </c>
+      <c r="N2" t="n">
+        <v>22311</v>
+      </c>
+      <c r="O2" t="n">
+        <v>71330</v>
+      </c>
+      <c r="P2" t="n">
+        <v>108946</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>83758</v>
+      </c>
+      <c r="R2" t="n">
+        <v>16156</v>
+      </c>
+      <c r="S2" t="n">
+        <v>84266</v>
+      </c>
+      <c r="T2" t="n">
+        <v>5595</v>
+      </c>
+      <c r="U2" t="n">
+        <v>139502</v>
+      </c>
+      <c r="V2" t="n">
+        <v>80539</v>
+      </c>
+      <c r="W2" t="n">
+        <v>7438</v>
+      </c>
+      <c r="X2" t="n">
+        <v>142740</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>137172</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>61563</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>69747</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>97218</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>24937</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>1301</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>94875</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>107899</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>52123</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>55280</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>17968</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>56411</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>41558</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>119898</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>53384</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>91001</v>
+      </c>
+      <c r="AO2" t="n">
+        <v>252</v>
+      </c>
+      <c r="AP2" t="n">
+        <v>112754</v>
+      </c>
+      <c r="AQ2" t="n">
+        <v>61564</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>42014</v>
+      </c>
+      <c r="AS2" t="n">
+        <v>65670</v>
+      </c>
+      <c r="AT2" t="n">
+        <v>129689</v>
+      </c>
+      <c r="AU2" t="n">
+        <v>42248</v>
+      </c>
+      <c r="AV2" t="n">
+        <v>32035</v>
+      </c>
+      <c r="AW2" t="n">
+        <v>86333</v>
+      </c>
+      <c r="AX2" t="n">
+        <v>64337</v>
+      </c>
+      <c r="AY2" t="n">
+        <v>129496</v>
+      </c>
+      <c r="AZ2" t="n">
+        <v>80751</v>
+      </c>
+      <c r="BA2" t="n">
+        <v>38414</v>
+      </c>
+      <c r="BB2" t="n">
+        <v>103152</v>
+      </c>
+      <c r="BC2" t="n">
+        <v>91938</v>
+      </c>
+      <c r="BD2" t="n">
+        <v>9432</v>
+      </c>
+      <c r="BE2" t="n">
+        <v>44044</v>
+      </c>
+      <c r="BF2" t="n">
+        <v>22663</v>
+      </c>
+      <c r="BG2" t="n">
+        <v>12312</v>
+      </c>
+      <c r="BH2" t="n">
+        <v>104341</v>
+      </c>
+      <c r="BI2" t="n">
+        <v>14197</v>
+      </c>
+      <c r="BJ2" t="n">
+        <v>36750</v>
+      </c>
+      <c r="BK2" t="n">
+        <v>4870</v>
+      </c>
+      <c r="BL2" t="n">
+        <v>112210</v>
+      </c>
+      <c r="BM2" t="n">
+        <v>9469</v>
+      </c>
+      <c r="BN2" t="n">
+        <v>77515</v>
+      </c>
+      <c r="BO2" t="n">
+        <v>48394</v>
+      </c>
+      <c r="BP2" t="n">
+        <v>11797</v>
+      </c>
+      <c r="BQ2" t="n">
+        <v>122215</v>
+      </c>
+      <c r="BR2" t="n">
+        <v>27344</v>
+      </c>
+      <c r="BS2" t="n">
+        <v>2513</v>
+      </c>
+      <c r="BT2" t="n">
+        <v>110947</v>
+      </c>
+      <c r="BU2" t="n">
+        <v>20816</v>
+      </c>
+      <c r="BV2" t="n">
+        <v>75106</v>
+      </c>
+      <c r="BW2" t="n">
+        <v>61869</v>
+      </c>
+      <c r="BX2" t="n">
+        <v>31494</v>
+      </c>
+      <c r="BY2" t="n">
+        <v>74761</v>
+      </c>
+      <c r="BZ2" t="n">
+        <v>59436</v>
+      </c>
+      <c r="CA2" t="n">
+        <v>115253</v>
+      </c>
+      <c r="CB2" t="n">
+        <v>47748</v>
+      </c>
+      <c r="CC2" t="n">
+        <v>37524</v>
+      </c>
+      <c r="CD2" t="n">
+        <v>15894</v>
+      </c>
+      <c r="CE2" t="n">
+        <v>27862</v>
+      </c>
+      <c r="CF2" t="n">
+        <v>32333</v>
+      </c>
+      <c r="CG2" t="n">
+        <v>94645</v>
+      </c>
+      <c r="CH2" t="n">
+        <v>76148</v>
+      </c>
+      <c r="CI2" t="n">
+        <v>48852</v>
+      </c>
+      <c r="CJ2" t="n">
+        <v>45972</v>
+      </c>
+      <c r="CK2" t="n">
+        <v>68130</v>
+      </c>
+      <c r="CL2" t="n">
+        <v>67407</v>
+      </c>
+      <c r="CM2" t="n">
+        <v>10309</v>
+      </c>
+      <c r="CN2" t="n">
+        <v>34764</v>
+      </c>
+      <c r="CO2" t="n">
+        <v>105632</v>
+      </c>
+      <c r="CP2" t="n">
+        <v>17848</v>
+      </c>
+      <c r="CQ2" t="n">
+        <v>128746</v>
+      </c>
+      <c r="CR2" t="n">
+        <v>99615</v>
+      </c>
+      <c r="CS2" t="n">
+        <v>144923</v>
+      </c>
+      <c r="CT2" t="n">
+        <v>0</v>
+      </c>
+      <c r="CU2" t="n">
+        <v>116517</v>
+      </c>
+      <c r="CV2" t="n">
+        <v>97853</v>
       </c>
     </row>
   </sheetData>
